--- a/hiv/catalogo_HIV.xlsx
+++ b/hiv/catalogo_HIV.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L178"/>
+  <dimension ref="A1:N178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -451,12 +451,14 @@
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="35" customWidth="1" min="11" max="11"/>
-    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -492,30 +494,40 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Alcance geográfico da intervenção</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Recursos necessários para a implementação</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Ano de início</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Pop. elegível</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Cobertura</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Custo por unidade</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>URL da Ficha</t>
         </is>
@@ -554,26 +566,32 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>2.477.000</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>82.0%</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>0.09841212043675299</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_01.html</t>
         </is>
@@ -613,17 +631,19 @@
           <t>Apoiar de intervenção nas pessoas e comunidades afetadas pelo HIV</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_02.html</t>
         </is>
@@ -660,17 +680,19 @@
           <t>Apoiar de intervenção nas pessoas e comunidades afetadas pelo HIV</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_03.html</t>
         </is>
@@ -709,17 +731,19 @@
           <t>Apoiar de intervenção nas pessoas e comunidades afetadas pelo HIV</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_04.html</t>
         </is>
@@ -756,17 +780,19 @@
           <t>Apoiar de intervenção nas pessoas e comunidades afetadas pelo HIV</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_05.html</t>
         </is>
@@ -808,24 +834,26 @@
           <t>Apoiar de intervenção nas pessoas e comunidades afetadas pelo HIV</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>FY19Q1</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Todos pacientes elegíveis</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>US AJUDA PrEP (102) das províncias de Manica (37), Niassa (18), Sofala (23), Tete (24). Dados ate JAN 2026</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_06.html</t>
         </is>
@@ -862,12 +890,22 @@
           <t>Apoiar de intervenção nas pessoas e comunidades afetadas pelo HIV</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos qualificados</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_07.html</t>
         </is>
@@ -905,12 +943,22 @@
           <t>Aumentar a adesão ao tratamento</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Materiais de apoio</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_08.html</t>
         </is>
@@ -948,12 +996,22 @@
           <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_09.html</t>
         </is>
@@ -990,12 +1048,22 @@
           <t>Capacitar pessoal para suporte a PVHIV</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Formação e materiais de apoio</t>
+        </is>
+      </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_10.html</t>
         </is>
@@ -1032,12 +1100,22 @@
           <t>disponibilizar o pacote no plataforma telesaude</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_11.html</t>
         </is>
@@ -1075,12 +1153,22 @@
           <t>Aumentar a adesão ao tratamento</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais de apoio</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_12.html</t>
         </is>
@@ -1118,12 +1206,22 @@
           <t>Diagnosticar e tratar doenças mentais relacionadas</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Profissionais de saúde qualificados</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_13.html</t>
         </is>
@@ -1161,12 +1259,22 @@
           <t>Apoiar crianças na aceitação do diagnóstico</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Materiais educativos e formações</t>
+        </is>
+      </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_14.html</t>
         </is>
@@ -1204,12 +1312,22 @@
           <t>Prover ambientes seguros paraPVHIV</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Programa de certificação e avaliação</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_15.html</t>
         </is>
@@ -1247,12 +1365,22 @@
           <t>Melhorar o suporte às famílias</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Recursos e tecnologia para avaliação</t>
+        </is>
+      </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_16.html</t>
         </is>
@@ -1290,12 +1418,22 @@
           <t>Mobilizar pares para apoio às PVHIV</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Formadores e recursos informativos</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_17.html</t>
         </is>
@@ -1335,26 +1473,36 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Testes de autoavalição e materiais informativos</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>254.946</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>50.22630007782692</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>0.385679676495397</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_18.html</t>
         </is>
@@ -1394,26 +1542,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Materiais e reagentes para teste</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>2001</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>254.946</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>50.22630007782692</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0.537877067032586</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_19.html</t>
         </is>
@@ -1456,12 +1614,14 @@
           <t>Diagnosticar e tratar HIV</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>Desde o inicio do Projecto em 2019</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>Todos os pacientes elegiveis 
 Todas as portas e modalidades de testagem
@@ -1469,14 +1629,14 @@
 Conselheiros leigos</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>Todas as US AJUDA (149) Manica (51), Niassa(18), Sofala (47) e Tete (33)</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_20.html</t>
         </is>
@@ -1513,12 +1673,22 @@
           <t>Fortalecer a coordenação de ATS no MISAU</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Capacidade de gestão e coordenação</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_21.html</t>
         </is>
@@ -1555,12 +1725,22 @@
           <t>Melhorar a implementação de ATS</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Formação e supervisão de pessoal</t>
+        </is>
+      </c>
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_22.html</t>
         </is>
@@ -1598,12 +1778,22 @@
           <t>Aumentar a testagem e diagnósticos precoces</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Materiais e reagentes para teste</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_23.html</t>
         </is>
@@ -1641,12 +1831,22 @@
           <t>Aumentar a adesão à PrEP entre populações em risco</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais de apoio</t>
+        </is>
+      </c>
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_24.html</t>
         </is>
@@ -1684,12 +1884,22 @@
           <t>Diagnosticar e tratar pessoas com HIV rapidamente</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Treinamento e materiais informativos</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_25.html</t>
         </is>
@@ -1726,12 +1936,22 @@
           <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias e Communidade</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_26.html</t>
         </is>
@@ -1768,12 +1988,22 @@
           <t>Garantir a precisão no diagnóstico de HIV</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Materiais de formação e recursos humanos</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_27.html</t>
         </is>
@@ -1810,12 +2040,22 @@
           <t>disponibilizar o pacote no plataforma telesaude</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
+        </is>
+      </c>
       <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="3" t="inlineStr"/>
       <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_28.html</t>
         </is>
@@ -1852,12 +2092,22 @@
           <t>Expandir o acesso e uso do ATHIV</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para capacitação e equipamentos</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_29.html</t>
         </is>
@@ -1894,12 +2144,22 @@
           <t>Melhorar a qualidade do atendimento em ATS</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Materiais de formação e acompanhamento</t>
+        </is>
+      </c>
       <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="3" t="inlineStr"/>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_30.html</t>
         </is>
@@ -1936,12 +2196,22 @@
           <t>Aumentar a testagem e a adesão ao tratamento</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos qualificados e materiais</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_31.html</t>
         </is>
@@ -1979,12 +2249,22 @@
           <t>Aumentar a testagem em unidades clínicas</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Materiais de apoio e reagentes para teste</t>
+        </is>
+      </c>
       <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_32.html</t>
         </is>
@@ -2022,12 +2302,22 @@
           <t>Aumentar a testagem voluntária</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Recursos e sensibilização nas comunidades</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_33.html</t>
         </is>
@@ -2065,12 +2355,22 @@
           <t>Expandir o acesso ao tratamento HIV</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Recursos para tratamento e capacitação</t>
+        </is>
+      </c>
       <c r="I35" s="3" t="inlineStr"/>
       <c r="J35" s="3" t="inlineStr"/>
       <c r="K35" s="3" t="inlineStr"/>
-      <c r="L35" s="3" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_34.html</t>
         </is>
@@ -2108,12 +2408,22 @@
           <t>Melhorar a detecção e tratamento precoce de HIV</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Materiais e equipamentos para testes</t>
+        </is>
+      </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_35.html</t>
         </is>
@@ -2153,26 +2463,36 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Estoque adequado de ARVs e insumos necessários</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>2.300.000</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>84.1%</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="L37" s="3" t="inlineStr">
         <is>
           <t>31.82389388066507</t>
         </is>
       </c>
-      <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr">
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_36.html</t>
         </is>
@@ -2212,17 +2532,19 @@
           <t>Garantir o fornecimento contínuo de ARVs</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_37.html</t>
         </is>
@@ -2259,17 +2581,19 @@
           <t>Garantir o fornecimento contínuo de ARVs</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_38.html</t>
         </is>
@@ -2306,17 +2630,19 @@
           <t>Garantir o fornecimento contínuo de ARVs</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_39.html</t>
         </is>
@@ -2353,17 +2679,19 @@
           <t>Garantir o fornecimento contínuo de ARVs</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="inlineStr"/>
-      <c r="L41" s="3" t="inlineStr">
+      <c r="L41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_40.html</t>
         </is>
@@ -2414,24 +2742,26 @@
           <t>Garantir o fornecimento contínuo de ARVs</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>FY19Q1</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>1.934.622</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>US AJUDA PrEP (102) das províncias de Manica (37), Niassa (18), Sofala (23), Tete (24). Dados ate JAN 2026</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_41.html</t>
         </is>
@@ -2470,14 +2800,24 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Materiais de apoio e recursos humanos para a formação</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
           <t>Sem Informação</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr">
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_42.html</t>
         </is>
@@ -2514,12 +2854,22 @@
           <t>Melhorar a qualidade das visitas de monitoria</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos qualificados e materiais de apoio</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_43.html</t>
         </is>
@@ -2557,12 +2907,22 @@
           <t>Aumentar a eficácia das intervenções</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Equipe de monitores e ferramentas de avaliação</t>
+        </is>
+      </c>
       <c r="I45" s="3" t="inlineStr"/>
       <c r="J45" s="3" t="inlineStr"/>
       <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr">
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_44.html</t>
         </is>
@@ -2599,12 +2959,22 @@
           <t>Fortalecer a monitoria em nível provincial</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Materiais de formação e logística</t>
+        </is>
+      </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_45.html</t>
         </is>
@@ -2642,12 +3012,22 @@
           <t>Aumentar o engajamento masculino</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Materiais educativos e recursos humanos</t>
+        </is>
+      </c>
       <c r="I47" s="3" t="inlineStr"/>
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="3" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr">
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_46.html</t>
         </is>
@@ -2684,12 +3064,22 @@
           <t>Melhorar a prestação de serviços TARV</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Recursos financeiros para recrutamento e treinamento</t>
+        </is>
+      </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_47.html</t>
         </is>
@@ -2726,12 +3116,22 @@
           <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
       <c r="I49" s="3" t="inlineStr"/>
       <c r="J49" s="3" t="inlineStr"/>
       <c r="K49" s="3" t="inlineStr"/>
-      <c r="L49" s="3" t="inlineStr">
+      <c r="L49" s="3" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr"/>
+      <c r="N49" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_48.html</t>
         </is>
@@ -2768,12 +3168,22 @@
           <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_49.html</t>
         </is>
@@ -2811,12 +3221,22 @@
           <t>Otimizar tratamento para todos os utentes</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Documentos e formações</t>
+        </is>
+      </c>
       <c r="I51" s="3" t="inlineStr"/>
       <c r="J51" s="3" t="inlineStr"/>
       <c r="K51" s="3" t="inlineStr"/>
-      <c r="L51" s="3" t="inlineStr">
+      <c r="L51" s="3" t="inlineStr"/>
+      <c r="M51" s="3" t="inlineStr"/>
+      <c r="N51" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_50.html</t>
         </is>
@@ -2853,12 +3273,22 @@
           <t>Garantir a eliminação da transmissão vertical</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais necessários</t>
+        </is>
+      </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_51.html</t>
         </is>
@@ -2896,12 +3326,22 @@
           <t>Aumentar a adesão ao tratamento</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Acompanhamento e suporte dos profissionais de saúde</t>
+        </is>
+      </c>
       <c r="I53" s="3" t="inlineStr"/>
       <c r="J53" s="3" t="inlineStr"/>
       <c r="K53" s="3" t="inlineStr"/>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="L53" s="3" t="inlineStr"/>
+      <c r="M53" s="3" t="inlineStr"/>
+      <c r="N53" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_52.html</t>
         </is>
@@ -2938,12 +3378,22 @@
           <t>Fortalecer a adesão ao tratamento</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Materiais e recursos para oficinas</t>
+        </is>
+      </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_53.html</t>
         </is>
@@ -2981,12 +3431,22 @@
           <t>Melhorar a integração dos serviços de saúde</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos qualificados e materiais de apoio</t>
+        </is>
+      </c>
       <c r="I55" s="3" t="inlineStr"/>
       <c r="J55" s="3" t="inlineStr"/>
       <c r="K55" s="3" t="inlineStr"/>
-      <c r="L55" s="3" t="inlineStr">
+      <c r="L55" s="3" t="inlineStr"/>
+      <c r="M55" s="3" t="inlineStr"/>
+      <c r="N55" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_54.html</t>
         </is>
@@ -3023,12 +3483,22 @@
           <t>Melhorar a integração e qualidade dos serviços</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Materiais de formação e recursos humanos para capacitação</t>
+        </is>
+      </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_55.html</t>
         </is>
@@ -3066,12 +3536,22 @@
           <t>Aumentar a competência dos clínicos</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr"/>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Materiais educativos e formação contínua</t>
+        </is>
+      </c>
       <c r="I57" s="3" t="inlineStr"/>
       <c r="J57" s="3" t="inlineStr"/>
       <c r="K57" s="3" t="inlineStr"/>
-      <c r="L57" s="3" t="inlineStr">
+      <c r="L57" s="3" t="inlineStr"/>
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_56.html</t>
         </is>
@@ -3109,12 +3589,22 @@
           <t>Melhorar a qualidade do atendimento</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Equipe de monitores e ferramentas de avaliação</t>
+        </is>
+      </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_57.html</t>
         </is>
@@ -3151,12 +3641,22 @@
           <t>disponibilizar o pacote no plataforma telesaude</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
+        </is>
+      </c>
       <c r="I59" s="3" t="inlineStr"/>
       <c r="J59" s="3" t="inlineStr"/>
       <c r="K59" s="3" t="inlineStr"/>
-      <c r="L59" s="3" t="inlineStr">
+      <c r="L59" s="3" t="inlineStr"/>
+      <c r="M59" s="3" t="inlineStr"/>
+      <c r="N59" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_58.html</t>
         </is>
@@ -3196,30 +3696,40 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Equipamentos para teste e formação de pessoal</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>245.610</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>51.7%</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>30.33081522210056</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>Dados de SESP</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_59.html</t>
         </is>
@@ -3259,26 +3769,36 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Materiais e reagentes para teste</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>2.032.370</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="K61" s="3" t="inlineStr">
         <is>
           <t>81.1%</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="L61" s="3" t="inlineStr">
         <is>
           <t>2.430270082098699</t>
         </is>
       </c>
-      <c r="K61" s="3" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr">
+      <c r="M61" s="3" t="inlineStr"/>
+      <c r="N61" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_60.html</t>
         </is>
@@ -3318,26 +3838,36 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Estoque adequado de ARVs pediátricos</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>177.000</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>55.2%</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>40.8587316200843</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_61.html</t>
         </is>
@@ -3376,17 +3906,19 @@
           <t>Garantir o acesso a ARVs para crianças</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr"/>
-      <c r="I63" s="3" t="inlineStr"/>
       <c r="J63" s="3" t="inlineStr"/>
       <c r="K63" s="3" t="inlineStr"/>
-      <c r="L63" s="3" t="inlineStr">
+      <c r="L63" s="3" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr"/>
+      <c r="N63" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_62.html</t>
         </is>
@@ -3424,17 +3956,19 @@
           <t>Garantir o acesso a ARVs para crianças</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_63.html</t>
         </is>
@@ -3472,17 +4006,19 @@
           <t>Garantir o acesso a ARVs para crianças</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr"/>
-      <c r="I65" s="3" t="inlineStr"/>
       <c r="J65" s="3" t="inlineStr"/>
       <c r="K65" s="3" t="inlineStr"/>
-      <c r="L65" s="3" t="inlineStr">
+      <c r="L65" s="3" t="inlineStr"/>
+      <c r="M65" s="3" t="inlineStr"/>
+      <c r="N65" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_64.html</t>
         </is>
@@ -3519,17 +4055,19 @@
           <t>Garantir o acesso a ARVs para crianças</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_65.html</t>
         </is>
@@ -3571,24 +4109,26 @@
           <t>Garantir o acesso a ARVs para crianças</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>FY19Q1</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>97.748</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="K67" s="3" t="inlineStr">
         <is>
           <t>Algumas US AJUDA das provincias de Manica , Niassa , Sofala , Tete</t>
         </is>
       </c>
-      <c r="J67" s="3" t="inlineStr"/>
-      <c r="K67" s="3" t="inlineStr"/>
-      <c r="L67" s="3" t="inlineStr">
+      <c r="L67" s="3" t="inlineStr"/>
+      <c r="M67" s="3" t="inlineStr"/>
+      <c r="N67" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_66.html</t>
         </is>
@@ -3625,12 +4165,22 @@
           <t>Melhorar o atendimento pediátrico</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Recursos financeiros para recrutamento e treinamento</t>
+        </is>
+      </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_67.html</t>
         </is>
@@ -3667,12 +4217,22 @@
           <t>Fortalecer a abordagem pediátrica</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr"/>
-      <c r="H69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos qualificados e materiais de apoio</t>
+        </is>
+      </c>
       <c r="I69" s="3" t="inlineStr"/>
       <c r="J69" s="3" t="inlineStr"/>
       <c r="K69" s="3" t="inlineStr"/>
-      <c r="L69" s="3" t="inlineStr">
+      <c r="L69" s="3" t="inlineStr"/>
+      <c r="M69" s="3" t="inlineStr"/>
+      <c r="N69" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_68.html</t>
         </is>
@@ -3710,12 +4270,22 @@
           <t>Aumentar o suporte e adesão ao tratamento</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para capacitação e acompanhamento</t>
+        </is>
+      </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_69.html</t>
         </is>
@@ -3752,12 +4322,22 @@
           <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
       <c r="I71" s="3" t="inlineStr"/>
       <c r="J71" s="3" t="inlineStr"/>
       <c r="K71" s="3" t="inlineStr"/>
-      <c r="L71" s="3" t="inlineStr">
+      <c r="L71" s="3" t="inlineStr"/>
+      <c r="M71" s="3" t="inlineStr"/>
+      <c r="N71" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_70.html</t>
         </is>
@@ -3794,12 +4374,22 @@
           <t>Melhorar a adesão e compreensão das normas</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Materiais de formação e recursos humanos</t>
+        </is>
+      </c>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_71.html</t>
         </is>
@@ -3836,12 +4426,22 @@
           <t>disponibilizar o pacote no plataforma telesaude</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr"/>
-      <c r="H73" s="3" t="inlineStr"/>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
+        </is>
+      </c>
       <c r="I73" s="3" t="inlineStr"/>
       <c r="J73" s="3" t="inlineStr"/>
       <c r="K73" s="3" t="inlineStr"/>
-      <c r="L73" s="3" t="inlineStr">
+      <c r="L73" s="3" t="inlineStr"/>
+      <c r="M73" s="3" t="inlineStr"/>
+      <c r="N73" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_72.html</t>
         </is>
@@ -3881,28 +4481,38 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Equipamentos para testes e formação de pessoal</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>158.532</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="J74" s="2" t="e">
+      <c r="L74" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>264541 novos inicios e 175826 reinicios</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_73.html</t>
         </is>
@@ -3942,22 +4552,32 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Estoque adequado de medicamentos e insumos</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>158.532</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr">
+      <c r="K75" s="3" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="J75" s="3" t="inlineStr"/>
-      <c r="K75" s="3" t="inlineStr"/>
-      <c r="L75" s="3" t="inlineStr">
+      <c r="L75" s="3" t="inlineStr"/>
+      <c r="M75" s="3" t="inlineStr"/>
+      <c r="N75" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_74.html</t>
         </is>
@@ -3997,22 +4617,32 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para aquisição de medicamentos</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>158.532</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_75.html</t>
         </is>
@@ -4050,12 +4680,22 @@
           <t>Melhorar a qualidade do acompanhamento</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr"/>
-      <c r="H77" s="3" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>Recursos para formação e capacitação de profissionais</t>
+        </is>
+      </c>
       <c r="I77" s="3" t="inlineStr"/>
       <c r="J77" s="3" t="inlineStr"/>
       <c r="K77" s="3" t="inlineStr"/>
-      <c r="L77" s="3" t="inlineStr">
+      <c r="L77" s="3" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr"/>
+      <c r="N77" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_76.html</t>
         </is>
@@ -4093,12 +4733,22 @@
           <t>Garantir a qualidade dos serviços prestados</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Equipe de monitores e ferramentas de avaliação</t>
+        </is>
+      </c>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr">
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_77.html</t>
         </is>
@@ -4136,12 +4786,22 @@
           <t>Melhorar o tratamento disponível</t>
         </is>
       </c>
-      <c r="G79" s="3" t="inlineStr"/>
-      <c r="H79" s="3" t="inlineStr"/>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>Materiais e recursos para expansão de serviços</t>
+        </is>
+      </c>
       <c r="I79" s="3" t="inlineStr"/>
       <c r="J79" s="3" t="inlineStr"/>
       <c r="K79" s="3" t="inlineStr"/>
-      <c r="L79" s="3" t="inlineStr">
+      <c r="L79" s="3" t="inlineStr"/>
+      <c r="M79" s="3" t="inlineStr"/>
+      <c r="N79" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_78.html</t>
         </is>
@@ -4179,12 +4839,22 @@
           <t>Melhorar o acesso a serviços de saúde</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Centro de referência de DAH</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais necessários para a implementação</t>
+        </is>
+      </c>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr">
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_79.html</t>
         </is>
@@ -4222,12 +4892,22 @@
           <t>Fortalecer a resposta ao HIV/TB</t>
         </is>
       </c>
-      <c r="G81" s="3" t="inlineStr"/>
-      <c r="H81" s="3" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>Recursos para capacitação e materiais de apoio</t>
+        </is>
+      </c>
       <c r="I81" s="3" t="inlineStr"/>
       <c r="J81" s="3" t="inlineStr"/>
       <c r="K81" s="3" t="inlineStr"/>
-      <c r="L81" s="3" t="inlineStr">
+      <c r="L81" s="3" t="inlineStr"/>
+      <c r="M81" s="3" t="inlineStr"/>
+      <c r="N81" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_80.html</t>
         </is>
@@ -4265,12 +4945,22 @@
           <t>Aumentar a capacidade de resposta ao tratamento</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Materiais de formação e recursos humanos para capacitação</t>
+        </is>
+      </c>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr">
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_81.html</t>
         </is>
@@ -4308,12 +4998,22 @@
           <t>Melhorar a detecção precoce de câncer cervical</t>
         </is>
       </c>
-      <c r="G83" s="3" t="inlineStr"/>
-      <c r="H83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>Materiais de rastreio e formação de pessoal</t>
+        </is>
+      </c>
       <c r="I83" s="3" t="inlineStr"/>
       <c r="J83" s="3" t="inlineStr"/>
       <c r="K83" s="3" t="inlineStr"/>
-      <c r="L83" s="3" t="inlineStr">
+      <c r="L83" s="3" t="inlineStr"/>
+      <c r="M83" s="3" t="inlineStr"/>
+      <c r="N83" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_82.html</t>
         </is>
@@ -4350,12 +5050,22 @@
           <t>Melhorar a resposta à resistência</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para reuniões e formadores</t>
+        </is>
+      </c>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr">
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_83.html</t>
         </is>
@@ -4392,12 +5102,22 @@
           <t>Aumentar a capacidade de testagem</t>
         </is>
       </c>
-      <c r="G85" s="3" t="inlineStr"/>
-      <c r="H85" s="3" t="inlineStr"/>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>Materiais de formação e equipamentos para treinamento</t>
+        </is>
+      </c>
       <c r="I85" s="3" t="inlineStr"/>
       <c r="J85" s="3" t="inlineStr"/>
       <c r="K85" s="3" t="inlineStr"/>
-      <c r="L85" s="3" t="inlineStr">
+      <c r="L85" s="3" t="inlineStr"/>
+      <c r="M85" s="3" t="inlineStr"/>
+      <c r="N85" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_84.html</t>
         </is>
@@ -4435,12 +5155,22 @@
           <t>Aumentar a eficácia da monitoria</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Equipamentos para monitoramento e recursos humanos</t>
+        </is>
+      </c>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="2" t="inlineStr">
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_85.html</t>
         </is>
@@ -4478,12 +5208,22 @@
           <t>Melhorar o diagnóstico em populações vulneráveis</t>
         </is>
       </c>
-      <c r="G87" s="3" t="inlineStr"/>
-      <c r="H87" s="3" t="inlineStr"/>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>Equipamentos m-PIMA e formação de pessoal</t>
+        </is>
+      </c>
       <c r="I87" s="3" t="inlineStr"/>
       <c r="J87" s="3" t="inlineStr"/>
       <c r="K87" s="3" t="inlineStr"/>
-      <c r="L87" s="3" t="inlineStr">
+      <c r="L87" s="3" t="inlineStr"/>
+      <c r="M87" s="3" t="inlineStr"/>
+      <c r="N87" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_86.html</t>
         </is>
@@ -4521,12 +5261,22 @@
           <t>Garantir a qualidade das testagens</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Materiais de avaliação e recursos humanos</t>
+        </is>
+      </c>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr">
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_87.html</t>
         </is>
@@ -4564,12 +5314,22 @@
           <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
-      <c r="G89" s="3" t="inlineStr"/>
-      <c r="H89" s="3" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
       <c r="I89" s="3" t="inlineStr"/>
       <c r="J89" s="3" t="inlineStr"/>
       <c r="K89" s="3" t="inlineStr"/>
-      <c r="L89" s="3" t="inlineStr">
+      <c r="L89" s="3" t="inlineStr"/>
+      <c r="M89" s="3" t="inlineStr"/>
+      <c r="N89" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_88.html</t>
         </is>
@@ -4607,12 +5367,22 @@
           <t>Melhorar a precisão dos testes</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para aquisição de painéis de proficiência</t>
+        </is>
+      </c>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_89.html</t>
         </is>
@@ -4650,12 +5420,22 @@
           <t>Aumentar a capacidade de monitoramento</t>
         </is>
       </c>
-      <c r="G91" s="3" t="inlineStr"/>
-      <c r="H91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>Equipamentos e formação para uso de m-PIMA e GeneXpert</t>
+        </is>
+      </c>
       <c r="I91" s="3" t="inlineStr"/>
       <c r="J91" s="3" t="inlineStr"/>
       <c r="K91" s="3" t="inlineStr"/>
-      <c r="L91" s="3" t="inlineStr">
+      <c r="L91" s="3" t="inlineStr"/>
+      <c r="M91" s="3" t="inlineStr"/>
+      <c r="N91" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_90.html</t>
         </is>
@@ -4693,12 +5473,22 @@
           <t>Aumentar a eficácia do tratamento</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos e protocolos de revisão</t>
+        </is>
+      </c>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr">
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_91.html</t>
         </is>
@@ -4736,12 +5526,22 @@
           <t>Garantir a qualidade dos testes</t>
         </is>
       </c>
-      <c r="G93" s="3" t="inlineStr"/>
-      <c r="H93" s="3" t="inlineStr"/>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>Materiais para verificação e recursos humanos</t>
+        </is>
+      </c>
       <c r="I93" s="3" t="inlineStr"/>
       <c r="J93" s="3" t="inlineStr"/>
       <c r="K93" s="3" t="inlineStr"/>
-      <c r="L93" s="3" t="inlineStr">
+      <c r="L93" s="3" t="inlineStr"/>
+      <c r="M93" s="3" t="inlineStr"/>
+      <c r="N93" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_92.html</t>
         </is>
@@ -4779,12 +5579,22 @@
           <t>Garantir o abastecimento contínuo de insumos</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para quantificação e logística</t>
+        </is>
+      </c>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr">
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_93.html</t>
         </is>
@@ -4821,12 +5631,22 @@
           <t>Melhorar a qualidade dos dados de farmácia</t>
         </is>
       </c>
-      <c r="G95" s="3" t="inlineStr"/>
-      <c r="H95" s="3" t="inlineStr"/>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos qualificados e materiais de apoio</t>
+        </is>
+      </c>
       <c r="I95" s="3" t="inlineStr"/>
       <c r="J95" s="3" t="inlineStr"/>
       <c r="K95" s="3" t="inlineStr"/>
-      <c r="L95" s="3" t="inlineStr">
+      <c r="L95" s="3" t="inlineStr"/>
+      <c r="M95" s="3" t="inlineStr"/>
+      <c r="N95" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_94.html</t>
         </is>
@@ -4863,12 +5683,22 @@
           <t>Garantir a disponibilidade de medicamentos</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Recursos financeiros para aquisição de medicamentos</t>
+        </is>
+      </c>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr">
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_95.html</t>
         </is>
@@ -4906,12 +5736,22 @@
           <t>Garantir a entrega pontual de insumos</t>
         </is>
       </c>
-      <c r="G97" s="3" t="inlineStr"/>
-      <c r="H97" s="3" t="inlineStr"/>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>Logística de transporte e recursos humanos</t>
+        </is>
+      </c>
       <c r="I97" s="3" t="inlineStr"/>
       <c r="J97" s="3" t="inlineStr"/>
       <c r="K97" s="3" t="inlineStr"/>
-      <c r="L97" s="3" t="inlineStr">
+      <c r="L97" s="3" t="inlineStr"/>
+      <c r="M97" s="3" t="inlineStr"/>
+      <c r="N97" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_96.html</t>
         </is>
@@ -4948,12 +5788,22 @@
           <t>Melhorar a gestão de medicamentos</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Materiais de formação e recursos humanos</t>
+        </is>
+      </c>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr">
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_97.html</t>
         </is>
@@ -4990,12 +5840,22 @@
           <t>Garantir a disponibilidade de medicamentos</t>
         </is>
       </c>
-      <c r="G99" s="3" t="inlineStr"/>
-      <c r="H99" s="3" t="inlineStr"/>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>Recursos financeiros para aquisição de insumos</t>
+        </is>
+      </c>
       <c r="I99" s="3" t="inlineStr"/>
       <c r="J99" s="3" t="inlineStr"/>
       <c r="K99" s="3" t="inlineStr"/>
-      <c r="L99" s="3" t="inlineStr">
+      <c r="L99" s="3" t="inlineStr"/>
+      <c r="M99" s="3" t="inlineStr"/>
+      <c r="N99" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_98.html</t>
         </is>
@@ -5034,28 +5894,38 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos e ferramentas para avaliação</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="J100" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I100" s="2" t="e">
+      <c r="K100" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="L100" s="2" t="inlineStr">
         <is>
           <t>3507.042253521127</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="M100" s="2" t="inlineStr">
         <is>
           <t># alcancado sao Unidade Santiarias</t>
         </is>
       </c>
-      <c r="L100" s="2" t="inlineStr">
+      <c r="N100" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_99.html</t>
         </is>
@@ -5095,17 +5965,19 @@
           <t>Melhorar a qualidade dos dados coletados</t>
         </is>
       </c>
-      <c r="G101" s="3" t="inlineStr">
+      <c r="G101" s="3" t="inlineStr"/>
+      <c r="H101" s="3" t="inlineStr"/>
+      <c r="I101" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr"/>
-      <c r="I101" s="3" t="inlineStr"/>
       <c r="J101" s="3" t="inlineStr"/>
       <c r="K101" s="3" t="inlineStr"/>
-      <c r="L101" s="3" t="inlineStr">
+      <c r="L101" s="3" t="inlineStr"/>
+      <c r="M101" s="3" t="inlineStr"/>
+      <c r="N101" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_100.html</t>
         </is>
@@ -5142,17 +6014,19 @@
           <t>Melhorar a qualidade dos dados coletados</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr">
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_101.html</t>
         </is>
@@ -5191,17 +6065,19 @@
           <t>Melhorar a qualidade dos dados coletados</t>
         </is>
       </c>
-      <c r="G103" s="3" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr"/>
+      <c r="H103" s="3" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H103" s="3" t="inlineStr"/>
-      <c r="I103" s="3" t="inlineStr"/>
       <c r="J103" s="3" t="inlineStr"/>
       <c r="K103" s="3" t="inlineStr"/>
-      <c r="L103" s="3" t="inlineStr">
+      <c r="L103" s="3" t="inlineStr"/>
+      <c r="M103" s="3" t="inlineStr"/>
+      <c r="N103" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_102.html</t>
         </is>
@@ -5240,17 +6116,19 @@
           <t>Melhorar a qualidade dos dados coletados</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr">
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_103.html</t>
         </is>
@@ -5298,26 +6176,28 @@
           <t>Melhorar a qualidade dos dados coletados</t>
         </is>
       </c>
-      <c r="G105" s="3" t="inlineStr">
+      <c r="G105" s="3" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr">
         <is>
           <t>Desde o inicio do Projecto em 2019</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
+      <c r="J105" s="3" t="inlineStr">
         <is>
           <t>Todos os pacientes elegiveis 
 Provedores das US
 Sistemas</t>
         </is>
       </c>
-      <c r="I105" s="3" t="inlineStr">
+      <c r="K105" s="3" t="inlineStr">
         <is>
           <t>Todas as US AJUDA (149) Manica (51), Niassa(18), Sofala (47) e Tete (33)</t>
         </is>
       </c>
-      <c r="J105" s="3" t="inlineStr"/>
-      <c r="K105" s="3" t="inlineStr"/>
-      <c r="L105" s="3" t="inlineStr">
+      <c r="L105" s="3" t="inlineStr"/>
+      <c r="M105" s="3" t="inlineStr"/>
+      <c r="N105" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_104.html</t>
         </is>
@@ -5354,12 +6234,22 @@
           <t>Melhorar a resposta ao HIV/SIDA</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para avaliação e monitoramento</t>
+        </is>
+      </c>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="inlineStr">
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_105.html</t>
         </is>
@@ -5396,12 +6286,22 @@
           <t>Fortalecer a capacidade de resposta estratégia</t>
         </is>
       </c>
-      <c r="G107" s="3" t="inlineStr"/>
-      <c r="H107" s="3" t="inlineStr"/>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>Materiais de formação e logística para oficinas</t>
+        </is>
+      </c>
       <c r="I107" s="3" t="inlineStr"/>
       <c r="J107" s="3" t="inlineStr"/>
       <c r="K107" s="3" t="inlineStr"/>
-      <c r="L107" s="3" t="inlineStr">
+      <c r="L107" s="3" t="inlineStr"/>
+      <c r="M107" s="3" t="inlineStr"/>
+      <c r="N107" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_106.html</t>
         </is>
@@ -5438,12 +6338,22 @@
           <t>disponibilizar o pacote no plataforma telesaude</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
+        </is>
+      </c>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr">
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_107.html</t>
         </is>
@@ -5481,12 +6391,22 @@
           <t>Melhorar a qualidade dos dados coletados</t>
         </is>
       </c>
-      <c r="G109" s="3" t="inlineStr"/>
-      <c r="H109" s="3" t="inlineStr"/>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos e ferramentas para avaliação</t>
+        </is>
+      </c>
       <c r="I109" s="3" t="inlineStr"/>
       <c r="J109" s="3" t="inlineStr"/>
       <c r="K109" s="3" t="inlineStr"/>
-      <c r="L109" s="3" t="inlineStr">
+      <c r="L109" s="3" t="inlineStr"/>
+      <c r="M109" s="3" t="inlineStr"/>
+      <c r="N109" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_108.html</t>
         </is>
@@ -5524,12 +6444,22 @@
           <t>Fortalecer a qualidade dos dados</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para visitas e apoio técnico</t>
+        </is>
+      </c>
       <c r="I110" s="2" t="inlineStr"/>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr">
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_109.html</t>
         </is>
@@ -5567,12 +6497,22 @@
           <t>Melhorar a transparência e uso dos dados</t>
         </is>
       </c>
-      <c r="G111" s="3" t="inlineStr"/>
-      <c r="H111" s="3" t="inlineStr"/>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>Recursos tecnológicos e humanos para desenvolvimento</t>
+        </is>
+      </c>
       <c r="I111" s="3" t="inlineStr"/>
       <c r="J111" s="3" t="inlineStr"/>
       <c r="K111" s="3" t="inlineStr"/>
-      <c r="L111" s="3" t="inlineStr">
+      <c r="L111" s="3" t="inlineStr"/>
+      <c r="M111" s="3" t="inlineStr"/>
+      <c r="N111" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_110.html</t>
         </is>
@@ -5610,12 +6550,22 @@
           <t>Melhorar a eficácia do sistema de informação</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Recursos técnicos e humanos para desenvolvimento</t>
+        </is>
+      </c>
       <c r="I112" s="2" t="inlineStr"/>
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="2" t="inlineStr">
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_111.html</t>
         </is>
@@ -5653,12 +6603,22 @@
           <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
-      <c r="G113" s="3" t="inlineStr"/>
-      <c r="H113" s="3" t="inlineStr"/>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
       <c r="I113" s="3" t="inlineStr"/>
       <c r="J113" s="3" t="inlineStr"/>
       <c r="K113" s="3" t="inlineStr"/>
-      <c r="L113" s="3" t="inlineStr">
+      <c r="L113" s="3" t="inlineStr"/>
+      <c r="M113" s="3" t="inlineStr"/>
+      <c r="N113" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_112.html</t>
         </is>
@@ -5695,12 +6655,22 @@
           <t>Garantir a operacionalidade das unidades de saúde</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Recursos financeiros para aquisição de equipamentos</t>
+        </is>
+      </c>
       <c r="I114" s="2" t="inlineStr"/>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="inlineStr">
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_113.html</t>
         </is>
@@ -5733,12 +6703,22 @@
           <t>Fortalecer a capacidade de gestão</t>
         </is>
       </c>
-      <c r="G115" s="3" t="inlineStr"/>
-      <c r="H115" s="3" t="inlineStr"/>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos qualificados e materiais de apoio</t>
+        </is>
+      </c>
       <c r="I115" s="3" t="inlineStr"/>
       <c r="J115" s="3" t="inlineStr"/>
       <c r="K115" s="3" t="inlineStr"/>
-      <c r="L115" s="3" t="inlineStr">
+      <c r="L115" s="3" t="inlineStr"/>
+      <c r="M115" s="3" t="inlineStr"/>
+      <c r="N115" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_114.html</t>
         </is>
@@ -5775,12 +6755,22 @@
           <t>Melhorar a capacidade técnica</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Recursos financeiros para aquisição de licenças</t>
+        </is>
+      </c>
       <c r="I116" s="2" t="inlineStr"/>
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr">
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_115.html</t>
         </is>
@@ -5817,12 +6807,22 @@
           <t>Melhorar a comunicação entre unidades</t>
         </is>
       </c>
-      <c r="G117" s="3" t="inlineStr"/>
-      <c r="H117" s="3" t="inlineStr"/>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>Recursos financeiros para serviços de comunicação</t>
+        </is>
+      </c>
       <c r="I117" s="3" t="inlineStr"/>
       <c r="J117" s="3" t="inlineStr"/>
       <c r="K117" s="3" t="inlineStr"/>
-      <c r="L117" s="3" t="inlineStr">
+      <c r="L117" s="3" t="inlineStr"/>
+      <c r="M117" s="3" t="inlineStr"/>
+      <c r="N117" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_116.html</t>
         </is>
@@ -5861,26 +6861,36 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais para implementação</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="J118" s="2" t="inlineStr">
         <is>
           <t>2.032.370</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
+      <c r="K118" s="2" t="inlineStr">
         <is>
           <t>91.0%</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr">
+      <c r="L118" s="2" t="inlineStr">
         <is>
           <t>0.1351748107687824</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr">
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_117.html</t>
         </is>
@@ -5918,12 +6928,22 @@
           <t>disponibilizar o pacote no plataforma telesaude</t>
         </is>
       </c>
-      <c r="G119" s="3" t="inlineStr"/>
-      <c r="H119" s="3" t="inlineStr"/>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
+        </is>
+      </c>
       <c r="I119" s="3" t="inlineStr"/>
       <c r="J119" s="3" t="inlineStr"/>
       <c r="K119" s="3" t="inlineStr"/>
-      <c r="L119" s="3" t="inlineStr">
+      <c r="L119" s="3" t="inlineStr"/>
+      <c r="M119" s="3" t="inlineStr"/>
+      <c r="N119" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_118.html</t>
         </is>
@@ -5958,12 +6978,22 @@
           <t>Fortalecer a abordagem da melhoria da qualidade</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos qualificados e capacitação</t>
+        </is>
+      </c>
       <c r="I120" s="2" t="inlineStr"/>
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="2" t="inlineStr">
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_119.html</t>
         </is>
@@ -5996,12 +7026,22 @@
           <t>Padronizar a oferta de serviços</t>
         </is>
       </c>
-      <c r="G121" s="3" t="inlineStr"/>
-      <c r="H121" s="3" t="inlineStr"/>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais para elaboração</t>
+        </is>
+      </c>
       <c r="I121" s="3" t="inlineStr"/>
       <c r="J121" s="3" t="inlineStr"/>
       <c r="K121" s="3" t="inlineStr"/>
-      <c r="L121" s="3" t="inlineStr">
+      <c r="L121" s="3" t="inlineStr"/>
+      <c r="M121" s="3" t="inlineStr"/>
+      <c r="N121" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_120.html</t>
         </is>
@@ -6035,12 +7075,22 @@
           <t>Aumentar a participação dos utentes na saúde</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para campanhas de sensibilização</t>
+        </is>
+      </c>
       <c r="I122" s="2" t="inlineStr"/>
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr">
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_121.html</t>
         </is>
@@ -6074,12 +7124,22 @@
           <t>Melhorar a supervisão e apoio técnico</t>
         </is>
       </c>
-      <c r="G123" s="3" t="inlineStr"/>
-      <c r="H123" s="3" t="inlineStr"/>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>Recursos tecnológicos e humanos para implementação</t>
+        </is>
+      </c>
       <c r="I123" s="3" t="inlineStr"/>
       <c r="J123" s="3" t="inlineStr"/>
       <c r="K123" s="3" t="inlineStr"/>
-      <c r="L123" s="3" t="inlineStr">
+      <c r="L123" s="3" t="inlineStr"/>
+      <c r="M123" s="3" t="inlineStr"/>
+      <c r="N123" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_122.html</t>
         </is>
@@ -6113,12 +7173,22 @@
           <t>Melhorar a transparência e uso dos dados</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Recursos tecnológicos e humanos para desenvolvimento</t>
+        </is>
+      </c>
       <c r="I124" s="2" t="inlineStr"/>
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="inlineStr">
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_123.html</t>
         </is>
@@ -6152,12 +7222,22 @@
           <t>Melhorar a qualidade dos serviços de saúde</t>
         </is>
       </c>
-      <c r="G125" s="3" t="inlineStr"/>
-      <c r="H125" s="3" t="inlineStr"/>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais para implementação</t>
+        </is>
+      </c>
       <c r="I125" s="3" t="inlineStr"/>
       <c r="J125" s="3" t="inlineStr"/>
       <c r="K125" s="3" t="inlineStr"/>
-      <c r="L125" s="3" t="inlineStr">
+      <c r="L125" s="3" t="inlineStr"/>
+      <c r="M125" s="3" t="inlineStr"/>
+      <c r="N125" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_124.html</t>
         </is>
@@ -6196,12 +7276,22 @@
           <t>Aumentar a capacitação dos profissionais de saúde</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Materiais de formação e recursos humanos</t>
+        </is>
+      </c>
       <c r="I126" s="2" t="inlineStr"/>
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="2" t="inlineStr">
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_125.html</t>
         </is>
@@ -6239,12 +7329,22 @@
           <t>Melhorar a visibilidade da informação</t>
         </is>
       </c>
-      <c r="G127" s="3" t="inlineStr"/>
-      <c r="H127" s="3" t="inlineStr"/>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>Recursos tecnológicos e humanos para desenvolvimento</t>
+        </is>
+      </c>
       <c r="I127" s="3" t="inlineStr"/>
       <c r="J127" s="3" t="inlineStr"/>
       <c r="K127" s="3" t="inlineStr"/>
-      <c r="L127" s="3" t="inlineStr">
+      <c r="L127" s="3" t="inlineStr"/>
+      <c r="M127" s="3" t="inlineStr"/>
+      <c r="N127" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_126.html</t>
         </is>
@@ -6282,12 +7382,22 @@
           <t>Coordenar esforços e compartilhar boas práticas</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para logística e organização de eventos</t>
+        </is>
+      </c>
       <c r="I128" s="2" t="inlineStr"/>
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="inlineStr">
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_127.html</t>
         </is>
@@ -6328,12 +7438,22 @@
           <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
-      <c r="G129" s="3" t="inlineStr"/>
-      <c r="H129" s="3" t="inlineStr"/>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
       <c r="I129" s="3" t="inlineStr"/>
       <c r="J129" s="3" t="inlineStr"/>
       <c r="K129" s="3" t="inlineStr"/>
-      <c r="L129" s="3" t="inlineStr">
+      <c r="L129" s="3" t="inlineStr"/>
+      <c r="M129" s="3" t="inlineStr"/>
+      <c r="N129" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_128.html</t>
         </is>
@@ -6373,28 +7493,38 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para PrEP</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="J130" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I130" s="2" t="e">
+      <c r="K130" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="J130" s="2" t="inlineStr">
+      <c r="L130" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K130" s="2" t="inlineStr">
+      <c r="M130" s="2" t="inlineStr">
         <is>
           <t>Nao iniciou em 2024</t>
         </is>
       </c>
-      <c r="L130" s="2" t="inlineStr">
+      <c r="N130" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_129.html</t>
         </is>
@@ -6434,30 +7564,40 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para PrEP</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="H131" s="3" t="inlineStr">
+      <c r="J131" s="3" t="inlineStr">
         <is>
           <t>3.185.533</t>
         </is>
       </c>
-      <c r="I131" s="3" t="inlineStr">
+      <c r="K131" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="J131" s="3" t="inlineStr">
+      <c r="L131" s="3" t="inlineStr">
         <is>
           <t>3715.393500000001</t>
         </is>
       </c>
-      <c r="K131" s="3" t="inlineStr">
+      <c r="M131" s="3" t="inlineStr">
         <is>
           <t>36 RAMJ 15-24 em seguimento no ano 2024, pois foi o inicio do piloto</t>
         </is>
       </c>
-      <c r="L131" s="3" t="inlineStr">
+      <c r="N131" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_130.html</t>
         </is>
@@ -6497,26 +7637,36 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para aquisição de lubrificantes</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="H132" s="2" t="e">
+      <c r="J132" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="I132" s="2" t="e">
+      <c r="K132" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="J132" s="2" t="inlineStr">
+      <c r="L132" s="2" t="inlineStr">
         <is>
           <t>0.061678806032677</t>
         </is>
       </c>
-      <c r="K132" s="2" t="inlineStr">
+      <c r="M132" s="2" t="inlineStr">
         <is>
           <t>dados de distribucao, Hom + Mulh 15-49</t>
         </is>
       </c>
-      <c r="L132" s="2" t="inlineStr">
+      <c r="N132" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_131.html</t>
         </is>
@@ -6556,28 +7706,38 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para ITS</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
           <t>2021 (novo versao)</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
+      <c r="J133" s="3" t="inlineStr">
         <is>
           <t>todos utentes na US</t>
         </is>
       </c>
-      <c r="I133" s="3" t="e">
+      <c r="K133" s="3" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="J133" s="3" t="inlineStr">
+      <c r="L133" s="3" t="inlineStr">
         <is>
           <t>0.6309392820691827</t>
         </is>
       </c>
-      <c r="K133" s="3" t="inlineStr">
+      <c r="M133" s="3" t="inlineStr">
         <is>
           <t>por causa de cobertura de livro de ITS não é possivel calcular um pop. Eligivel</t>
         </is>
       </c>
-      <c r="L133" s="3" t="inlineStr">
+      <c r="N133" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_132.html</t>
         </is>
@@ -6617,30 +7777,40 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para aquisição de preservativos</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="J134" s="2" t="inlineStr">
         <is>
           <t>8.159.149</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr">
+      <c r="K134" s="2" t="inlineStr">
         <is>
           <t>68.6%</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="L134" s="2" t="inlineStr">
         <is>
           <t>0.4605463310123192</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
+      <c r="M134" s="2" t="inlineStr">
         <is>
           <t>dados de distribucao Mulher 15 - 49 anos</t>
         </is>
       </c>
-      <c r="L134" s="2" t="inlineStr">
+      <c r="N134" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_133.html</t>
         </is>
@@ -6680,30 +7850,40 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para PrEP Oral</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr">
+      <c r="J135" s="3" t="inlineStr">
         <is>
           <t>30.767.054</t>
         </is>
       </c>
-      <c r="I135" s="3" t="inlineStr">
+      <c r="K135" s="3" t="inlineStr">
         <is>
           <t>0.8%</t>
         </is>
       </c>
-      <c r="J135" s="3" t="inlineStr">
+      <c r="L135" s="3" t="inlineStr">
         <is>
           <t>21.33839519575633</t>
         </is>
       </c>
-      <c r="K135" s="3" t="inlineStr">
+      <c r="M135" s="3" t="inlineStr">
         <is>
           <t>Novo inicios a PrEP para o ano 2024</t>
         </is>
       </c>
-      <c r="L135" s="3" t="inlineStr">
+      <c r="N135" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_134.html</t>
         </is>
@@ -6743,30 +7923,40 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para aquisição e distribuição de preservativos</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="J136" s="2" t="inlineStr">
         <is>
           <t>7.388.905</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
+      <c r="K136" s="2" t="inlineStr">
         <is>
           <t>21.810947630264565</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="L136" s="2" t="inlineStr">
         <is>
           <t>0.04648415651820172</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr">
+      <c r="M136" s="2" t="inlineStr">
         <is>
           <t>dados de distribucao Homen 15 - 49 anos</t>
         </is>
       </c>
-      <c r="L136" s="2" t="inlineStr">
+      <c r="N136" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_135.html</t>
         </is>
@@ -6806,17 +7996,19 @@
           <t>Aumentar a proteção contra o HIV</t>
         </is>
       </c>
-      <c r="G137" s="3" t="inlineStr">
+      <c r="G137" s="3" t="inlineStr"/>
+      <c r="H137" s="3" t="inlineStr"/>
+      <c r="I137" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr"/>
-      <c r="I137" s="3" t="inlineStr"/>
       <c r="J137" s="3" t="inlineStr"/>
       <c r="K137" s="3" t="inlineStr"/>
-      <c r="L137" s="3" t="inlineStr">
+      <c r="L137" s="3" t="inlineStr"/>
+      <c r="M137" s="3" t="inlineStr"/>
+      <c r="N137" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_136.html</t>
         </is>
@@ -6853,17 +8045,19 @@
           <t>Aumentar a proteção contra o HIV</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="2" t="inlineStr"/>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="2" t="inlineStr">
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_137.html</t>
         </is>
@@ -6900,17 +8094,19 @@
           <t>Aumentar a proteção contra o HIV</t>
         </is>
       </c>
-      <c r="G139" s="3" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr"/>
+      <c r="H139" s="3" t="inlineStr"/>
+      <c r="I139" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr"/>
-      <c r="I139" s="3" t="inlineStr"/>
       <c r="J139" s="3" t="inlineStr"/>
       <c r="K139" s="3" t="inlineStr"/>
-      <c r="L139" s="3" t="inlineStr">
+      <c r="L139" s="3" t="inlineStr"/>
+      <c r="M139" s="3" t="inlineStr"/>
+      <c r="N139" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_138.html</t>
         </is>
@@ -6948,17 +8144,19 @@
           <t>Aumentar a proteção contra o HIV</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr"/>
-      <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="2" t="inlineStr">
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_139.html</t>
         </is>
@@ -6998,12 +8196,14 @@
           <t>Aumentar a proteção contra o HIV</t>
         </is>
       </c>
-      <c r="G141" s="3" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr"/>
+      <c r="H141" s="3" t="inlineStr"/>
+      <c r="I141" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2021 com o piloto em Manica e depois expansão nacional </t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
+      <c r="J141" s="3" t="inlineStr">
         <is>
           <t>Provedores das portas de captação da PrEP e das PUs da PrEP
 Pontos focais provinciais, distritais e das US 
@@ -7011,14 +8211,14 @@
 População elegível para PrEP no geral incluindo MG/ML</t>
         </is>
       </c>
-      <c r="I141" s="3" t="inlineStr">
+      <c r="K141" s="3" t="inlineStr">
         <is>
           <t>US AJUDA PrEP (102) das províncias de Manica (37), Niassa (18), Sofala (23), Tete (24). Dados ate JAN 2026</t>
         </is>
       </c>
-      <c r="J141" s="3" t="inlineStr"/>
-      <c r="K141" s="3" t="inlineStr"/>
-      <c r="L141" s="3" t="inlineStr">
+      <c r="L141" s="3" t="inlineStr"/>
+      <c r="M141" s="3" t="inlineStr"/>
+      <c r="N141" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_140.html</t>
         </is>
@@ -7060,29 +8260,31 @@
           <t>Aumentar a proteção contra o HIV</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
         <is>
           <t>Desde o inicio do Projecto em 2019</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">População dos locais abrangidos </t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr">
+      <c r="K142" s="2" t="inlineStr">
         <is>
           <t>US AJUDA PrEP (102) das províncias de Manica (37), Niassa (18), Sofala (23), Tete (24). Dados ate JAN 2026</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr"/>
-      <c r="K142" s="2" t="inlineStr">
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Actividades suspensas emJ aneiro 2025 em alinhamento as orientações do "waiver" e do doador
 Mantem-se o apoio as intervenções dentro da US </t>
         </is>
       </c>
-      <c r="L142" s="2" t="inlineStr">
+      <c r="N142" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_141.html</t>
         </is>
@@ -7119,12 +8321,22 @@
           <t>Aumentar a conscientização e utilização de PrEP</t>
         </is>
       </c>
-      <c r="G143" s="3" t="inlineStr"/>
-      <c r="H143" s="3" t="inlineStr"/>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>Materiais de capacitação e recursos humanos</t>
+        </is>
+      </c>
       <c r="I143" s="3" t="inlineStr"/>
       <c r="J143" s="3" t="inlineStr"/>
       <c r="K143" s="3" t="inlineStr"/>
-      <c r="L143" s="3" t="inlineStr">
+      <c r="L143" s="3" t="inlineStr"/>
+      <c r="M143" s="3" t="inlineStr"/>
+      <c r="N143" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_142.html</t>
         </is>
@@ -7162,12 +8374,22 @@
           <t>Aumentar o acesso à PrEP</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para PrEP</t>
+        </is>
+      </c>
       <c r="I144" s="2" t="inlineStr"/>
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr"/>
-      <c r="L144" s="2" t="inlineStr">
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_143.html</t>
         </is>
@@ -7205,12 +8427,22 @@
           <t>Garantir a qualidade da implementação</t>
         </is>
       </c>
-      <c r="G145" s="3" t="inlineStr"/>
-      <c r="H145" s="3" t="inlineStr"/>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais para monitoramento</t>
+        </is>
+      </c>
       <c r="I145" s="3" t="inlineStr"/>
       <c r="J145" s="3" t="inlineStr"/>
       <c r="K145" s="3" t="inlineStr"/>
-      <c r="L145" s="3" t="inlineStr">
+      <c r="L145" s="3" t="inlineStr"/>
+      <c r="M145" s="3" t="inlineStr"/>
+      <c r="N145" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_144.html</t>
         </is>
@@ -7248,12 +8480,22 @@
           <t>Aumentar a aceitação e uso da PrEP Oral</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para campanhas de sensibilização</t>
+        </is>
+      </c>
       <c r="I146" s="2" t="inlineStr"/>
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="2" t="inlineStr">
+      <c r="L146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_145.html</t>
         </is>
@@ -7291,12 +8533,22 @@
           <t>Aumentar a aceitação e uso da PrEP Injectável</t>
         </is>
       </c>
-      <c r="G147" s="3" t="inlineStr"/>
-      <c r="H147" s="3" t="inlineStr"/>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>Recursos para campanhas de sensibilização</t>
+        </is>
+      </c>
       <c r="I147" s="3" t="inlineStr"/>
       <c r="J147" s="3" t="inlineStr"/>
       <c r="K147" s="3" t="inlineStr"/>
-      <c r="L147" s="3" t="inlineStr">
+      <c r="L147" s="3" t="inlineStr"/>
+      <c r="M147" s="3" t="inlineStr"/>
+      <c r="N147" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_146.html</t>
         </is>
@@ -7334,12 +8586,22 @@
           <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
       <c r="I148" s="2" t="inlineStr"/>
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr"/>
-      <c r="L148" s="2" t="inlineStr">
+      <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_147.html</t>
         </is>
@@ -7376,12 +8638,22 @@
           <t>Aumentar a capacidade dos profissionais de saúde</t>
         </is>
       </c>
-      <c r="G149" s="3" t="inlineStr"/>
-      <c r="H149" s="3" t="inlineStr"/>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>Materiais de formação e recursos humanos</t>
+        </is>
+      </c>
       <c r="I149" s="3" t="inlineStr"/>
       <c r="J149" s="3" t="inlineStr"/>
       <c r="K149" s="3" t="inlineStr"/>
-      <c r="L149" s="3" t="inlineStr">
+      <c r="L149" s="3" t="inlineStr"/>
+      <c r="M149" s="3" t="inlineStr"/>
+      <c r="N149" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_148.html</t>
         </is>
@@ -7418,12 +8690,22 @@
           <t>Melhorar a coordenação e eficiência das estratégias</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para a realização da reunião</t>
+        </is>
+      </c>
       <c r="I150" s="2" t="inlineStr"/>
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr"/>
-      <c r="L150" s="2" t="inlineStr">
+      <c r="L150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_149.html</t>
         </is>
@@ -7463,28 +8745,38 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para tratamento</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr">
+      <c r="J151" s="3" t="inlineStr">
         <is>
           <t>36.171</t>
         </is>
       </c>
-      <c r="I151" s="3" t="inlineStr">
+      <c r="K151" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="J151" s="3" t="e">
+      <c r="L151" s="3" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="K151" s="3" t="inlineStr">
+      <c r="M151" s="3" t="inlineStr">
         <is>
           <t>Carga Viral para VHB nao foi implmentado em 2024</t>
         </is>
       </c>
-      <c r="L151" s="3" t="inlineStr">
+      <c r="N151" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_150.html</t>
         </is>
@@ -7524,30 +8816,40 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para tratamento</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="J152" s="2" t="inlineStr">
         <is>
           <t>36.171</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr">
+      <c r="K152" s="2" t="inlineStr">
         <is>
           <t>89.1%</t>
         </is>
       </c>
-      <c r="J152" s="2" t="inlineStr">
+      <c r="L152" s="2" t="inlineStr">
         <is>
           <t>14.55053042992741</t>
         </is>
       </c>
-      <c r="K152" s="2" t="inlineStr">
+      <c r="M152" s="2" t="inlineStr">
         <is>
           <t>Ainda foi um piloto ate o fim de 2024, em MC tinha 7,615, Nampula 18,706, Sofala 5,917</t>
         </is>
       </c>
-      <c r="L152" s="2" t="inlineStr">
+      <c r="N152" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_151.html</t>
         </is>
@@ -7587,28 +8889,38 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para tratamento</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
           <t>&lt;2018</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
+      <c r="J153" s="3" t="inlineStr">
         <is>
           <t>Pessoas com sinais ou sintomas</t>
         </is>
       </c>
-      <c r="I153" s="3" t="e">
+      <c r="K153" s="3" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="J153" s="3" t="inlineStr">
+      <c r="L153" s="3" t="inlineStr">
         <is>
           <t>2.041635729911516</t>
         </is>
       </c>
-      <c r="K153" s="3" t="inlineStr">
+      <c r="M153" s="3" t="inlineStr">
         <is>
           <t>testados para Sifilis no livro de ITS</t>
         </is>
       </c>
-      <c r="L153" s="3" t="inlineStr">
+      <c r="N153" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_152.html</t>
         </is>
@@ -7648,30 +8960,40 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para tratamento</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>134.000</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
+      <c r="K154" s="2" t="inlineStr">
         <is>
           <t>81.8%</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr">
+      <c r="L154" s="2" t="inlineStr">
         <is>
           <t>8.066636253214423</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr">
+      <c r="M154" s="2" t="inlineStr">
         <is>
           <t>MG HIV+ na CPN</t>
         </is>
       </c>
-      <c r="L154" s="2" t="inlineStr">
+      <c r="N154" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_153.html</t>
         </is>
@@ -7711,26 +9033,36 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para tratamento</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr">
+      <c r="J155" s="3" t="inlineStr">
         <is>
           <t>2.111.754</t>
         </is>
       </c>
-      <c r="I155" s="3" t="inlineStr">
+      <c r="K155" s="3" t="inlineStr">
         <is>
           <t>99.0%</t>
         </is>
       </c>
-      <c r="J155" s="3" t="inlineStr">
+      <c r="L155" s="3" t="inlineStr">
         <is>
           <t>1.33270233448056</t>
         </is>
       </c>
-      <c r="K155" s="3" t="inlineStr"/>
-      <c r="L155" s="3" t="inlineStr">
+      <c r="M155" s="3" t="inlineStr"/>
+      <c r="N155" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_154.html</t>
         </is>
@@ -7770,17 +9102,19 @@
           <t>Aumentar a eficiência do tratamento</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr"/>
-      <c r="I156" s="2" t="inlineStr"/>
       <c r="J156" s="2" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="2" t="inlineStr">
+      <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_155.html</t>
         </is>
@@ -7817,17 +9151,19 @@
           <t>Aumentar a eficiência do tratamento</t>
         </is>
       </c>
-      <c r="G157" s="3" t="inlineStr">
+      <c r="G157" s="3" t="inlineStr"/>
+      <c r="H157" s="3" t="inlineStr"/>
+      <c r="I157" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr"/>
-      <c r="I157" s="3" t="inlineStr"/>
       <c r="J157" s="3" t="inlineStr"/>
       <c r="K157" s="3" t="inlineStr"/>
-      <c r="L157" s="3" t="inlineStr">
+      <c r="L157" s="3" t="inlineStr"/>
+      <c r="M157" s="3" t="inlineStr"/>
+      <c r="N157" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_156.html</t>
         </is>
@@ -7864,17 +9200,19 @@
           <t>Aumentar a eficiência do tratamento</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr"/>
-      <c r="I158" s="2" t="inlineStr"/>
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
-      <c r="L158" s="2" t="inlineStr">
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_157.html</t>
         </is>
@@ -7911,17 +9249,19 @@
           <t>Aumentar a eficiência do tratamento</t>
         </is>
       </c>
-      <c r="G159" s="3" t="inlineStr">
+      <c r="G159" s="3" t="inlineStr"/>
+      <c r="H159" s="3" t="inlineStr"/>
+      <c r="I159" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr"/>
-      <c r="I159" s="3" t="inlineStr"/>
       <c r="J159" s="3" t="inlineStr"/>
       <c r="K159" s="3" t="inlineStr"/>
-      <c r="L159" s="3" t="inlineStr">
+      <c r="L159" s="3" t="inlineStr"/>
+      <c r="M159" s="3" t="inlineStr"/>
+      <c r="N159" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_158.html</t>
         </is>
@@ -7959,26 +9299,28 @@
           <t>Aumentar a eficiência do tratamento</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr">
         <is>
           <t>Desde o inicio do Projecto em 2019</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="J160" s="2" t="inlineStr">
         <is>
           <t>Mulheres gravidas e lactantes
 Provedores dos servicos de SMI
 MM</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr">
+      <c r="K160" s="2" t="inlineStr">
         <is>
           <t>Todas as US AJUDA (149) Manica (51), Niassa(18), Sofala (47) e Tete (33)</t>
         </is>
       </c>
-      <c r="J160" s="2" t="inlineStr"/>
-      <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="2" t="inlineStr">
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_159.html</t>
         </is>
@@ -8015,24 +9357,26 @@
           <t>Aumentar a eficiência do tratamento</t>
         </is>
       </c>
-      <c r="G161" s="3" t="inlineStr">
+      <c r="G161" s="3" t="inlineStr"/>
+      <c r="H161" s="3" t="inlineStr"/>
+      <c r="I161" s="3" t="inlineStr">
         <is>
           <t>Desde o inicio do Projecto em 2019</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr">
+      <c r="J161" s="3" t="inlineStr">
         <is>
           <t>Mulher Lactante  e pacientes HIV+                                                                                                                                                                                  ESMI</t>
         </is>
       </c>
-      <c r="I161" s="3" t="inlineStr">
+      <c r="K161" s="3" t="inlineStr">
         <is>
           <t>Todas as US AJUDA (149) Manica (51), Niassa(18), Sofala (47) e Tete (33)</t>
         </is>
       </c>
-      <c r="J161" s="3" t="inlineStr"/>
-      <c r="K161" s="3" t="inlineStr"/>
-      <c r="L161" s="3" t="inlineStr">
+      <c r="L161" s="3" t="inlineStr"/>
+      <c r="M161" s="3" t="inlineStr"/>
+      <c r="N161" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_160.html</t>
         </is>
@@ -8070,12 +9414,22 @@
           <t>Aumentar a cobertura das intervenções de PTV</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais para implementação</t>
+        </is>
+      </c>
       <c r="I162" s="2" t="inlineStr"/>
       <c r="J162" s="2" t="inlineStr"/>
       <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="2" t="inlineStr">
+      <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_161.html</t>
         </is>
@@ -8112,12 +9466,22 @@
           <t>Melhorar a coordenação e implementação</t>
         </is>
       </c>
-      <c r="G163" s="3" t="inlineStr"/>
-      <c r="H163" s="3" t="inlineStr"/>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>Nacional e Provincial</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>Recursos para logística e organização de reuniões</t>
+        </is>
+      </c>
       <c r="I163" s="3" t="inlineStr"/>
       <c r="J163" s="3" t="inlineStr"/>
       <c r="K163" s="3" t="inlineStr"/>
-      <c r="L163" s="3" t="inlineStr">
+      <c r="L163" s="3" t="inlineStr"/>
+      <c r="M163" s="3" t="inlineStr"/>
+      <c r="N163" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_162.html</t>
         </is>
@@ -8154,12 +9518,22 @@
           <t>disponibilizar o pacote no plataforma telesaude</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
+        </is>
+      </c>
       <c r="I164" s="2" t="inlineStr"/>
       <c r="J164" s="2" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="2" t="inlineStr">
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_163.html</t>
         </is>
@@ -8197,12 +9571,22 @@
           <t>Garantir a eliminação da transmissão vertical</t>
         </is>
       </c>
-      <c r="G165" s="3" t="inlineStr"/>
-      <c r="H165" s="3" t="inlineStr"/>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais necessários</t>
+        </is>
+      </c>
       <c r="I165" s="3" t="inlineStr"/>
       <c r="J165" s="3" t="inlineStr"/>
       <c r="K165" s="3" t="inlineStr"/>
-      <c r="L165" s="3" t="inlineStr">
+      <c r="L165" s="3" t="inlineStr"/>
+      <c r="M165" s="3" t="inlineStr"/>
+      <c r="N165" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_164.html</t>
         </is>
@@ -8240,12 +9624,22 @@
           <t>Monitorar o progresso e eficácia do plano</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais para avaliação</t>
+        </is>
+      </c>
       <c r="I166" s="2" t="inlineStr"/>
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="2" t="inlineStr">
+      <c r="L166" s="2" t="inlineStr"/>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_165.html</t>
         </is>
@@ -8282,12 +9676,22 @@
           <t>Fortalecer a gestão e implementação das intervenções</t>
         </is>
       </c>
-      <c r="G167" s="3" t="inlineStr"/>
-      <c r="H167" s="3" t="inlineStr"/>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos qualificados e materiais de apoio</t>
+        </is>
+      </c>
       <c r="I167" s="3" t="inlineStr"/>
       <c r="J167" s="3" t="inlineStr"/>
       <c r="K167" s="3" t="inlineStr"/>
-      <c r="L167" s="3" t="inlineStr">
+      <c r="L167" s="3" t="inlineStr"/>
+      <c r="M167" s="3" t="inlineStr"/>
+      <c r="N167" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_166.html</t>
         </is>
@@ -8324,12 +9728,22 @@
           <t>Melhorar a capacidade de atendimento</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>Recursos financeiros para contratação</t>
+        </is>
+      </c>
       <c r="I168" s="2" t="inlineStr"/>
       <c r="J168" s="2" t="inlineStr"/>
       <c r="K168" s="2" t="inlineStr"/>
-      <c r="L168" s="2" t="inlineStr">
+      <c r="L168" s="2" t="inlineStr"/>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_167.html</t>
         </is>
@@ -8366,12 +9780,22 @@
           <t>Aumentar a capacidade de resposta comunitária</t>
         </is>
       </c>
-      <c r="G169" s="3" t="inlineStr"/>
-      <c r="H169" s="3" t="inlineStr"/>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>Communidade</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>Materiais de formação e recursos humanos</t>
+        </is>
+      </c>
       <c r="I169" s="3" t="inlineStr"/>
       <c r="J169" s="3" t="inlineStr"/>
       <c r="K169" s="3" t="inlineStr"/>
-      <c r="L169" s="3" t="inlineStr">
+      <c r="L169" s="3" t="inlineStr"/>
+      <c r="M169" s="3" t="inlineStr"/>
+      <c r="N169" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_168.html</t>
         </is>
@@ -8409,12 +9833,22 @@
           <t>Aumentar a conscientização e educação em saúde</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para desenvolvimento de materiais de comunicação</t>
+        </is>
+      </c>
       <c r="I170" s="2" t="inlineStr"/>
       <c r="J170" s="2" t="inlineStr"/>
       <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="2" t="inlineStr">
+      <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_169.html</t>
         </is>
@@ -8452,12 +9886,22 @@
           <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
-      <c r="G171" s="3" t="inlineStr"/>
-      <c r="H171" s="3" t="inlineStr"/>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
       <c r="I171" s="3" t="inlineStr"/>
       <c r="J171" s="3" t="inlineStr"/>
       <c r="K171" s="3" t="inlineStr"/>
-      <c r="L171" s="3" t="inlineStr">
+      <c r="L171" s="3" t="inlineStr"/>
+      <c r="M171" s="3" t="inlineStr"/>
+      <c r="N171" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_170.html</t>
         </is>
@@ -8495,12 +9939,22 @@
           <t>Informar estratégias e intervenções baseadas em evidências</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para pesquisa e coleta de dados</t>
+        </is>
+      </c>
       <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="2" t="inlineStr"/>
       <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="2" t="inlineStr">
+      <c r="L172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_171.html</t>
         </is>
@@ -8540,26 +9994,36 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para tratamento</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="H173" s="3" t="inlineStr">
+      <c r="J173" s="3" t="inlineStr">
         <is>
           <t>266.240</t>
         </is>
       </c>
-      <c r="I173" s="3" t="inlineStr">
+      <c r="K173" s="3" t="inlineStr">
         <is>
           <t>93.2%</t>
         </is>
       </c>
-      <c r="J173" s="3" t="inlineStr">
+      <c r="L173" s="3" t="inlineStr">
         <is>
           <t>14.80509942741094</t>
         </is>
       </c>
-      <c r="K173" s="3" t="inlineStr"/>
-      <c r="L173" s="3" t="inlineStr">
+      <c r="M173" s="3" t="inlineStr"/>
+      <c r="N173" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_172.html</t>
         </is>
@@ -8599,17 +10063,19 @@
           <t>Melhorar o tratamento e prevenção de TB</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr"/>
-      <c r="I174" s="2" t="inlineStr"/>
       <c r="J174" s="2" t="inlineStr"/>
       <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="2" t="inlineStr">
+      <c r="L174" s="2" t="inlineStr"/>
+      <c r="M174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_173.html</t>
         </is>
@@ -8646,17 +10112,19 @@
           <t>Melhorar o tratamento e prevenção de TB</t>
         </is>
       </c>
-      <c r="G175" s="3" t="inlineStr">
+      <c r="G175" s="3" t="inlineStr"/>
+      <c r="H175" s="3" t="inlineStr"/>
+      <c r="I175" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H175" s="3" t="inlineStr"/>
-      <c r="I175" s="3" t="inlineStr"/>
       <c r="J175" s="3" t="inlineStr"/>
       <c r="K175" s="3" t="inlineStr"/>
-      <c r="L175" s="3" t="inlineStr">
+      <c r="L175" s="3" t="inlineStr"/>
+      <c r="M175" s="3" t="inlineStr"/>
+      <c r="N175" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_174.html</t>
         </is>
@@ -8696,17 +10164,19 @@
           <t>Melhorar o tratamento e prevenção de TB</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr"/>
-      <c r="I176" s="2" t="inlineStr"/>
       <c r="J176" s="2" t="inlineStr"/>
       <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="2" t="inlineStr">
+      <c r="L176" s="2" t="inlineStr"/>
+      <c r="M176" s="2" t="inlineStr"/>
+      <c r="N176" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_175.html</t>
         </is>
@@ -8743,17 +10213,19 @@
           <t>Melhorar o tratamento e prevenção de TB</t>
         </is>
       </c>
-      <c r="G177" s="3" t="inlineStr">
+      <c r="G177" s="3" t="inlineStr"/>
+      <c r="H177" s="3" t="inlineStr"/>
+      <c r="I177" s="3" t="inlineStr">
         <is>
           <t>2011 (MC)
 2025 (Gaza)</t>
         </is>
       </c>
-      <c r="H177" s="3" t="inlineStr"/>
-      <c r="I177" s="3" t="inlineStr"/>
       <c r="J177" s="3" t="inlineStr"/>
       <c r="K177" s="3" t="inlineStr"/>
-      <c r="L177" s="3" t="inlineStr">
+      <c r="L177" s="3" t="inlineStr"/>
+      <c r="M177" s="3" t="inlineStr"/>
+      <c r="N177" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_176.html</t>
         </is>
@@ -8797,16 +10269,18 @@
           <t>Melhorar o tratamento e prevenção de TB</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>Desde o inicio do Projecto em 2019</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr"/>
-      <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="2" t="inlineStr"/>
       <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="2" t="inlineStr">
+      <c r="L178" s="2" t="inlineStr"/>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_177.html</t>
         </is>

--- a/hiv/catalogo_HIV.xlsx
+++ b/hiv/catalogo_HIV.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N178"/>
+  <dimension ref="A1:N155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -610,15 +610,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>RH</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">▪Nacional: 1 assessora de APSS
-▪Provincial: Gestor de APSS (1 MC)
-▪Distritos (MC): Oficiais de APSS e Psicólogos distritais
-▪US (MC/GZ): Conselheiros, Gestores de caso, supervisores de campo, conselheiros comunitários, AJM, HC e EP </t>
+          <t>Apoio técnico e logistico para realização de formações em sala assim como em serviço</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -628,15 +625,22 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Apoiar de intervenção nas pessoas e comunidades afetadas pelo HIV</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
+          <t>Aumentar a capacidade de resposta dos profissionais</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Unidades de Saúde</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Materiais de formação e recursos humanos</t>
+        </is>
+      </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr"/>
@@ -662,12 +666,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Supplies</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Apoio técnico e logistico para realização de formações em sala assim como em serviço</t>
+          <t xml:space="preserve">. Aquisição de material de escritório (canetas, cadernos, papeleiros, etc)
+. Impressão de instrumentos de registos e Job aids
+. Alocacao de mobiliario </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -677,15 +683,22 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Apoiar de intervenção nas pessoas e comunidades afetadas pelo HIV</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>Garantir a disponibilidade de materiais necessários</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Unidades de Saúde</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Recursos financeiros e logísticos</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -711,14 +724,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Supplies</t>
+          <t>RH (Nivel Central)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">. Aquisição de material de escritório (canetas, cadernos, papeleiros, etc)
-. Impressão de instrumentos de registos e Job aids
-. Alocacao de mobiliario </t>
+          <t>Contratação de conselheiros leigos  e educadores de Pares para oferta de Apoio Psicossocial na US e Comunidade.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -731,14 +742,17 @@
           <t>Apoiar de intervenção nas pessoas e comunidades afetadas pelo HIV</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos qualificados</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
@@ -762,12 +776,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Apoio Tecnico</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Apoio técnico ao Sistema Nacional de Saúde através de oficiais técnicos nas Unidades Sanitárias e distritos, gestores a nível provincial e assessores técnicos a nível central, garantindo apoio direto no terreno, coordenação programática e orientação estratégica para a melhoria da qualidade dos serviços.</t>
+          <t>Seguimento Preventivo de utentes Vivendo com HIV (Casos especiais, utentes reintegrados)  e reintegração de pacientes faltosos e abandonos atraves de chamadas telefonicas , Visitas domiciliares e envio de mensagens lembretes e de reforço de adesão</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -777,17 +792,20 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Apoiar de intervenção nas pessoas e comunidades afetadas pelo HIV</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
+          <t>Aumentar a adesão ao tratamento</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Materiais de apoio</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
@@ -811,17 +829,13 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>APSS</t>
+          <t xml:space="preserve">
+Supplies/Insumos</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1. Contratação e alocação de conselheiros, mães mentoras, AJM e psicólogos 
-2. Geração e impressão de listas a partir do SESP para apoio na identificação de pacientes que necessitam de intervenção de APSS (factores de risco, faltosos e seguimento de adesão)
-3. Provisão directa de serviços de aconselhamento para reforço de adesão 
-4. Reprodução de material de apoio e instrumentos de registo
-6. Visitas ao domicilio para provisao de servicos de APSS (seguimento preventivo, reintegracao, reforco de adesao, etc) 
-8. Monitoria do desempenho do staff comunitario</t>
+          <t>Reprodução de materiais de apoio no âmbito da oferta dos Serviços de APSS/PP</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -831,26 +845,22 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Apoiar de intervenção nas pessoas e comunidades afetadas pelo HIV</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>FY19Q1</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Todos pacientes elegíveis</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>US AJUDA PrEP (102) das províncias de Manica (37), Niassa (18), Sofala (23), Tete (24). Dados ate JAN 2026</t>
-        </is>
-      </c>
+          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
@@ -872,12 +882,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>RH (Nivel Central)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Contratação de conselheiros leigos  e educadores de Pares para oferta de Apoio Psicossocial na US e Comunidade.</t>
+          <t>Capacitação dos Atendentes do ALO VIDA nas areas do PNC ITS HIV e SIDA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -887,17 +897,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Apoiar de intervenção nas pessoas e comunidades afetadas pelo HIV</t>
+          <t>Capacitar pessoal para suporte a PVHIV</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Recursos humanos qualificados</t>
+          <t>Formação e materiais de apoio</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -924,13 +934,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Seguimento Preventivo de utentes Vivendo com HIV (Casos especiais, utentes reintegrados)  e reintegração de pacientes faltosos e abandonos atraves de chamadas telefonicas , Visitas domiciliares e envio de mensagens lembretes e de reforço de adesão</t>
+          <t xml:space="preserve"> Conversão do Pacote de Auto estigma para Treino de Provedores na plataforma de Telessaude  </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -940,17 +949,17 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a adesão ao tratamento</t>
+          <t>disponibilizar o pacote no plataforma telesaude</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Materiais de apoio</t>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
@@ -977,13 +986,13 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Supplies/Insumos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Reprodução de materiais de apoio no âmbito da oferta dos Serviços de APSS/PP</t>
+          <t>Oferta integrada de Apoio Psicossocial para preparação (Aconselhamento Pre-TARV) e seguimento de adesão de Utentes Vivendo com HIV</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -993,17 +1002,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
+          <t>Aumentar a adesão ao tratamento</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>contratos de impressão</t>
+          <t>Recursos humanos e materiais de apoio</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1030,12 +1039,13 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Capacitação dos Atendentes do ALO VIDA nas areas do PNC ITS HIV e SIDA</t>
+          <t>Rastreio de Doenças Mentais em PVHIV com Factores Psicossociais que afectam a adesão</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1045,7 +1055,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Capacitar pessoal para suporte a PVHIV</t>
+          <t>Diagnosticar e tratar doenças mentais relacionadas</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1055,7 +1065,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Formação e materiais de apoio</t>
+          <t>Profissionais de saúde qualificados</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
@@ -1082,12 +1092,13 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Conversão do Pacote de Auto estigma para Treino de Provedores na plataforma de Telessaude  </t>
+          <t>Revelação de Diagnostico para crianças vivendo com HIV</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1097,17 +1108,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>disponibilizar o pacote no plataforma telesaude</t>
+          <t>Apoiar crianças na aceitação do diagnóstico</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>equipamento de gravação, tempo, plataform de telesaude</t>
+          <t>Materiais educativos e formações</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1140,7 +1151,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Oferta integrada de Apoio Psicossocial para preparação (Aconselhamento Pre-TARV) e seguimento de adesão de Utentes Vivendo com HIV</t>
+          <t>Certificação de Unidades Sanitarias Livres de Estigma e Discriminação</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1150,17 +1161,17 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a adesão ao tratamento</t>
+          <t>Prover ambientes seguros paraPVHIV</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Recursos humanos e materiais de apoio</t>
+          <t>Programa de certificação e avaliação</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
@@ -1193,7 +1204,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Rastreio de Doenças Mentais em PVHIV com Factores Psicossociais que afectam a adesão</t>
+          <t>Avaliação e actualização da ferramenta de apoio as famílias de PVHIV</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1203,17 +1214,17 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Diagnosticar e tratar doenças mentais relacionadas</t>
+          <t>Melhorar o suporte às famílias</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Profissionais de saúde qualificados</t>
+          <t>Recursos e tecnologia para avaliação</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1246,7 +1257,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Revelação de Diagnostico para crianças vivendo com HIV</t>
+          <t>Elaboração do Guião integrado de Abordagens de Pares para Utentes Vivendo com HIV</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1256,7 +1267,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Apoiar crianças na aceitação do diagnóstico</t>
+          <t>Mobilizar pares para apoio às PVHIV</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1266,7 +1277,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Materiais educativos e formações</t>
+          <t>Formadores e recursos informativos</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
@@ -1288,18 +1299,18 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>APSS</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Oral Teste (Auto Teste)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Certificação de Unidades Sanitarias Livres de Estigma e Discriminação</t>
+          <t>Medicamentos/
+Insumos</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1309,7 +1320,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Prover ambientes seguros paraPVHIV</t>
+          <t>Aumentar a testagem e diagnósticos</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1319,13 +1330,29 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Programa de certificação e avaliação</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>Testes de autoavalição e materiais informativos</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>254.946</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>50.22630007782692</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0.385679676495397</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1341,18 +1368,18 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>APSS</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>ATS TDR HIV</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Avaliação e actualização da ferramenta de apoio as famílias de PVHIV</t>
+          <t>Medicamentos/
+Insumos</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1362,7 +1389,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Melhorar o suporte às famílias</t>
+          <t>Diagnosticar e tratar HIV</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1372,13 +1399,29 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Recursos e tecnologia para avaliação</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
+          <t>Materiais e reagentes para teste</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>254.946</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>50.22630007782692</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>0.537877067032586</t>
+        </is>
+      </c>
       <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr">
         <is>
@@ -1394,18 +1437,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>APSS</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>RH (Nivel Central)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Elaboração do Guião integrado de Abordagens de Pares para Utentes Vivendo com HIV</t>
+          <t>Assessor para área de ATS no MISAU</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1415,17 +1457,17 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Mobilizar pares para apoio às PVHIV</t>
+          <t>Fortalecer a coordenação de ATS no MISAU</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Formadores e recursos informativos</t>
+          <t>Capacidade de gestão e coordenação</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1452,13 +1494,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Oral Teste (Auto Teste)</t>
+          <t>RH (Nivel US)</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Medicamentos/
-Insumos</t>
+          <t>Contratação de Conselheiros para implementação do ATIP e do ATIU na US</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1468,39 +1509,23 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a testagem e diagnósticos</t>
+          <t>Melhorar a implementação de ATS</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Testes de autoavalição e materiais informativos</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>254.946</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>50.22630007782692</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>0.385679676495397</t>
-        </is>
-      </c>
+          <t>Formação e supervisão de pessoal</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
       <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="3" t="inlineStr">
         <is>
@@ -1521,13 +1546,13 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ATS TDR HIV</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Medicamentos/
-Insumos</t>
+          <t>Oferta de Aconselhamento e Testagem Iniciado pelo Utente (ATIU) na Comunidade, incluindo a distribuição do ATHIV para todos utentes elegíveis</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1537,7 +1562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Diagnosticar e tratar HIV</t>
+          <t>Aumentar a testagem e diagnósticos precoces</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1550,26 +1575,10 @@
           <t>Materiais e reagentes para teste</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>254.946</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>50.22630007782692</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0.537877067032586</t>
-        </is>
-      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1590,18 +1599,13 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>1. Provisão direta de serviços clínicos de ATS na US e comunidade e ligacao aos CT
-2. Distribuição de selftesting na comunidade
-3. Formações de certificação inicial 
-4. Formações de recertificação a cada dois (2) anos
-5. Reprodução de material de apoio e de instrumentos de registo de ATS
-6. Aquisição de cronómetros e pilhas
-7. Aquisição de batas (uniforme) para os conselheiros/staff leigo alocado as US</t>
+          <t>Implementação faseada de uso de ATHIV para o inicio e continuidade da PrEP oral e injectável</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1611,29 +1615,22 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Diagnosticar e tratar HIV</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>Desde o inicio do Projecto em 2019</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Todos os pacientes elegiveis 
-Todas as portas e modalidades de testagem
-Provedores das US
-Conselheiros leigos</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>Todas as US AJUDA (149) Manica (51), Niassa(18), Sofala (47) e Tete (33)</t>
-        </is>
-      </c>
+          <t>Aumentar a adesão à PrEP entre populações em risco</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais de apoio</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
       <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="inlineStr">
@@ -1655,12 +1652,13 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>RH (Nivel Central)</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Assessor para área de ATS no MISAU</t>
+          <t>Implementação da estratégia de Caso índice para o alcance de casos com HIV</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1670,17 +1668,17 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Fortalecer a coordenação de ATS no MISAU</t>
+          <t>Diagnosticar e tratar pessoas com HIV rapidamente</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Capacidade de gestão e coordenação</t>
+          <t>Treinamento e materiais informativos</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1707,12 +1705,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>RH (Nivel US)</t>
+          <t>Supplies/Insumos</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Contratação de Conselheiros para implementação do ATIP e do ATIU na US</t>
+          <t>Reprodução e alocação na US e comunidade dos algoritmos simplificados para elegibilidade para testagem do HIV</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1722,17 +1720,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a implementação de ATS</t>
+          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Unidades Sanitarias e Communidade</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Formação e supervisão de pessoal</t>
+          <t>contratos de impressão</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
@@ -1759,13 +1757,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Oferta de Aconselhamento e Testagem Iniciado pelo Utente (ATIU) na Comunidade, incluindo a distribuição do ATHIV para todos utentes elegíveis</t>
+          <t>Formações para implementação nacional do algoritmo de 3 testes</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1775,17 +1772,17 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Aumentar a testagem e diagnósticos precoces</t>
+          <t>Garantir a precisão no diagnóstico de HIV</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Materiais e reagentes para teste</t>
+          <t>Materiais de formação e recursos humanos</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1812,13 +1809,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Implementação faseada de uso de ATHIV para o inicio e continuidade da PrEP oral e injectável</t>
+          <t>Conversão do pacote de formacao de ATS para a plataforma telessaúde</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1828,17 +1824,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a adesão à PrEP entre populações em risco</t>
+          <t>disponibilizar o pacote no plataforma telesaude</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Recursos humanos e materiais de apoio</t>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
@@ -1865,13 +1861,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Implementação da estratégia de Caso índice para o alcance de casos com HIV</t>
+          <t>Formações para implementação e expansão do ATHIV na US</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1881,7 +1876,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Diagnosticar e tratar pessoas com HIV rapidamente</t>
+          <t>Expandir o acesso e uso do ATHIV</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1891,7 +1886,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Treinamento e materiais informativos</t>
+          <t>Recursos para capacitação e equipamentos</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1918,12 +1913,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Supplies/Insumos</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Reprodução e alocação na US e comunidade dos algoritmos simplificados para elegibilidade para testagem do HIV</t>
+          <t>Formações em ATS incluindo ATHIV</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1933,17 +1928,17 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
+          <t>Melhorar a qualidade do atendimento em ATS</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias e Communidade</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>contratos de impressão</t>
+          <t>Materiais de formação e acompanhamento</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
@@ -1975,7 +1970,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Formações para implementação nacional do algoritmo de 3 testes</t>
+          <t>Capacitação de provedores para Oferta de Aconselhamento e Testagem Iniciado pelo Provedor (ATIP) de rotina e mediante avaliação de elegibilidade nos serviços clínicos.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1985,7 +1980,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Garantir a precisão no diagnóstico de HIV</t>
+          <t>Aumentar a testagem e a adesão ao tratamento</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1995,7 +1990,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Materiais de formação e recursos humanos</t>
+          <t>Recursos humanos qualificados e materiais</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2022,12 +2017,13 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Conversão do pacote de formacao de ATS para a plataforma telessaúde</t>
+          <t xml:space="preserve">Oferta de Aconselhamento e Testagem Iniciado pelo Provedor (ATIP) de rotina e mediante avaliação de elegibilidade nos serviços clínicos da Unidade Sanitária, para todos utentes elegíveis </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -2037,17 +2033,17 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>disponibilizar o pacote no plataforma telesaude</t>
+          <t>Aumentar a testagem em unidades clínicas</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>equipamento de gravação, tempo, plataform de telesaude</t>
+          <t>Materiais de apoio e reagentes para teste</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr"/>
@@ -2074,12 +2070,13 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Formações para implementação e expansão do ATHIV na US</t>
+          <t xml:space="preserve">Oferta de Aconselhamento e Testagem Iniciado pelo Utente (ATIU) na UATS da Unidade Sanitária, para todos utentes voluntários </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2089,7 +2086,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Expandir o acesso e uso do ATHIV</t>
+          <t>Aumentar a testagem voluntária</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2099,7 +2096,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Recursos para capacitação e equipamentos</t>
+          <t>Recursos e sensibilização nas comunidades</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2126,12 +2123,13 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Formações em ATS incluindo ATHIV</t>
+          <t>Oferta de ATHIV nas US</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2141,7 +2139,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade do atendimento em ATS</t>
+          <t>Expandir o acesso ao tratamento HIV</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2151,7 +2149,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Materiais de formação e acompanhamento</t>
+          <t>Recursos para tratamento e capacitação</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr"/>
@@ -2178,12 +2176,13 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Capacitação de provedores para Oferta de Aconselhamento e Testagem Iniciado pelo Provedor (ATIP) de rotina e mediante avaliação de elegibilidade nos serviços clínicos.</t>
+          <t>Oferta do ATHIV sanguineo</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2193,17 +2192,17 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Aumentar a testagem e a adesão ao tratamento</t>
+          <t>Melhorar a detecção e tratamento precoce de HIV</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Recursos humanos qualificados e materiais</t>
+          <t>Materiais e equipamentos para testes</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2225,18 +2224,18 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>C&amp;T ADULTO</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>ARVs Adultos</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oferta de Aconselhamento e Testagem Iniciado pelo Provedor (ATIP) de rotina e mediante avaliação de elegibilidade nos serviços clínicos da Unidade Sanitária, para todos utentes elegíveis </t>
+          <t>Medicamentos/
+Insumos</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2246,7 +2245,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a testagem em unidades clínicas</t>
+          <t>Garantir o fornecimento contínuo de ARVs</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2256,13 +2255,29 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Materiais de apoio e reagentes para teste</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr"/>
+          <t>Estoque adequado de ARVs e insumos necessários</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>&lt;2015</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>2.300.000</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>84.1%</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>31.82389388066507</t>
+        </is>
+      </c>
       <c r="M33" s="3" t="inlineStr"/>
       <c r="N33" s="3" t="inlineStr">
         <is>
@@ -2278,18 +2293,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>C&amp;T ADULTO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>C&amp;T Adulto: Formações/Treinos</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oferta de Aconselhamento e Testagem Iniciado pelo Utente (ATIU) na UATS da Unidade Sanitária, para todos utentes voluntários </t>
+          <t>Apoio técnico e logistico para realização de formações em sala assim como em serviço</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2299,20 +2313,24 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Aumentar a testagem voluntária</t>
+          <t>Melhorar a qualidade dos serviços de saúde</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Unidades de Saúde</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Recursos e sensibilização nas comunidades</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t>Materiais de formação e recursos humanos</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
@@ -2331,18 +2349,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>C&amp;T ADULTO</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>C&amp;T Adulto: Supplies</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Oferta de ATHIV nas US</t>
+          <t>Alocação de material de escritório, instrumentos de registo, material medico cirurgico anualmente</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2352,20 +2369,24 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Expandir o acesso ao tratamento HIV</t>
+          <t>Melhorar o registro e a gestão de dados</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Unidades de Saúde</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Recursos para tratamento e capacitação</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
+          <t>Recursos para aquisição de materiais</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
       <c r="J35" s="3" t="inlineStr"/>
       <c r="K35" s="3" t="inlineStr"/>
       <c r="L35" s="3" t="inlineStr"/>
@@ -2384,18 +2405,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>C&amp;T ADULTO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Oferta do ATHIV sanguineo</t>
+          <t>Realizar reunião híbrida sobre a implementação dos MDS</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2405,7 +2425,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a detecção e tratamento precoce de HIV</t>
+          <t>Melhorar a implementação dos MDS em comunidades</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2415,10 +2435,14 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Materiais e equipamentos para testes</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>Materiais de apoio e recursos humanos para a formação</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
@@ -2442,13 +2466,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>ARVs Adultos</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Medicamentos/
-Insumos</t>
+          <t>Oficina de Trabalho para a actualizaçao da Plataforma das visitas de monitoria das intervenções vitais no âmbito da qualidade assistencial</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2458,39 +2481,23 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Garantir o fornecimento contínuo de ARVs</t>
+          <t>Melhorar a qualidade das visitas de monitoria</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Estoque adequado de ARVs e insumos necessários</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>&lt;2015</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>2.300.000</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>84.1%</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>31.82389388066507</t>
-        </is>
-      </c>
+          <t>Recursos humanos qualificados e materiais de apoio</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="3" t="inlineStr"/>
       <c r="N37" s="3" t="inlineStr">
         <is>
@@ -2511,15 +2518,13 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T Adulto: RH</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>▪Nacional: 1 assessora de C&amp;T_Adulto
-▪Provincial: Gestor de C&amp;T_adulto (1 MC/ 1 GZ)
-▪Distritos: Coordenadores distritais
-▪US: MC- Alocação de TMGs nas US com défice de RH (actualmente cerca de 15% destes são pontos focais de programas nas US). MC/GZ - Oficiais de programa e Alocação de arquivistas nas US's de médio e grande volume.</t>
+          <t>Realizar visitas de monitoria das intervenções vitais no âmbito da qualidade assistencial</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2529,17 +2534,20 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Garantir o fornecimento contínuo de ARVs</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
+          <t>Aumentar a eficácia das intervenções</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Equipe de monitores e ferramentas de avaliação</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
@@ -2563,12 +2571,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T Adulto: Formações/Treinos</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Apoio técnico e logistico para realização de formações em sala assim como em serviço</t>
+          <t>Realizar oficinas de trabalho provinciais para a monitoria das intervenções vitais no âmbito da qualidade assistencial</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2578,17 +2586,20 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Garantir o fornecimento contínuo de ARVs</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
+          <t>Fortalecer a monitoria em nível provincial</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Materiais de formação e logística</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="inlineStr"/>
       <c r="L39" s="3" t="inlineStr"/>
@@ -2612,12 +2623,13 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T Adulto: Supplies</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Alocação de material de escritório, instrumentos de registo, material medico cirurgico anualmente</t>
+          <t xml:space="preserve">Implementação do guiao operacional para engajamento masculino </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2627,17 +2639,20 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Garantir o fornecimento contínuo de ARVs</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
+          <t>Aumentar o engajamento masculino</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Materiais educativos e recursos humanos</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
@@ -2661,12 +2676,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T Adulto: Apoio Tecnico</t>
+          <t>RH (Nivel Central)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Apoio técnico ao Sistema Nacional de Saúde através de oficiais técnicos nas Unidades Sanitárias e distritos, gestores a nível provincial e assessores técnicos a nível central, garantindo apoio direto no terreno, coordenação programática e orientação estratégica para a melhoria da qualidade dos serviços.</t>
+          <t xml:space="preserve">Contratação de Técnicos de Saude para prestação de serviços integrados de TARV </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2676,17 +2691,20 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Garantir o fornecimento contínuo de ARVs</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
+          <t>Melhorar a prestação de serviços TARV</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Recursos financeiros para recrutamento e treinamento</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="inlineStr"/>
       <c r="L41" s="3" t="inlineStr"/>
@@ -2710,26 +2728,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T Adulto</t>
+          <t>Supplies/Insumos</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1. Provisão directa de servicos clinicos atraves de DSD Staff alocados as US
-2. Apoio tecnico presencial e remota
-3. Revisão diaria de FM (CV, TPT, MDS) e colocacao de stickers para oferta de servico
-4. Trangulacao de dados (Activos em TARV, Novos inicios, CV, MI, DAH)
-5. Implementacao do novo Master Card (Formacao virtual e em servico, reproducao e distribuicao pelas US)
-6. Implementação dos Pacote/Directriz  de MQ, DAH, EM , MDS, entre outros 
-7. Expansao dos diversos serviços (DS, DAH, etc)
-8. MQHIV
-9. Apoio na realizacao  dos Comites de Servicos clinicos
-10. Recolha, analise e discussões dos dados  de Monitoria Intensiva
-11. Implementacao da Mentoria clinica 
-12. Cascata de Doenca avancada por HIV (Rastreio, Diagnostico, oferta Profilaxia/tratamento, triangulacao)
-13. Visita de apoio tecnico/supervisão
-14.  Aquisicao de material medico-cirurgico e cabines de manejo de citostaticos
-15.  Aquisicao de material de escritorio, mesas, cadeiras e armarios</t>
+          <t xml:space="preserve">Reprodução do Guia de MDS para HIV </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2739,26 +2743,22 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Garantir o fornecimento contínuo de ARVs</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>FY19Q1</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>1.934.622</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>US AJUDA PrEP (102) das províncias de Manica (37), Niassa (18), Sofala (23), Tete (24). Dados ate JAN 2026</t>
-        </is>
-      </c>
+          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Supplies/Insumos</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Realizar reunião híbrida sobre a implementação dos MDS</t>
+          <t>Assegurar a Reproducao e distribuição das cadernetas do Utente</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2795,24 +2795,20 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a implementação dos MDS em comunidades</t>
+          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Materiais de apoio e recursos humanos para a formação</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="3" t="inlineStr"/>
       <c r="L43" s="3" t="inlineStr"/>
@@ -2836,12 +2832,13 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Oficina de Trabalho para a actualizaçao da Plataforma das visitas de monitoria das intervenções vitais no âmbito da qualidade assistencial</t>
+          <t>Actualização periódica dos materiais de apoio para area de C&amp;T, em conformidade com as normas vigentes (Guiões, Directrizes e Pacotes de Formação...)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2851,7 +2848,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade das visitas de monitoria</t>
+          <t>Otimizar tratamento para todos os utentes</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2861,7 +2858,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Recursos humanos qualificados e materiais de apoio</t>
+          <t>Documentos e formações</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2888,13 +2885,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Realizar visitas de monitoria das intervenções vitais no âmbito da qualidade assistencial</t>
+          <t>Realizar refrescamentos e actualizacoes nas normas de TARV para criancas, adolescentes e adultos usando as diferentes plataformas Online existentes (nivel central, provincial e a nivel da US)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2904,7 +2900,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a eficácia das intervenções</t>
+          <t>Garantir a eliminação da transmissão vertical</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -2914,7 +2910,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Equipe de monitores e ferramentas de avaliação</t>
+          <t>Recursos humanos e materiais necessários</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr"/>
@@ -2941,12 +2937,13 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Realizar oficinas de trabalho provinciais para a monitoria das intervenções vitais no âmbito da qualidade assistencial</t>
+          <t>Garantir que todos os utentes (adultos, adolescentes e  crianças)  estejam em TARV com  regimes optimizados de acordo com as normas nacionais.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2956,7 +2953,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Fortalecer a monitoria em nível provincial</t>
+          <t>Aumentar a adesão ao tratamento</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2966,7 +2963,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Materiais de formação e logística</t>
+          <t>Acompanhamento e suporte dos profissionais de saúde</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2993,13 +2990,12 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Implementação do guiao operacional para engajamento masculino </t>
+          <t xml:space="preserve">Realizar oficina de Comite Terapeutico </t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -3009,7 +3005,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Aumentar o engajamento masculino</t>
+          <t>Fortalecer a adesão ao tratamento</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3019,7 +3015,7 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Materiais educativos e recursos humanos</t>
+          <t>Materiais e recursos para oficinas</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr"/>
@@ -3046,12 +3042,13 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>RH (Nivel Central)</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Técnicos de Saude para prestação de serviços integrados de TARV </t>
+          <t>Manter e reforçar a implementação de Dispensa Semestral nas 408 US em implementação e expandir para todos os pacientes elegiveis em coordenacao do MISAU de acordo com a disponibilidade de stocks de ARVs, priorizando áreas afectadas por crises humanitárias (incluíndo instabilidade política, desastres naturais e outros)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3061,17 +3058,17 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a prestação de serviços TARV</t>
+          <t>Melhorar a integração dos serviços de saúde</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Recursos financeiros para recrutamento e treinamento</t>
+          <t>Recursos humanos qualificados e materiais de apoio</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -3098,12 +3095,12 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Supplies/Insumos</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reprodução do Guia de MDS para HIV </t>
+          <t>Capacitação para Integração de serviços de DNTs e C&amp;T de HIV/SIDA</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -3113,17 +3110,17 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
+          <t>Melhorar a integração e qualidade dos serviços</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>contratos de impressão</t>
+          <t>Materiais de formação e recursos humanos para capacitação</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr"/>
@@ -3150,12 +3147,13 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Supplies/Insumos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Assegurar a Reproducao e distribuição das cadernetas do Utente</t>
+          <t>Formação de clínicos na gestão da hipertensão (pacote de integração)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3165,17 +3163,17 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
+          <t>Aumentar a competência dos clínicos</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>contratos de impressão</t>
+          <t>Materiais educativos e formação contínua</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -3208,7 +3206,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Actualização periódica dos materiais de apoio para area de C&amp;T, em conformidade com as normas vigentes (Guiões, Directrizes e Pacotes de Formação...)</t>
+          <t>Realizar visitas de monitoria das intervenções vitais no âmbito da qualidade assistencial</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -3218,17 +3216,17 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Otimizar tratamento para todos os utentes</t>
+          <t>Melhorar a qualidade do atendimento</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>Documentos e formações</t>
+          <t>Equipe de monitores e ferramentas de avaliação</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr"/>
@@ -3260,7 +3258,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Realizar refrescamentos e actualizacoes nas normas de TARV para criancas, adolescentes e adultos usando as diferentes plataformas Online existentes (nivel central, provincial e a nivel da US)</t>
+          <t xml:space="preserve">Conversão para o modelo de telessaude do pacote no âmbito da resposta as situações de emergência </t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3270,17 +3268,17 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Garantir a eliminação da transmissão vertical</t>
+          <t>disponibilizar o pacote no plataforma telesaude</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Recursos humanos e materiais necessários</t>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3302,18 +3300,18 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T ADULTO</t>
+          <t>C&amp;T GERAL</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t xml:space="preserve">CD4 </t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Garantir que todos os utentes (adultos, adolescentes e  crianças)  estejam em TARV com  regimes optimizados de acordo com as normas nacionais.</t>
+          <t>Medicamentos/
+Insumos</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -3323,7 +3321,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a adesão ao tratamento</t>
+          <t>Garantir a realização de testes de CD4</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -3333,14 +3331,34 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>Acompanhamento e suporte dos profissionais de saúde</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr"/>
-      <c r="J53" s="3" t="inlineStr"/>
-      <c r="K53" s="3" t="inlineStr"/>
-      <c r="L53" s="3" t="inlineStr"/>
-      <c r="M53" s="3" t="inlineStr"/>
+          <t>Equipamentos para teste e formação de pessoal</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>245.610</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>51.7%</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>30.33081522210056</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Dados de SESP</t>
+        </is>
+      </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_52.html</t>
@@ -3355,17 +3373,18 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T ADULTO</t>
+          <t>C&amp;T GERAL</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Carga Viral</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Realizar oficina de Comite Terapeutico </t>
+          <t>Medicamentos/
+Insumos</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3375,7 +3394,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Fortalecer a adesão ao tratamento</t>
+          <t>Monitorar a carga viral dos pacientes</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3385,13 +3404,29 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Materiais e recursos para oficinas</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
+          <t>Materiais e reagentes para teste</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>2.032.370</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>81.1%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>2.430270082098699</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3407,18 +3442,18 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T ADULTO</t>
+          <t>C&amp;T PED</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>ARVs Pediátricos</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Manter e reforçar a implementação de Dispensa Semestral nas 408 US em implementação e expandir para todos os pacientes elegiveis em coordenacao do MISAU de acordo com a disponibilidade de stocks de ARVs, priorizando áreas afectadas por crises humanitárias (incluíndo instabilidade política, desastres naturais e outros)</t>
+          <t>Medicamentos/
+Insumos</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -3428,7 +3463,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a integração dos serviços de saúde</t>
+          <t>Garantir o acesso a ARVs para crianças</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -3438,13 +3473,29 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Recursos humanos qualificados e materiais de apoio</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="3" t="inlineStr"/>
-      <c r="K55" s="3" t="inlineStr"/>
-      <c r="L55" s="3" t="inlineStr"/>
+          <t>Estoque adequado de ARVs pediátricos</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>&lt;2015</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>177.000</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>55.2%</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>40.8587316200843</t>
+        </is>
+      </c>
       <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="3" t="inlineStr">
         <is>
@@ -3460,17 +3511,18 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T ADULTO</t>
+          <t>C&amp;T PED</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>C&amp;T Ped: Formações/Treinos</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Capacitação para Integração de serviços de DNTs e C&amp;T de HIV/SIDA</t>
+          <t>∙ Apoio técnico e logístico para a realização de formações em sala e em serviço.
+∙ Suporte à realização do estágio clínico de provedores de C&amp;T ped no Centro de Excelência Pediátrico de Mavalane(Maputo Cidade)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3480,7 +3532,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a integração e qualidade dos serviços</t>
+          <t>Garantir o tratamento adequado para crianças</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3490,10 +3542,14 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Materiais de formação e recursos humanos para capacitação</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
+          <t>Medicamentos e insumos pediátricos</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
@@ -3512,18 +3568,18 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T ADULTO</t>
+          <t>C&amp;T PED</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>C&amp;T Ped: Supplies</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Formação de clínicos na gestão da hipertensão (pacote de integração)</t>
+          <t>∙ Alocação de material de escritório, instrumentos de registo, material medico cirurgico anualmente;
+∙ Apetrechamento das paragens únicas de pediatria com material lúdico;</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -3533,7 +3589,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a competência dos clínicos</t>
+          <t>Melhorar a qualidade de atendimento em saúde</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -3543,10 +3599,14 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>Materiais educativos e formação contínua</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr"/>
+          <t>Recursos humanos e materiais para formação</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
       <c r="J57" s="3" t="inlineStr"/>
       <c r="K57" s="3" t="inlineStr"/>
       <c r="L57" s="3" t="inlineStr"/>
@@ -3565,18 +3625,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T ADULTO</t>
+          <t>C&amp;T PED</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>RH (Nivel Central)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Realizar visitas de monitoria das intervenções vitais no âmbito da qualidade assistencial</t>
+          <t>Contratação de TMG para as paragens únicas de pediatria</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3586,17 +3645,17 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade do atendimento</t>
+          <t>Melhorar o atendimento pediátrico</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Equipe de monitores e ferramentas de avaliação</t>
+          <t>Recursos financeiros para recrutamento e treinamento</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3618,17 +3677,17 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T ADULTO</t>
+          <t>C&amp;T PED</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>RH (Nivel Central)</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conversão para o modelo de telessaude do pacote no âmbito da resposta as situações de emergência </t>
+          <t>Assessora para área de HIV Pediatrico e do Adolescente</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -3638,7 +3697,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>disponibilizar o pacote no plataforma telesaude</t>
+          <t>Fortalecer a abordagem pediátrica</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -3648,7 +3707,7 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>equipamento de gravação, tempo, plataform de telesaude</t>
+          <t>Recursos humanos qualificados e materiais de apoio</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr"/>
@@ -3670,18 +3729,18 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T GERAL</t>
+          <t>C&amp;T PED</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CD4 </t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Medicamentos/
-Insumos</t>
+          <t>Expandir e monitorar a implementação das intervenções das mães mentoras para as crianças dos 0-10 anos em todas as unidades sanitárias TARV.</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3691,7 +3750,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Garantir a realização de testes de CD4</t>
+          <t>Aumentar o suporte e adesão ao tratamento</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3701,34 +3760,14 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Equipamentos para teste e formação de pessoal</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>245.610</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>51.7%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>30.33081522210056</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>Dados de SESP</t>
-        </is>
-      </c>
+          <t>Recursos para capacitação e acompanhamento</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_59.html</t>
@@ -3743,18 +3782,17 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T GERAL</t>
+          <t>C&amp;T PED</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Carga Viral</t>
+          <t>Supplies/Insumos</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Medicamentos/
-Insumos</t>
+          <t xml:space="preserve">Reproduzir/Distribuir e alocar as ferramentas de TARV pediátrico e do adolescente e jovem incluindo: materias de formação, algoritmos, job aids, tripticos e  album seriado com mensagens de C&amp;T de adolescentes e jovens , albuns seriados "conhecendo os ARVs pediátricos) </t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -3764,39 +3802,23 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Monitorar a carga viral dos pacientes</t>
+          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Materiais e reagentes para teste</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>2.032.370</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>81.1%</t>
-        </is>
-      </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t>2.430270082098699</t>
-        </is>
-      </c>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
+      <c r="K61" s="3" t="inlineStr"/>
+      <c r="L61" s="3" t="inlineStr"/>
       <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="3" t="inlineStr">
         <is>
@@ -3817,13 +3839,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>ARVs Pediátricos</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Medicamentos/
-Insumos</t>
+          <t>Realizar actualizações e refrescamentos nas normas de HIV para crianças e adolescentes</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3833,7 +3854,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Garantir o acesso a ARVs para crianças</t>
+          <t>Melhorar a adesão e compreensão das normas</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3843,29 +3864,13 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Estoque adequado de ARVs pediátricos</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>&lt;2015</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>177.000</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>55.2%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>40.8587316200843</t>
-        </is>
-      </c>
+          <t>Materiais de formação e recursos humanos</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3886,14 +3891,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T Ped: RH</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>▪Nacional: 1 assessora de C&amp;T_Pediatrico
-▪Provincial: Gestor de C&amp;T_Pediatrico (1 MC/ 1 GZ)
-▪US: Contratação e alocação de mães mentoras de pediatria nas U.S apoiadas (28 em MC e 22 em GZ); Alocação de Oficiais de Programa de Pediatria em U.S de grande volume em Maputo Cidade</t>
+          <t>Realizar a conversão do pacote de HIV Pediátrico e do adolesente na plataforma Telesaúde</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -3903,17 +3906,20 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Garantir o acesso a ARVs para crianças</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr"/>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
+          <t>disponibilizar o pacote no plataforma telesaude</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr"/>
       <c r="J63" s="3" t="inlineStr"/>
       <c r="K63" s="3" t="inlineStr"/>
       <c r="L63" s="3" t="inlineStr"/>
@@ -3932,18 +3938,18 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T PED</t>
+          <t>Doenca Avancada</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T Ped: Formações/Treinos</t>
+          <t>Testes DAH</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>∙ Apoio técnico e logístico para a realização de formações em sala e em serviço.
-∙ Suporte à realização do estágio clínico de provedores de C&amp;T ped no Centro de Excelência Pediátrico de Mavalane(Maputo Cidade)</t>
+          <t>Medicamentos/
+Insumos</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3953,21 +3959,42 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Garantir o acesso a ARVs para crianças</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
+          <t>Melhorar a detecção precoce de doenças avançadas</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Equipamentos para testes e formação de pessoal</t>
+        </is>
+      </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>158.532</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>264541 novos inicios e 175826 reinicios</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_63.html</t>
@@ -3982,18 +4009,18 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T PED</t>
+          <t>Doenca Avancada</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T Ped: Supplies</t>
+          <t>Tratamento Meningite</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>∙ Alocação de material de escritório, instrumentos de registo, material medico cirurgico anualmente;
-∙ Apetrechamento das paragens únicas de pediatria com material lúdico;</t>
+          <t>Medicamentos/
+Insumos</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -4003,19 +4030,34 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Garantir o acesso a ARVs para crianças</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr"/>
-      <c r="H65" s="3" t="inlineStr"/>
+          <t>Garantir tratamento eficaz para meningite</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Estoque adequado de medicamentos e insumos</t>
+        </is>
+      </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr"/>
-      <c r="K65" s="3" t="inlineStr"/>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>158.532</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="inlineStr">
@@ -4032,17 +4074,18 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T PED</t>
+          <t>Doenca Avancada</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T Ped: Apoio Tecnico</t>
+          <t>Tratamento Sarcoma Kaposi</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Apoio técnico ao Sistema Nacional de Saúde através de oficiais técnicos nas Unidades Sanitárias e distritos, gestores a nível provincial e assessores técnicos a nível central, garantindo apoio direto no terreno, coordenação programática e orientação estratégica para a melhoria da qualidade dos serviços.</t>
+          <t>Medicamentos/
+Insumos</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4052,19 +4095,34 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Garantir o acesso a ARVs para crianças</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
+          <t>Aumentar a adesão ao tratamento de Sarcoma Kaposi</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para aquisição de medicamentos</t>
+        </is>
+      </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>158.532</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
@@ -4081,22 +4139,18 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T PED</t>
+          <t>Doenca Avancada</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T Ped</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>1. Provisao directa de servicos atraves dos TMG  alocados  nas PU de Ped pelo Projeto
-2. Aquisição de equipamentos e insumos para expanção de paragem unica Pediatria (Estetoscopio, esfigmomanometro, balanca, altimetro) e de escritorio)     
-3.  Planificacao , organisacao e monitoria das oficinas de TARV Pediatrico 
-4. Contratação das MM Pediatricas ,formacao ,  manutenção e supervisão das actividades 
-5. Apoio das US na capacitacao dos facilitadores de ligacao e implementação do programa OVC   
-6.  Encontros de coordenação com actores comunitários dos diferentes programa ( AJM , OVC , MM )</t>
+          <t>Capacitação de provedores no âmbito do seguimento de utentes com DAH</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -4106,26 +4160,22 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Garantir o acesso a ARVs para crianças</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>FY19Q1</t>
-        </is>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>97.748</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>Algumas US AJUDA das provincias de Manica , Niassa , Sofala , Tete</t>
-        </is>
-      </c>
+          <t>Melhorar a qualidade do acompanhamento</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Recursos para formação e capacitação de profissionais</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
+      <c r="K67" s="3" t="inlineStr"/>
       <c r="L67" s="3" t="inlineStr"/>
       <c r="M67" s="3" t="inlineStr"/>
       <c r="N67" s="3" t="inlineStr">
@@ -4142,17 +4192,18 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T PED</t>
+          <t>Doenca Avancada</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>RH (Nivel Central)</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Contratação de TMG para as paragens únicas de pediatria</t>
+          <t>Realização de visitas de monitoria no âmbito dos serviços vitais oferecidos aos utentes com DAH</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4162,17 +4213,17 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Melhorar o atendimento pediátrico</t>
+          <t>Garantir a qualidade dos serviços prestados</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Recursos financeiros para recrutamento e treinamento</t>
+          <t>Equipe de monitores e ferramentas de avaliação</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -4194,17 +4245,18 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T PED</t>
+          <t>Doenca Avancada</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>RH (Nivel Central)</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Assessora para área de HIV Pediatrico e do Adolescente</t>
+          <t>Apoiar a implementação ou expansão de tratamento de Sarcoma de Kaposi  (pequenas reabilitações, aquisição de cabines de manejo de citostáticos e de outros equipamentos para apetrechamento das salas de tratamento)</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -4214,17 +4266,17 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Fortalecer a abordagem pediátrica</t>
+          <t>Melhorar o tratamento disponível</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>Recursos humanos qualificados e materiais de apoio</t>
+          <t>Materiais e recursos para expansão de serviços</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr"/>
@@ -4246,7 +4298,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T PED</t>
+          <t>Doenca Avancada</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4257,7 +4309,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Expandir e monitorar a implementação das intervenções das mães mentoras para as crianças dos 0-10 anos em todas as unidades sanitárias TARV.</t>
+          <t>Assegurar a oferta de serviços ambulatórios completos de DAH na CRAM (alto maé) como Centro de referência de DAH</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4267,17 +4319,17 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Aumentar o suporte e adesão ao tratamento</t>
+          <t>Melhorar o acesso a serviços de saúde</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Centro de referência de DAH</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Recursos para capacitação e acompanhamento</t>
+          <t>Recursos humanos e materiais necessários para a implementação</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -4299,17 +4351,18 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T PED</t>
+          <t>Doenca Avancada</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Supplies/Insumos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reproduzir/Distribuir e alocar as ferramentas de TARV pediátrico e do adolescente e jovem incluindo: materias de formação, algoritmos, job aids, tripticos e  album seriado com mensagens de C&amp;T de adolescentes e jovens , albuns seriados "conhecendo os ARVs pediátricos) </t>
+          <t xml:space="preserve">Fornecer apoio técnico na componente TB/HIV a nível nacional, incluindo a implementação do pacote de doença avançada na paragem única, implementação faseada de Raio-X digital e CAD 4) apoiar na disseminação. </t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -4319,17 +4372,17 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
+          <t>Fortalecer a resposta ao HIV/TB</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>contratos de impressão</t>
+          <t>Recursos para capacitação e materiais de apoio</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr"/>
@@ -4351,17 +4404,18 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>C&amp;T PED</t>
+          <t>Doenca Avancada</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Realizar actualizações e refrescamentos nas normas de HIV para crianças e adolescentes</t>
+          <t>Capacitação para a implementação ou expansão de tratamento de Sarcoma de Kaposi  (formações)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4371,7 +4425,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a adesão e compreensão das normas</t>
+          <t>Aumentar a capacidade de resposta ao tratamento</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -4381,7 +4435,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Materiais de formação e recursos humanos</t>
+          <t>Materiais de formação e recursos humanos para capacitação</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -4403,17 +4457,18 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>C&amp;T PED</t>
+          <t>Doenca Avancada</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Realizar a conversão do pacote de HIV Pediátrico e do adolesente na plataforma Telesaúde</t>
+          <t>Fortalecer o rastreio de lesões pré-cancerosas do colo do utero entre MVHIV (CACUM )</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -4423,17 +4478,17 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>disponibilizar o pacote no plataforma telesaude</t>
+          <t>Melhorar a detecção precoce de câncer cervical</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>equipamento de gravação, tempo, plataform de telesaude</t>
+          <t>Materiais de rastreio e formação de pessoal</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr"/>
@@ -4455,18 +4510,17 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Doenca Avancada</t>
+          <t>Laboratório</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Testes DAH</t>
+          <t>Reuniões</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Medicamentos/
-Insumos</t>
+          <t xml:space="preserve">Intervenções no âmbito da resposta a resistencia aos Antiretrovirais de HIV </t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4476,42 +4530,24 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a detecção precoce de doenças avançadas</t>
+          <t>Melhorar a resposta à resistência</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Equipamentos para testes e formação de pessoal</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>158.532</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>264541 novos inicios e 175826 reinicios</t>
-        </is>
-      </c>
+          <t>Recursos para reuniões e formadores</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_73.html</t>
@@ -4526,18 +4562,17 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Doenca Avancada</t>
+          <t>Laboratório</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Tratamento Meningite</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Medicamentos/
-Insumos</t>
+          <t xml:space="preserve">Treinos sobre testagem de CD4 de diferentes plataformas </t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -4547,7 +4582,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Garantir tratamento eficaz para meningite</t>
+          <t>Aumentar a capacidade de testagem</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -4557,24 +4592,12 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>Estoque adequado de medicamentos e insumos</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>158.532</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
+          <t>Materiais de formação e equipamentos para treinamento</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="3" t="inlineStr"/>
       <c r="L75" s="3" t="inlineStr"/>
       <c r="M75" s="3" t="inlineStr"/>
       <c r="N75" s="3" t="inlineStr">
@@ -4591,18 +4614,18 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Doenca Avancada</t>
+          <t>Laboratório</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Tratamento Sarcoma Kaposi</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Medicamentos/
-Insumos</t>
+          <t xml:space="preserve">Fortalecer a monitoria de CV de HIV com recurso ao plasma. </t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4612,7 +4635,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Aumentar a adesão ao tratamento de Sarcoma Kaposi</t>
+          <t>Aumentar a eficácia da monitoria</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4622,24 +4645,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Recursos para aquisição de medicamentos</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>158.532</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>15.2%</t>
-        </is>
-      </c>
+          <t>Equipamentos para monitoramento e recursos humanos</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
@@ -4656,7 +4667,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Doenca Avancada</t>
+          <t>Laboratório</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -4667,7 +4678,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Capacitação de provedores no âmbito do seguimento de utentes com DAH</t>
+          <t>Integrar o m-PIMA para carga viral e PCR nas brigadas e clínicas móveis, visando populações vulneráveis e contextos de emergência.</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -4677,7 +4688,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade do acompanhamento</t>
+          <t>Melhorar o diagnóstico em populações vulneráveis</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -4687,7 +4698,7 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>Recursos para formação e capacitação de profissionais</t>
+          <t>Equipamentos m-PIMA e formação de pessoal</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr"/>
@@ -4709,7 +4720,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Doenca Avancada</t>
+          <t>Laboratório</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4720,7 +4731,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Realização de visitas de monitoria no âmbito dos serviços vitais oferecidos aos utentes com DAH</t>
+          <t xml:space="preserve">Avaliação de melhoria de qualidade de testagem rápida de HIV, Sífilis e Hepatite </t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4730,7 +4741,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Garantir a qualidade dos serviços prestados</t>
+          <t>Garantir a qualidade das testagens</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -4740,7 +4751,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Equipe de monitores e ferramentas de avaliação</t>
+          <t>Materiais de avaliação e recursos humanos</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4762,18 +4773,18 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Doenca Avancada</t>
+          <t>Laboratório</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t xml:space="preserve">
+Supplies/Insumos</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Apoiar a implementação ou expansão de tratamento de Sarcoma de Kaposi  (pequenas reabilitações, aquisição de cabines de manejo de citostáticos e de outros equipamentos para apetrechamento das salas de tratamento)</t>
+          <t xml:space="preserve">Desenvolvimento e Reprodução de material de apoio para HIVDR, Algoritmos laboratoriais, e livros de resgisto para CIQ  </t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -4783,17 +4794,17 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Melhorar o tratamento disponível</t>
+          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>Materiais e recursos para expansão de serviços</t>
+          <t>contratos de impressão</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr"/>
@@ -4815,7 +4826,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Doenca Avancada</t>
+          <t>Laboratório</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4826,7 +4837,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Assegurar a oferta de serviços ambulatórios completos de DAH na CRAM (alto maé) como Centro de referência de DAH</t>
+          <t>Assegurar a disponibilidade contínua de painéis de proficiência para a testagem em todos os níveis do sistema de saúde.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4836,17 +4847,17 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Melhorar o acesso a serviços de saúde</t>
+          <t>Melhorar a precisão dos testes</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Centro de referência de DAH</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Recursos humanos e materiais necessários para a implementação</t>
+          <t>Recursos para aquisição de painéis de proficiência</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4868,7 +4879,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Doenca Avancada</t>
+          <t>Laboratório</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -4879,7 +4890,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fornecer apoio técnico na componente TB/HIV a nível nacional, incluindo a implementação do pacote de doença avançada na paragem única, implementação faseada de Raio-X digital e CAD 4) apoiar na disseminação. </t>
+          <t>Expandir o uso de m-PIMA e do GeneXpert para a monitoria da Carga Viral e DPI</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -4889,17 +4900,17 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Fortalecer a resposta ao HIV/TB</t>
+          <t>Aumentar a capacidade de monitoramento</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>Recursos para capacitação e materiais de apoio</t>
+          <t>Equipamentos e formação para uso de m-PIMA e GeneXpert</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr"/>
@@ -4921,7 +4932,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Doenca Avancada</t>
+          <t>Laboratório</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4932,7 +4943,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Capacitação para a implementação ou expansão de tratamento de Sarcoma de Kaposi  (formações)</t>
+          <t>Implementar a revisão de casos para todos pacientes com CV acima de 50 e 1000c/ml com todos provedores antes de apresentar ao comite TARV</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4942,7 +4953,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Aumentar a capacidade de resposta ao tratamento</t>
+          <t>Aumentar a eficácia do tratamento</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4952,7 +4963,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Materiais de formação e recursos humanos para capacitação</t>
+          <t>Recursos humanos e protocolos de revisão</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4974,7 +4985,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Doenca Avancada</t>
+          <t>Laboratório</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -4985,7 +4996,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Fortalecer o rastreio de lesões pré-cancerosas do colo do utero entre MVHIV (CACUM )</t>
+          <t>Verificação de novos lotes de testes rápidos antes da distribuição no SNS</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -4995,17 +5006,17 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a detecção precoce de câncer cervical</t>
+          <t>Garantir a qualidade dos testes</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>Materiais de rastreio e formação de pessoal</t>
+          <t>Materiais para verificação e recursos humanos</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr"/>
@@ -5027,17 +5038,18 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Laboratório</t>
+          <t>Logística/ Aquisição</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Reuniões</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intervenções no âmbito da resposta a resistencia aos Antiretrovirais de HIV </t>
+          <t>Realizar a quantificação anual de ARVs, TDRs de HIV, autotestes, insumos de redução de danos, kits de carga viral e TPT, bem como actualizar os planos de aprovisionamento.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5047,17 +5059,17 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a resposta à resistência</t>
+          <t>Garantir o abastecimento contínuo de insumos</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Recursos para reuniões e formadores</t>
+          <t>Recursos para quantificação e logística</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -5079,7 +5091,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Laboratório</t>
+          <t>Logística/ Aquisição</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -5089,7 +5101,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Treinos sobre testagem de CD4 de diferentes plataformas </t>
+          <t>Realizar supervisões de farmácia com enfoque na avaliação da qualidade dos dados.</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -5099,7 +5111,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a capacidade de testagem</t>
+          <t>Melhorar a qualidade dos dados de farmácia</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -5109,7 +5121,7 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>Materiais de formação e equipamentos para treinamento</t>
+          <t>Recursos humanos qualificados e materiais de apoio</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr"/>
@@ -5131,18 +5143,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Laboratório</t>
+          <t>Logística/ Aquisição</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Supplies/Insumos</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fortalecer a monitoria de CV de HIV com recurso ao plasma. </t>
+          <t>Adquirir medicamentos para TARV, PTV, Testes Rápidos de HIV, Carga viral de HIV e DPI, PrEP, TPT e autotestes.</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5152,17 +5163,17 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Aumentar a eficácia da monitoria</t>
+          <t>Garantir a disponibilidade de medicamentos</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Equipamentos para monitoramento e recursos humanos</t>
+          <t>Recursos financeiros para aquisição de medicamentos</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
@@ -5184,7 +5195,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Laboratório</t>
+          <t>Logística/ Aquisição</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -5195,7 +5206,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Integrar o m-PIMA para carga viral e PCR nas brigadas e clínicas móveis, visando populações vulneráveis e contextos de emergência.</t>
+          <t>Assegurar o transporte de medicamentos, através da terceirização e da frota da CMAM, a todos os níveis.</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -5205,17 +5216,17 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Melhorar o diagnóstico em populações vulneráveis</t>
+          <t>Garantir a entrega pontual de insumos</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>Equipamentos m-PIMA e formação de pessoal</t>
+          <t>Logística de transporte e recursos humanos</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr"/>
@@ -5237,18 +5248,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Laboratório</t>
+          <t>Logística/ Aquisição</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avaliação de melhoria de qualidade de testagem rápida de HIV, Sífilis e Hepatite </t>
+          <t>Actualização do manual de procedimentos de gestão de  medicamentos e artigos médicos integrados no programa de HIV, abrangendo TARV adulto e pediátrico, PrEP, PTV, testagem e outras intervenções associadas.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5258,7 +5268,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Garantir a qualidade das testagens</t>
+          <t>Melhorar a gestão de medicamentos</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -5268,7 +5278,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Materiais de avaliação e recursos humanos</t>
+          <t>Materiais de formação e recursos humanos</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -5290,18 +5300,17 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Laboratório</t>
+          <t>Logística/ Aquisição</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Supplies/Insumos</t>
+          <t>Supplies/Insumos</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desenvolvimento e Reprodução de material de apoio para HIVDR, Algoritmos laboratoriais, e livros de resgisto para CIQ  </t>
+          <t xml:space="preserve">Adquirir Medicamentos para ITS/IOS, DNT (Cotrimoxazol, Penicilina Benatinica...) </t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -5311,17 +5320,17 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
+          <t>Garantir a disponibilidade de medicamentos</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>contratos de impressão</t>
+          <t>Recursos financeiros para aquisição de insumos</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr"/>
@@ -5343,18 +5352,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Laboratório</t>
+          <t>M&amp;A e Sistemas</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Qualidade</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Assegurar a disponibilidade contínua de painéis de proficiência para a testagem em todos os níveis do sistema de saúde.</t>
+          <t>Avaliacao de Qualidade de Dados</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5364,7 +5372,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a precisão dos testes</t>
+          <t>Melhorar a qualidade dos dados coletados</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -5374,14 +5382,32 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Recursos para aquisição de painéis de proficiência</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>Recursos humanos e ferramentas para avaliação</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>&lt;2015</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>3507.042253521127</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t># alcancado sao Unidade Santiarias</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_89.html</t>
@@ -5396,18 +5422,17 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Laboratório</t>
+          <t>M&amp;A e Sistemas</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Expandir o uso de m-PIMA e do GeneXpert para a monitoria da Carga Viral e DPI</t>
+          <t>Apoio técnico e logistico para realização de formações em sala assim como em serviço</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -5417,7 +5442,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a capacidade de monitoramento</t>
+          <t>Garantir a continuidade dos serviços de saúde</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -5427,10 +5452,14 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>Equipamentos e formação para uso de m-PIMA e GeneXpert</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr"/>
+          <t>Recursos financeiros e logísticos</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
       <c r="J91" s="3" t="inlineStr"/>
       <c r="K91" s="3" t="inlineStr"/>
       <c r="L91" s="3" t="inlineStr"/>
@@ -5449,18 +5478,18 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Laboratório</t>
+          <t>M&amp;A e Sistemas</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Supplies</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Implementar a revisão de casos para todos pacientes com CV acima de 50 e 1000c/ml com todos provedores antes de apresentar ao comite TARV</t>
+          <t xml:space="preserve"> ∙ Aquisição e alocação de material de escritório e mobiliário para as provincias;
+Apoio em comunicação/internet para os pontos focais de estatística, NEDs e Direcção  Municipal de Saúde (M&amp;A) e/ou Apoio em comunicação/internet para as US's para implementação de sistemas</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5470,7 +5499,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Aumentar a eficácia do tratamento</t>
+          <t>Aumentar a conscientização sobre o HIV e PrEP</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -5480,10 +5509,14 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Recursos humanos e protocolos de revisão</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr"/>
+          <t>Materiais de formação e recursos humanos</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
@@ -5502,18 +5535,17 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Laboratório</t>
+          <t>M&amp;A e Sistemas</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>RH (Nivel Central)</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Verificação de novos lotes de testes rápidos antes da distribuição no SNS</t>
+          <t>Avaliacão da implementacão do 2.º Plano de Aceleração da Resposta ao HIV e SIDA e desenvolvimento do 3.º Plano de Aceleração da Resposta ao HIV e SIDA</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -5523,7 +5555,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Garantir a qualidade dos testes</t>
+          <t>Melhorar a resposta ao HIV/SIDA</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -5533,7 +5565,7 @@
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>Materiais para verificação e recursos humanos</t>
+          <t>Recursos para avaliação e monitoramento</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr"/>
@@ -5555,18 +5587,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Logística/ Aquisição</t>
+          <t>M&amp;A e Sistemas</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Realizar a quantificação anual de ARVs, TDRs de HIV, autotestes, insumos de redução de danos, kits de carga viral e TPT, bem como actualizar os planos de aprovisionamento.</t>
+          <t>Realizar oficinas anuais de informação estratégica</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5576,17 +5607,17 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Garantir o abastecimento contínuo de insumos</t>
+          <t>Fortalecer a capacidade de resposta estratégia</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Recursos para quantificação e logística</t>
+          <t>Materiais de formação e logística para oficinas</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -5608,7 +5639,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Logística/ Aquisição</t>
+          <t>M&amp;A e Sistemas</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -5618,7 +5649,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Realizar supervisões de farmácia com enfoque na avaliação da qualidade dos dados.</t>
+          <t>Conversão do procedimento operacional padrão de Avaliação da Qualidade dos Dados para a plataforma Telessaúde</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -5628,17 +5659,17 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade dos dados de farmácia</t>
+          <t>disponibilizar o pacote no plataforma telesaude</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>Recursos humanos qualificados e materiais de apoio</t>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr"/>
@@ -5660,17 +5691,18 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Logística/ Aquisição</t>
+          <t>M&amp;A e Sistemas</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Supplies/Insumos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Adquirir medicamentos para TARV, PTV, Testes Rápidos de HIV, Carga viral de HIV e DPI, PrEP, TPT e autotestes.</t>
+          <t>Realizar Rondas Anuais de Avaliação da Qualidade dos Dados</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5680,7 +5712,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Garantir a disponibilidade de medicamentos</t>
+          <t>Melhorar a qualidade dos dados coletados</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -5690,7 +5722,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Recursos financeiros para aquisição de medicamentos</t>
+          <t>Recursos humanos e ferramentas para avaliação</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
@@ -5712,7 +5744,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Logística/ Aquisição</t>
+          <t>M&amp;A e Sistemas</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -5723,7 +5755,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Assegurar o transporte de medicamentos, através da terceirização e da frota da CMAM, a todos os níveis.</t>
+          <t>Realizar visitas de apoio técnico no âmbito da melhoria da qualidade de dados</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -5733,17 +5765,17 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Garantir a entrega pontual de insumos</t>
+          <t>Fortalecer a qualidade dos dados</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>Logística de transporte e recursos humanos</t>
+          <t>Recursos para visitas e apoio técnico</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr"/>
@@ -5765,17 +5797,18 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Logística/ Aquisição</t>
+          <t>M&amp;A e Sistemas</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Actualização do manual de procedimentos de gestão de  medicamentos e artigos médicos integrados no programa de HIV, abrangendo TARV adulto e pediátrico, PrEP, PTV, testagem e outras intervenções associadas.</t>
+          <t>Desenvolvimento e manutenção de sistemas de visualização e partilha de dados programáticos (Dashboards)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5785,17 +5818,17 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a gestão de medicamentos</t>
+          <t>Melhorar a transparência e uso dos dados</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Materiais de formação e recursos humanos</t>
+          <t>Recursos tecnológicos e humanos para desenvolvimento</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
@@ -5817,17 +5850,18 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Logística/ Aquisição</t>
+          <t>M&amp;A e Sistemas</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Supplies/Insumos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adquirir Medicamentos para ITS/IOS, DNT (Cotrimoxazol, Penicilina Benatinica...) </t>
+          <t>Desenvolvimento de novos instrumentos do SIS para o Programa de HIV</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -5837,7 +5871,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Garantir a disponibilidade de medicamentos</t>
+          <t>Melhorar a eficácia do sistema de informação</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -5847,7 +5881,7 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>Recursos financeiros para aquisição de insumos</t>
+          <t>Recursos técnicos e humanos para desenvolvimento</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr"/>
@@ -5874,12 +5908,13 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Qualidade</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Avaliacao de Qualidade de Dados</t>
+          <t>Reprodução dos instrumentos do SIS para o Programa de HIV</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5889,42 +5924,24 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade dos dados coletados</t>
+          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Recursos humanos e ferramentas para avaliação</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>&lt;2015</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>3507.042253521127</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t># alcancado sao Unidade Santiarias</t>
-        </is>
-      </c>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_99.html</t>
@@ -5944,15 +5961,12 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>RH</t>
+          <t>Supplies/Insumos</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>▪Nacional: 1 assessor de M&amp;A, Gestor de M&amp;A (MISAU)
-▪Provincial: Gestor de M&amp;A (1 MC / 1 GZ), Assessor de M&amp;A na SPS/DPS (1 MC / 1 GZ)
-▪Distritos (MC/GZ): Oficiais de M&amp;A
-▪US (MC/GZ): Alocação de oficiais de dados/digitadores/Assistentes de dados</t>
+          <t>Aquisição de equipamento informático e material de escritório</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -5962,17 +5976,20 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade dos dados coletados</t>
-        </is>
-      </c>
-      <c r="G101" s="3" t="inlineStr"/>
-      <c r="H101" s="3" t="inlineStr"/>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
+          <t>Garantir a operacionalidade das unidades de saúde</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>Recursos financeiros para aquisição de equipamentos</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr"/>
       <c r="J101" s="3" t="inlineStr"/>
       <c r="K101" s="3" t="inlineStr"/>
       <c r="L101" s="3" t="inlineStr"/>
@@ -5996,32 +6013,31 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>RH (Nivel Central)</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Apoio técnico e logistico para realização de formações em sala assim como em serviço</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
+          <t>Assessores da area de M&amp;A para o MISAU (central, provincial)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade dos dados coletados</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
+          <t>Fortalecer a capacidade de gestão</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos qualificados e materiais de apoio</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
@@ -6045,14 +6061,12 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Supplies</t>
+          <t>Supplies/Insumos</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ∙ Aquisição e alocação de material de escritório e mobiliário para as 2 provincias;
- ∙ Maputo Cidade: Apoio em comunicação/internet para os pontos focais de estatística, NEDs e Direcção  Municipal de Saúde (M&amp;A);
- ∙ Gaza: Apoio em comunicação/internet para as US's para implementação de sistemas</t>
+          <t>Aquisição de Licenças de aplicativos (Zoom, Antivirus, Power BI e microsoft office).</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
@@ -6062,17 +6076,20 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade dos dados coletados</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="inlineStr"/>
-      <c r="H103" s="3" t="inlineStr"/>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
+          <t>Melhorar a capacidade técnica</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>Recursos financeiros para aquisição de licenças</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr"/>
       <c r="J103" s="3" t="inlineStr"/>
       <c r="K103" s="3" t="inlineStr"/>
       <c r="L103" s="3" t="inlineStr"/>
@@ -6096,14 +6113,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Apoio Tecnico</t>
+          <t>Supplies/Insumos</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Apoio técnico ao Sistema Nacional de Saúde através de oficiais técnicos nas Unidades Sanitárias e distritos, gestores a nível provincial e assessores técnicos a nível central, garantindo apoio direto no terreno, coordenação programática e orientação estratégica para a melhoria da qualidade dos serviços: 
-∙ Realização de AQDs (apoio técnico e logística) para todos os níveis das provincias apoiadas
-∙ Apoio na implementação e expansão de sistemas electrónicos</t>
+          <t>Custos de comunicação (internet, telefones)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -6113,17 +6128,20 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade dos dados coletados</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
+          <t>Melhorar a comunicação entre unidades</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Recursos financeiros para serviços de comunicação</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr"/>
@@ -6142,28 +6160,17 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>M&amp;A e Sistemas</t>
+          <t>Melhoria de Qualidade</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
+          <t>Qualidade</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Monitoria semanal de indicadores chave
-2. Digitacao de dados no EPTS
-3. Triangulacao semanal, mensal e trimestral
-4. Auditoria do ePTS: completude
-5. Auditorias internas e do MISAU
-6. Implementacao do modulo de CCR (piloto)
-7. Analise semanal, mensal, trimestral de dados
-8. Aquisicao e distribuicao de telemoveis para chamadas preventivas e de reintegracao
-9. Reporte ao PEPFAR e MISAU: recontagem dos dados manuais
-10. Dashbaords visualizacao de dados
-11. Monitoria das actividaes dos digitadores
-12. Impressão, reprodução e distribuicao dos diferentes materiais de registo </t>
+          <t>Implementação dos Ciclos PDSA</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
@@ -6173,29 +6180,39 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade dos dados coletados</t>
-        </is>
-      </c>
-      <c r="G105" s="3" t="inlineStr"/>
-      <c r="H105" s="3" t="inlineStr"/>
+          <t>Melhorar a qualidade dos serviços de saúde</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais para implementação</t>
+        </is>
+      </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>Desde o inicio do Projecto em 2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>Todos os pacientes elegiveis 
-Provedores das US
-Sistemas</t>
+          <t>2.032.370</t>
         </is>
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>Todas as US AJUDA (149) Manica (51), Niassa(18), Sofala (47) e Tete (33)</t>
-        </is>
-      </c>
-      <c r="L105" s="3" t="inlineStr"/>
+          <t>91.0%</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>0.1351748107687824</t>
+        </is>
+      </c>
       <c r="M105" s="3" t="inlineStr"/>
       <c r="N105" s="3" t="inlineStr">
         <is>
@@ -6211,17 +6228,18 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A e Sistemas</t>
+          <t>Melhoria de Qualidade</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>RH (Nivel Central)</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Avaliacão da implementacão do 2.º Plano de Aceleração da Resposta ao HIV e SIDA e desenvolvimento do 3.º Plano de Aceleração da Resposta ao HIV e SIDA</t>
+          <t>Estratégia de Coaching (conversão para a plataforma de Telessaúde, incluíndo integração de um pacote simplificado na capacitação de Mentores)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -6231,7 +6249,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a resposta ao HIV/SIDA</t>
+          <t>disponibilizar o pacote no plataforma telesaude</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -6241,7 +6259,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Recursos para avaliação e monitoramento</t>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
@@ -6263,27 +6281,25 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>M&amp;A e Sistemas</t>
+          <t>Melhoria de Qualidade</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>RH (Nivel Central)</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Realizar oficinas anuais de informação estratégica</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
+          <t xml:space="preserve">
+Assessores da área de MQ para o MISAU
+</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Fortalecer a capacidade de resposta estratégia</t>
+          <t>Fortalecer a abordagem da melhoria da qualidade</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -6293,7 +6309,7 @@
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>Materiais de formação e logística para oficinas</t>
+          <t>Recursos humanos qualificados e capacitação</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr"/>
@@ -6315,27 +6331,23 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A e Sistemas</t>
+          <t>Melhoria de Qualidade</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>RH (Nivel Central)</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Conversão do procedimento operacional padrão de Avaliação da Qualidade dos Dados para a plataforma Telessaúde</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
+          <t>Elaboração do Manual de Gestão do Program que inclui orientações sobre a oferta de serviços nas áreas do PNC ITS-HIV/SIDA</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>disponibilizar o pacote no plataforma telesaude</t>
+          <t>Padronizar a oferta de serviços</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -6345,7 +6357,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>equipamento de gravação, tempo, plataform de telesaude</t>
+          <t>Recursos humanos e materiais para elaboração</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -6367,7 +6379,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>M&amp;A e Sistemas</t>
+          <t>Melhoria de Qualidade</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -6378,27 +6390,23 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Realizar Rondas Anuais de Avaliação da Qualidade dos Dados</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
+          <t>Engajamento do utente na melhoria da qualidade assistencial</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade dos dados coletados</t>
+          <t>Aumentar a participação dos utentes na saúde</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>Recursos humanos e ferramentas para avaliação</t>
+          <t>Recursos para campanhas de sensibilização</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr"/>
@@ -6420,7 +6428,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A e Sistemas</t>
+          <t>Melhoria de Qualidade</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6431,17 +6439,13 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Realizar visitas de apoio técnico no âmbito da melhoria da qualidade de dados</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
+          <t>Implementação da ferramenta eletrónica de Mentoria</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Fortalecer a qualidade dos dados</t>
+          <t>Melhorar a supervisão e apoio técnico</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -6451,7 +6455,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Recursos para visitas e apoio técnico</t>
+          <t>Recursos tecnológicos e humanos para implementação</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -6473,7 +6477,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>M&amp;A e Sistemas</t>
+          <t>Melhoria de Qualidade</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -6484,14 +6488,10 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Desenvolvimento e manutenção de sistemas de visualização e partilha de dados programáticos (Dashboards)</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
+          <t>Implementação de MI em todas US com ciclos de MQHIV e SESP</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
           <t>Melhorar a transparência e uso dos dados</t>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A e Sistemas</t>
+          <t>Melhoria de Qualidade</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6537,27 +6537,23 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Desenvolvimento de novos instrumentos do SIS para o Programa de HIV</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Implementação dos ciclos de MQHIV </t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a eficácia do sistema de informação</t>
+          <t>Melhorar a qualidade dos serviços de saúde</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Recursos técnicos e humanos para desenvolvimento</t>
+          <t>Recursos humanos e materiais para implementação</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
@@ -6579,7 +6575,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>M&amp;A e Sistemas</t>
+          <t>Melhoria de Qualidade</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -6590,7 +6586,8 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Reprodução dos instrumentos do SIS para o Programa de HIV</t>
+          <t xml:space="preserve">
+Sessões de Mentoria (PrEP, ATS-APSS e Clínica) em todas US TARV</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
@@ -6600,17 +6597,17 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
+          <t>Aumentar a capacitação dos profissionais de saúde</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>contratos de impressão</t>
+          <t>Materiais de formação e recursos humanos</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr"/>
@@ -6632,17 +6629,18 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A e Sistemas</t>
+          <t>Melhoria de Qualidade</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Supplies/Insumos</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Aquisição de equipamento informático e material de escritório</t>
+          <t>Assegurar a disponibilidade de dados de MI num dashboard nacional</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6652,7 +6650,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Garantir a operacionalidade das unidades de saúde</t>
+          <t>Melhorar a visibilidade da informação</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -6662,7 +6660,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Recursos financeiros para aquisição de equipamentos</t>
+          <t>Recursos tecnológicos e humanos para desenvolvimento</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
@@ -6684,23 +6682,28 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>M&amp;A e Sistemas</t>
+          <t>Melhoria de Qualidade</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>RH (Nivel Central)</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Assessores da area de M&amp;A para o MISAU (central, provincial)</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr"/>
+          <t>Realizar a Reunião Provincial e Nacional de MQ HIV</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Fortalecer a capacidade de gestão</t>
+          <t>Coordenar esforços e compartilhar boas práticas</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -6710,7 +6713,7 @@
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>Recursos humanos qualificados e materiais de apoio</t>
+          <t>Recursos para logística e organização de eventos</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr"/>
@@ -6732,17 +6735,21 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A e Sistemas</t>
+          <t>Melhoria de Qualidade</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Supplies/Insumos</t>
+          <t xml:space="preserve">
+Supplies/Insumos</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Aquisição de Licenças de aplicativos (Zoom, Antivirus, Power BI e microsoft office).</t>
+          <t>Reprodução de instrumento de MQ HIV:
+- Tabelas de Mentorias (PrEP, ATS-APSS e Clínica)
+- Guião dos encontros semanais do CGSC da US
+- Ficha de Monitoria de Implementação do Plano de Acção de MQ e Planos de Acção de MQ</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6752,17 +6759,17 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a capacidade técnica</t>
+          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>nacional</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Recursos financeiros para aquisição de licenças</t>
+          <t>contratos de impressão</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
@@ -6784,17 +6791,18 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>M&amp;A e Sistemas</t>
+          <t>Prevenção</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Supplies/Insumos</t>
+          <t>PREP Vaginal</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Custos de comunicação (internet, telefones)</t>
+          <t>Medicamentos/
+Insumos</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
@@ -6804,24 +6812,42 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a comunicação entre unidades</t>
+          <t>Aumentar a prevenção do HIV</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>Recursos financeiros para serviços de comunicação</t>
-        </is>
-      </c>
-      <c r="I117" s="3" t="inlineStr"/>
-      <c r="J117" s="3" t="inlineStr"/>
-      <c r="K117" s="3" t="inlineStr"/>
-      <c r="L117" s="3" t="inlineStr"/>
-      <c r="M117" s="3" t="inlineStr"/>
+          <t>Medicamentos e insumos para PrEP</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>Nao iniciou em 2024</t>
+        </is>
+      </c>
       <c r="N117" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_116.html</t>
@@ -6836,17 +6862,18 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Melhoria de Qualidade</t>
+          <t>Prevenção</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Qualidade</t>
+          <t>PREP Injectavel</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Implementação dos Ciclos PDSA</t>
+          <t>Medicamentos/
+Insumos</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6856,7 +6883,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade dos serviços de saúde</t>
+          <t>Aumentar a prevenção do HIV</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -6866,30 +6893,34 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Recursos humanos e materiais para implementação</t>
+          <t>Medicamentos e insumos para PrEP</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2.032.370</t>
+          <t>3.185.533</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>0.1351748107687824</t>
-        </is>
-      </c>
-      <c r="M118" s="2" t="inlineStr"/>
+          <t>3715.393500000001</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>36 RAMJ 15-24 em seguimento no ano 2024, pois foi o inicio do piloto</t>
+        </is>
+      </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_117.html</t>
@@ -6904,18 +6935,18 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Melhoria de Qualidade</t>
+          <t>Prevenção</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Lubrificante</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Estratégia de Coaching (conversão para a plataforma de Telessaúde, incluíndo integração de um pacote simplificado na capacitação de Mentores)</t>
+          <t>Medicamentos/
+Insumos</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
@@ -6925,24 +6956,40 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>disponibilizar o pacote no plataforma telesaude</t>
+          <t>Reduzir o risco de transmissão do HIV</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>equipamento de gravação, tempo, plataform de telesaude</t>
-        </is>
-      </c>
-      <c r="I119" s="3" t="inlineStr"/>
-      <c r="J119" s="3" t="inlineStr"/>
-      <c r="K119" s="3" t="inlineStr"/>
-      <c r="L119" s="3" t="inlineStr"/>
-      <c r="M119" s="3" t="inlineStr"/>
+          <t>Recursos para aquisição de lubrificantes</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>&lt;2015</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K119" s="3" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>0.061678806032677</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>dados de distribucao, Hom + Mulh 15-49</t>
+        </is>
+      </c>
       <c r="N119" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_118.html</t>
@@ -6957,42 +7004,63 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Melhoria de Qualidade</t>
+          <t>Prevenção</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>RH (Nivel Central)</t>
+          <t>ITS</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Assessores da área de MQ para o MISAU
-</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr"/>
+          <t>Medicamentos/
+Insumos</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Fortalecer a abordagem da melhoria da qualidade</t>
+          <t>Tratar e prevenir infecções</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Recursos humanos qualificados e capacitação</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-      <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="2" t="inlineStr"/>
-      <c r="M120" s="2" t="inlineStr"/>
+          <t>Medicamentos e insumos para ITS</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>2021 (novo versao)</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>todos utentes na US</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>0.6309392820691827</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>por causa de cobertura de livro de ITS não é possivel calcular um pop. Eligivel</t>
+        </is>
+      </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_119.html</t>
@@ -7007,40 +7075,65 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Melhoria de Qualidade</t>
+          <t>Prevenção</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>RH (Nivel Central)</t>
+          <t>Femininos</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Elaboração do Manual de Gestão do Program que inclui orientações sobre a oferta de serviços nas áreas do PNC ITS-HIV/SIDA</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr"/>
+          <t>Medicamentos/
+Insumos</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Padronizar a oferta de serviços</t>
+          <t>Aumentar a proteção contra o HIV</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>Recursos humanos e materiais para elaboração</t>
-        </is>
-      </c>
-      <c r="I121" s="3" t="inlineStr"/>
-      <c r="J121" s="3" t="inlineStr"/>
-      <c r="K121" s="3" t="inlineStr"/>
-      <c r="L121" s="3" t="inlineStr"/>
-      <c r="M121" s="3" t="inlineStr"/>
+          <t>Recursos para aquisição de preservativos</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>&lt;2015</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>8.159.149</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>68.6%</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>0.4605463310123192</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>dados de distribucao Mulher 15 - 49 anos</t>
+        </is>
+      </c>
       <c r="N121" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_120.html</t>
@@ -7055,24 +7148,28 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Melhoria de Qualidade</t>
+          <t>Prevenção</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>PREP Oral</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Engajamento do utente na melhoria da qualidade assistencial</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr"/>
+          <t>Medicamentos/
+Insumos</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Aumentar a participação dos utentes na saúde</t>
+          <t>Aumentar a prevenção do HIV</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -7082,14 +7179,34 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Recursos para campanhas de sensibilização</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-      <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="2" t="inlineStr"/>
-      <c r="M122" s="2" t="inlineStr"/>
+          <t>Medicamentos e insumos para PrEP Oral</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>30.767.054</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>21.33839519575633</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>Novo inicios a PrEP para o ano 2024</t>
+        </is>
+      </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_121.html</t>
@@ -7104,24 +7221,28 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Melhoria de Qualidade</t>
+          <t>Prevenção</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Implementação da ferramenta eletrónica de Mentoria</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr"/>
+          <t>Medicamentos/
+Insumos</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a supervisão e apoio técnico</t>
+          <t>Aumentar a proteção contra o HIV</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -7131,14 +7252,34 @@
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>Recursos tecnológicos e humanos para implementação</t>
-        </is>
-      </c>
-      <c r="I123" s="3" t="inlineStr"/>
-      <c r="J123" s="3" t="inlineStr"/>
-      <c r="K123" s="3" t="inlineStr"/>
-      <c r="L123" s="3" t="inlineStr"/>
-      <c r="M123" s="3" t="inlineStr"/>
+          <t>Recursos para aquisição e distribuição de preservativos</t>
+        </is>
+      </c>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>&lt;2015</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>7.388.905</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>21.810947630264565</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>0.04648415651820172</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>dados de distribucao Homen 15 - 49 anos</t>
+        </is>
+      </c>
       <c r="N123" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_122.html</t>
@@ -7153,37 +7294,44 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Melhoria de Qualidade</t>
+          <t>Prevenção</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Implementação de MI em todas US com ciclos de MQHIV e SESP</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr"/>
+          <t>Apoio tecnico e logistico em todos pacotes de formacao de prevencao a nivel de US, distrito e Provincia</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a transparência e uso dos dados</t>
+          <t>Aumentar a capacidade de resposta em prevenção</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Unidades de Saúde</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Recursos tecnológicos e humanos para desenvolvimento</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr"/>
+          <t>Materiais de formação e recursos humanos</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
@@ -7202,37 +7350,44 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Melhoria de Qualidade</t>
+          <t>Prevenção</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Supplies</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Implementação dos ciclos de MQHIV </t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr"/>
+          <t>Alocacao de consumiveis de testagem (luvas, alccol, algodao) mobiliario (mesas de testagem, cadeiras de utentes)</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a qualidade dos serviços de saúde</t>
+          <t>Garantir a disponibilidade de materiais necessários</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Unidades de Saúde</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>Recursos humanos e materiais para implementação</t>
-        </is>
-      </c>
-      <c r="I125" s="3" t="inlineStr"/>
+          <t>Recursos financeiros e logísticos</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
       <c r="J125" s="3" t="inlineStr"/>
       <c r="K125" s="3" t="inlineStr"/>
       <c r="L125" s="3" t="inlineStr"/>
@@ -7251,19 +7406,17 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Melhoria de Qualidade</t>
+          <t>Prevenção</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Sessões de Mentoria (PrEP, ATS-APSS e Clínica) em todas US TARV</t>
+          <t>Capacitar Pessoal Leigo para Criação de Demanda para prevenção Combinada, incluindo PrEP injectavel</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7273,7 +7426,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Aumentar a capacitação dos profissionais de saúde</t>
+          <t>Aumentar a conscientização e utilização de PrEP</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -7283,7 +7436,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Materiais de formação e recursos humanos</t>
+          <t>Materiais de capacitação e recursos humanos</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
@@ -7305,7 +7458,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Melhoria de Qualidade</t>
+          <t>Prevenção</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -7316,7 +7469,7 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Assegurar a disponibilidade de dados de MI num dashboard nacional</t>
+          <t>Implementação e Expansão da PrEP (Oral e Injectável)</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
@@ -7326,17 +7479,17 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Melhorar a visibilidade da informação</t>
+          <t>Aumentar o acesso à PrEP</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>Recursos tecnológicos e humanos para desenvolvimento</t>
+          <t>Medicamentos e insumos para PrEP</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr"/>
@@ -7358,18 +7511,18 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Melhoria de Qualidade</t>
+          <t>Prevenção</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
+          <t>Intervenção
 (Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Realizar a Reunião Provincial e Nacional de MQ HIV</t>
+          <t>Realizar visitas de monitoria da implementação e expansão da PrEP (Oral e Injectável)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7379,17 +7532,17 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Coordenar esforços e compartilhar boas práticas</t>
+          <t>Garantir a qualidade da implementação</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Recursos para logística e organização de eventos</t>
+          <t>Recursos humanos e materiais para monitoramento</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
@@ -7411,21 +7564,18 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Melhoria de Qualidade</t>
+          <t>Prevenção</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Supplies/Insumos</t>
+          <t>Intervenção
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Reprodução de instrumento de MQ HIV:
-- Tabelas de Mentorias (PrEP, ATS-APSS e Clínica)
-- Guião dos encontros semanais do CGSC da US
-- Ficha de Monitoria de Implementação do Plano de Acção de MQ e Planos de Acção de MQ</t>
+          <t>Criacao de Demanda para PrEP Oral</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
@@ -7435,17 +7585,17 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
+          <t>Aumentar a aceitação e uso da PrEP Oral</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>contratos de impressão</t>
+          <t>Recursos para campanhas de sensibilização</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr"/>
@@ -7472,590 +7622,553 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>PREP Vaginal</t>
+          <t>Intervenção
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Criacao de Demanda para PrEP Injectavel (LEN)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Aumentar a aceitação e uso da PrEP Injectável</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para campanhas de sensibilização</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_129.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>hiv_130</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Prevenção</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Supplies/Insumos</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Reprodução de material de IEC para PrEP</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr"/>
+      <c r="J131" s="3" t="inlineStr"/>
+      <c r="K131" s="3" t="inlineStr"/>
+      <c r="L131" s="3" t="inlineStr"/>
+      <c r="M131" s="3" t="inlineStr"/>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_130.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>hiv_131</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Prevenção</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Formações/Treinos</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Capacitação para implementação da PrEP Oral e Injectável</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Aumentar a capacidade dos profissionais de saúde</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Materiais de formação e recursos humanos</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_131.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>hiv_132</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Prevenção</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Reunião</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Reunião de monitoria das estratégias no âmbito da resposta ao primeiro 95 e fortalecimento da implementação da PrEP</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>Melhorar a coordenação e eficiência das estratégias</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>Recursos para a realização da reunião</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr"/>
+      <c r="K133" s="3" t="inlineStr"/>
+      <c r="L133" s="3" t="inlineStr"/>
+      <c r="M133" s="3" t="inlineStr"/>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_132.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>hiv_133</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>PTV (Eliminação Tripla)</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Carga Viral Hepatite B</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Medicamentos/
 Insumos</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>Aumentar a prevenção do HIV</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Melhorar a monitoria e tratamento da Hepatite B</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>Unidades Sanitarias</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>Medicamentos e insumos para PrEP</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K130" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L130" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M130" s="2" t="inlineStr">
-        <is>
-          <t>Nao iniciou em 2024</t>
-        </is>
-      </c>
-      <c r="N130" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_129.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>hiv_130</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>Prevenção</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>PREP Injectavel</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para tratamento</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>36.171</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>Carga Viral para VHB nao foi implmentado em 2024</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_133.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>hiv_134</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>PTV (Eliminação Tripla)</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>TDR Hepatite B</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>Medicamentos/
 Insumos</t>
         </is>
       </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t>Aumentar a prevenção do HIV</t>
-        </is>
-      </c>
-      <c r="G131" s="3" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>Melhorar o tratamento de Hepatite B</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>Unidades Sanitarias</t>
         </is>
       </c>
-      <c r="H131" s="3" t="inlineStr">
-        <is>
-          <t>Medicamentos e insumos para PrEP</t>
-        </is>
-      </c>
-      <c r="I131" s="3" t="inlineStr">
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para tratamento</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>3.185.533</t>
-        </is>
-      </c>
-      <c r="K131" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="L131" s="3" t="inlineStr">
-        <is>
-          <t>3715.393500000001</t>
-        </is>
-      </c>
-      <c r="M131" s="3" t="inlineStr">
-        <is>
-          <t>36 RAMJ 15-24 em seguimento no ano 2024, pois foi o inicio do piloto</t>
-        </is>
-      </c>
-      <c r="N131" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_130.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>hiv_131</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Prevenção</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Lubrificante</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>36.171</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>89.1%</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>14.55053042992741</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>Ainda foi um piloto ate o fim de 2024, em MC tinha 7,615, Nampula 18,706, Sofala 5,917</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_134.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>hiv_135</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>PTV (Eliminação Tripla)</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>TDR Sifilis</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Medicamentos/
 Insumos</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>Reduzir o risco de transmissão do HIV</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Reduzir a transmissão de sífilis</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>Unidades Sanitarias</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>Recursos para aquisição de lubrificantes</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>&lt;2015</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="e">
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para tratamento</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>&lt;2018</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Pessoas com sinais ou sintomas</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K132" s="2" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L132" s="2" t="inlineStr">
-        <is>
-          <t>0.061678806032677</t>
-        </is>
-      </c>
-      <c r="M132" s="2" t="inlineStr">
-        <is>
-          <t>dados de distribucao, Hom + Mulh 15-49</t>
-        </is>
-      </c>
-      <c r="N132" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_131.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>hiv_132</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>Prevenção</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>ITS</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>2.041635729911516</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>testados para Sifilis no livro de ITS</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_135.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>hiv_136</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>PTV (Eliminação Tripla)</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>ARVs PTV</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>Medicamentos/
 Insumos</t>
         </is>
       </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>Tratar e prevenir infecções</t>
-        </is>
-      </c>
-      <c r="G133" s="3" t="inlineStr">
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>Melhorar o tratamento e adesão ao tratamento de HIV</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
         <is>
           <t>Unidades Sanitarias</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
-        <is>
-          <t>Medicamentos e insumos para ITS</t>
-        </is>
-      </c>
-      <c r="I133" s="3" t="inlineStr">
-        <is>
-          <t>2021 (novo versao)</t>
-        </is>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>todos utentes na US</t>
-        </is>
-      </c>
-      <c r="K133" s="3" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="L133" s="3" t="inlineStr">
-        <is>
-          <t>0.6309392820691827</t>
-        </is>
-      </c>
-      <c r="M133" s="3" t="inlineStr">
-        <is>
-          <t>por causa de cobertura de livro de ITS não é possivel calcular um pop. Eligivel</t>
-        </is>
-      </c>
-      <c r="N133" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_132.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>hiv_133</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Prevenção</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Femininos</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para tratamento</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>&lt;2015</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>134.000</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>8.066636253214423</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>MG HIV+ na CPN</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_136.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>hiv_137</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>PTV (Eliminação Tripla)</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>DUO Sifilis e HIV</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Medicamentos/
 Insumos</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>Aumentar a proteção contra o HIV</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Aumentar a eficiência do tratamento</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>Unidades Sanitarias</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>Recursos para aquisição de preservativos</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>&lt;2015</t>
-        </is>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>8.159.149</t>
-        </is>
-      </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>68.6%</t>
-        </is>
-      </c>
-      <c r="L134" s="2" t="inlineStr">
-        <is>
-          <t>0.4605463310123192</t>
-        </is>
-      </c>
-      <c r="M134" s="2" t="inlineStr">
-        <is>
-          <t>dados de distribucao Mulher 15 - 49 anos</t>
-        </is>
-      </c>
-      <c r="N134" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_133.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>hiv_134</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>Prevenção</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>PREP Oral</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>Medicamentos/
-Insumos</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t>Aumentar a prevenção do HIV</t>
-        </is>
-      </c>
-      <c r="G135" s="3" t="inlineStr">
-        <is>
-          <t>Unidades Sanitarias</t>
-        </is>
-      </c>
-      <c r="H135" s="3" t="inlineStr">
-        <is>
-          <t>Medicamentos e insumos para PrEP Oral</t>
-        </is>
-      </c>
-      <c r="I135" s="3" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>30.767.054</t>
-        </is>
-      </c>
-      <c r="K135" s="3" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="L135" s="3" t="inlineStr">
-        <is>
-          <t>21.33839519575633</t>
-        </is>
-      </c>
-      <c r="M135" s="3" t="inlineStr">
-        <is>
-          <t>Novo inicios a PrEP para o ano 2024</t>
-        </is>
-      </c>
-      <c r="N135" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_134.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>hiv_135</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Prevenção</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Medicamentos/
-Insumos</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>Aumentar a proteção contra o HIV</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>Unidades Sanitarias</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>Recursos para aquisição e distribuição de preservativos</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
-        <is>
-          <t>&lt;2015</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>7.388.905</t>
-        </is>
-      </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>21.810947630264565</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="inlineStr">
-        <is>
-          <t>0.04648415651820172</t>
-        </is>
-      </c>
-      <c r="M136" s="2" t="inlineStr">
-        <is>
-          <t>dados de distribucao Homen 15 - 49 anos</t>
-        </is>
-      </c>
-      <c r="N136" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_135.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>hiv_136</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>Prevenção</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>RH</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>▪Nacional: 1 assessora de Prevenção
-▪Provincial: Gestor de Prevenção (MC 1, GZ 1), Gestor de ATS/APSS (1 MC/ 1 GZ)
-▪Distritos: Oficiais distritais de ATS/APSS
-▪US: Alocacao de conselheiros e gestores de caso</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t>Aumentar a proteção contra o HIV</t>
-        </is>
-      </c>
-      <c r="G137" s="3" t="inlineStr"/>
-      <c r="H137" s="3" t="inlineStr"/>
-      <c r="I137" s="3" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
-      <c r="J137" s="3" t="inlineStr"/>
-      <c r="K137" s="3" t="inlineStr"/>
-      <c r="L137" s="3" t="inlineStr"/>
-      <c r="M137" s="3" t="inlineStr"/>
-      <c r="N137" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_136.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>hiv_137</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>Prevenção</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Formações/Treinos</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Apoio tecnico e logistico em todos pacotes de formacao de prevencao a nivel de US, distrito e Provincia</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>Aumentar a proteção contra o HIV</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Medicamentos e insumos para tratamento</t>
+        </is>
+      </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
-      <c r="J138" s="2" t="inlineStr"/>
-      <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="2" t="inlineStr"/>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>2.111.754</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>99.0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>1.33270233448056</t>
+        </is>
+      </c>
       <c r="M138" s="2" t="inlineStr"/>
       <c r="N138" s="2" t="inlineStr">
         <is>
@@ -8071,17 +8184,17 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Prevenção</t>
+          <t>PTV (Eliminação Tripla)</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Supplies</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Alocacao de consumiveis de testagem (luvas, alccol, algodao) mobiliario (mesas de testagem, cadeiras de utentes)</t>
+          <t>Apoio técnico e logístico para a realização de formações em sala e em serviço a nivel Provincial, Distrital e da US</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
@@ -8091,15 +8204,22 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a proteção contra o HIV</t>
-        </is>
-      </c>
-      <c r="G139" s="3" t="inlineStr"/>
-      <c r="H139" s="3" t="inlineStr"/>
+          <t>Melhorar a qualidade do atendimento PTV</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>Materiais de formação e recursos humanos</t>
+        </is>
+      </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="J139" s="3" t="inlineStr"/>
@@ -8120,18 +8240,17 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Prevenção</t>
+          <t>PTV (Eliminação Tripla)</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Apoio Tecnico</t>
+          <t>Supplies</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Apoio técnico ao Sistema Nacional de Saúde através de oficiais técnicos nas Unidades Sanitárias e distritos, gestores a nível provincial e assessores técnicos a nível central, garantindo apoio direto no terreno, coordenação programática e orientação estratégica para a melhoria da qualidade dos serviços.</t>
+          <t>Alocacao de material escritorio, material medico cirurgico, instrumentos de registo e material IEC</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -8141,15 +8260,22 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Aumentar a proteção contra o HIV</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr"/>
+          <t>Melhorar a gestão e atendimento em saúde</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Unidades Sanitarias</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para aquisição de materiais</t>
+        </is>
+      </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr"/>
@@ -8170,20 +8296,17 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Prevenção</t>
+          <t>PTV (Eliminação Tripla)</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Apoio Tecnico</t>
+          <t>CACUM</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>1. Expansão da PrEP para todos os sites TARV 
-2. Chamadas lembrete antes da consulta (atribuição/aquisição de telefone e credito)
-5. Encontros de analise e discussão de dados nas US
-6. Provisão directa de serviços através dos TMG alocados pelo projecto</t>
+          <t xml:space="preserve">Apoio técnico ao Sistema Nacional de Saúde para a implementacao de abordagem de CACUM: 1.Compra de aparelhos de termoablacao para as provincia  e transporte de aparelho comprados com  fundos do Misau                                                                                                                                                                                                                                                                           5. Compra de aparelhos de Leep para as provincias                                                                                                                                                                                                                                                                                                        6. Aquisição de insumos (Acido acetico, lugol, hemogin, mangueiras, especulos, pincas, panelas de esterilizacao, )filtros de carvao, etc)para maquinas de LEEP e material medico cirurgico (Marqueza, gambiar), manutenção dos equipamentosetc.                                                                                                                                                                                                                                 7. Apoio na formacao de Termoabalaco e de Leep                                                                                                                                                                                                                                                                                         8. Fornecimento de credito e telemovel aos hospitais de referencia                                                                                                                                                                                                                                                      9. Fornecimento de subsidio de transporte a mulheres com lesao maior que 75% para o hospital de referencia                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        12. Geracao de lista de mulheres sem rastreio a mais de 1 ano, para referencia para rastreio        </t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
@@ -8193,27 +8316,32 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a proteção contra o HIV</t>
-        </is>
-      </c>
-      <c r="G141" s="3" t="inlineStr"/>
-      <c r="H141" s="3" t="inlineStr"/>
+          <t>Melhorar a coordenação e eficiência do sistema</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais para implementação</t>
+        </is>
+      </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021 com o piloto em Manica e depois expansão nacional </t>
+          <t>Sem Informação</t>
         </is>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>Provedores das portas de captação da PrEP e das PUs da PrEP
-Pontos focais provinciais, distritais e das US 
-Todas as US PrEP 
-População elegível para PrEP no geral incluindo MG/ML</t>
+          <t>Mulher Lactante  e pacientes HIV+                                                                                                                                                                                  ESMI</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
-          <t>US AJUDA PrEP (102) das províncias de Manica (37), Niassa (18), Sofala (23), Tete (24). Dados ate JAN 2026</t>
+          <t>Todas as US AJUDA (149) Manica (51), Niassa(18), Sofala (47) e Tete (33)</t>
         </is>
       </c>
       <c r="L141" s="3" t="inlineStr"/>
@@ -8232,22 +8360,18 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Prevenção</t>
+          <t>PTV (Eliminação Tripla)</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Comportamental</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1. Campanhas de comunicação
-2. Palestras
-3. Diálogos comunitários
-4. Contratacao de conselheiros efacilitadores de dialogos
-4. Spots radiofónicos nas rádios comunitárias
-5. Conversas nas rádios comunitários de diferentes temas com provedores de saude: adesão ao tratamento, CV, testagem, VBG, PrEP, PTV, etc.</t>
+          <t>Oferta do pacote de PTV do HIV, Sífilis e Hepatite B</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -8257,33 +8381,24 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Aumentar a proteção contra o HIV</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr"/>
-      <c r="I142" s="2" t="inlineStr">
-        <is>
-          <t>Desde o inicio do Projecto em 2019</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">População dos locais abrangidos </t>
-        </is>
-      </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>US AJUDA PrEP (102) das províncias de Manica (37), Niassa (18), Sofala (23), Tete (24). Dados ate JAN 2026</t>
-        </is>
-      </c>
+          <t>Aumentar a cobertura das intervenções de PTV</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Recursos humanos e materiais para implementação</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr"/>
-      <c r="M142" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Actividades suspensas emJ aneiro 2025 em alinhamento as orientações do "waiver" e do doador
-Mantem-se o apoio as intervenções dentro da US </t>
-        </is>
-      </c>
+      <c r="M142" s="2" t="inlineStr"/>
       <c r="N142" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_141.html</t>
@@ -8298,17 +8413,17 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Prevenção</t>
+          <t>PTV (Eliminação Tripla)</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Formações/Treinos</t>
+          <t>Reuniões</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Capacitar Pessoal Leigo para Criação de Demanda para prevenção Combinada, incluindo PrEP injectavel</t>
+          <t>Realização da oficina de trabalho, nacionail e provinciais, no âmbito da monitoria da implementação do Plano Nacional de Tripla Eliminação da Transmissão Vertical do HIV, Sífilis e Hepatite B 2026- 2030</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
@@ -8318,17 +8433,17 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a conscientização e utilização de PrEP</t>
+          <t>Melhorar a coordenação e implementação</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional e Provincial</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>Materiais de capacitação e recursos humanos</t>
+          <t>Recursos para logística e organização de reuniões</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr"/>
@@ -8350,18 +8465,17 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Prevenção</t>
+          <t>PTV (Eliminação Tripla)</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Implementação e Expansão da PrEP (Oral e Injectável)</t>
+          <t>Actualizações do pacote de PTV, incluíndo capacitações e conversão para a plataforma de telessáude</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -8371,17 +8485,17 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Aumentar o acesso à PrEP</t>
+          <t>disponibilizar o pacote no plataforma telesaude</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Medicamentos e insumos para PrEP</t>
+          <t>equipamento de gravação, tempo, plataform de telesaude</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
@@ -8403,18 +8517,18 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Prevenção</t>
+          <t>PTV (Eliminação Tripla)</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Intervenção
+          <t>Intervenção 
 (Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Realizar visitas de monitoria da implementação e expansão da PrEP (Oral e Injectável)</t>
+          <t>Supervisão integrada de PTV e SMI</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
@@ -8424,7 +8538,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Garantir a qualidade da implementação</t>
+          <t>Garantir a eliminação da transmissão vertical</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -8434,7 +8548,7 @@
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>Recursos humanos e materiais para monitoramento</t>
+          <t>Recursos humanos e materiais necessários</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr"/>
@@ -8456,18 +8570,18 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Prevenção</t>
+          <t>PTV (Eliminação Tripla)</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Intervenção
+          <t>Intervenção 
 (Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Criacao de Demanda para PrEP Oral</t>
+          <t>Avaliação do meio termo da implementação do Plano Nacional  de Tripla ETV do HIV, Sífilis e Hepatite B 2026- 2030</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -8477,17 +8591,17 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Aumentar a aceitação e uso da PrEP Oral</t>
+          <t>Monitorar o progresso e eficácia do plano</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Recursos para campanhas de sensibilização</t>
+          <t>Recursos humanos e materiais para avaliação</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
@@ -8509,18 +8623,17 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Prevenção</t>
+          <t>PTV (Eliminação Tripla)</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Intervenção
-(Planificada ou Em Curso)</t>
+          <t>RH (Nivel Central)</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Criacao de Demanda para PrEP Injectavel (LEN)</t>
+          <t>Assessor para área de PTV  no MISAU</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
@@ -8530,17 +8643,17 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a aceitação e uso da PrEP Injectável</t>
+          <t>Fortalecer a gestão e implementação das intervenções</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>Recursos para campanhas de sensibilização</t>
+          <t>Recursos humanos qualificados e materiais de apoio</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr"/>
@@ -8562,18 +8675,17 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Prevenção</t>
+          <t>PTV (Eliminação Tripla)</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-Supplies/Insumos</t>
+          <t>RH (Nivel Central)</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Reprodução de material de IEC para PrEP</t>
+          <t>Contratação de enfermeiras para o sector de SMI (CPN, CCR e SAAJ)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -8583,17 +8695,17 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
+          <t>Melhorar a capacidade de atendimento</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>nacional</t>
+          <t>Unidades Sanitarias</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>contratos de impressão</t>
+          <t>Recursos financeiros para contratação</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
@@ -8615,7 +8727,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Prevenção</t>
+          <t>PTV (Eliminação Tripla)</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -8625,7 +8737,7 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Capacitação para implementação da PrEP Oral e Injectável</t>
+          <t xml:space="preserve">Desenvolvimento e implementação do pacote de formação de pais e cuidadores, líderes comunitários, religiosos e políticos em matéria de PTV, SSR e PF </t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -8635,12 +8747,12 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a capacidade dos profissionais de saúde</t>
+          <t>Aumentar a capacidade de resposta comunitária</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>Unidades Sanitarias</t>
+          <t>Communidade</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
@@ -8667,17 +8779,18 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Prevenção</t>
+          <t>PTV (Eliminação Tripla)</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Reunião</t>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Reunião de monitoria das estratégias no âmbito da resposta ao primeiro 95 e fortalecimento da implementação da PrEP</t>
+          <t>Desenvolvimento de material IEC no âmbito da tripla ETV do HIV, Sífilis e Hepatite B</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8687,7 +8800,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Melhorar a coordenação e eficiência das estratégias</t>
+          <t>Aumentar a conscientização e educação em saúde</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -8697,7 +8810,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Recursos para a realização da reunião</t>
+          <t>Recursos para desenvolvimento de materiais de comunicação</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr"/>
@@ -8724,202 +8837,162 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Carga Viral Hepatite B</t>
+          <t xml:space="preserve">
+Supplies/Insumos</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Reprodução de material de apoio no âmbito da tripla ETV do HIV, Sífilis e Hepatite B</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>nacional</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>contratos de impressão</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr"/>
+      <c r="J151" s="3" t="inlineStr"/>
+      <c r="K151" s="3" t="inlineStr"/>
+      <c r="L151" s="3" t="inlineStr"/>
+      <c r="M151" s="3" t="inlineStr"/>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_150.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>hiv_151</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>PTV (Eliminação Tripla)</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Intervenção 
+(Planificada ou Em Curso)</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Avaliação para identificar barreiras locais, facilitadores, mitos e percepções em torno da Tripla Eliminação para informar a estratégia de CMSC.</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Informar estratégias e intervenções baseadas em evidências</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Recursos para pesquisa e coleta de dados</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_151.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>hiv_152</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>TB/HIV</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>TPT</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>Medicamentos/
 Insumos</t>
         </is>
       </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t>Melhorar a monitoria e tratamento da Hepatite B</t>
-        </is>
-      </c>
-      <c r="G151" s="3" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>Prim/Sec/ Tec/Quar</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>Melhorar o tratamento e prevenção de TB</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
         <is>
           <t>Unidades Sanitarias</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr">
+      <c r="H153" s="3" t="inlineStr">
         <is>
           <t>Medicamentos e insumos para tratamento</t>
         </is>
       </c>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>36.171</t>
-        </is>
-      </c>
-      <c r="K151" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="L151" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M151" s="3" t="inlineStr">
-        <is>
-          <t>Carga Viral para VHB nao foi implmentado em 2024</t>
-        </is>
-      </c>
-      <c r="N151" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_150.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>hiv_151</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>TDR Hepatite B</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Medicamentos/
-Insumos</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>Melhorar o tratamento de Hepatite B</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>Unidades Sanitarias</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>Medicamentos e insumos para tratamento</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>36.171</t>
-        </is>
-      </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>89.1%</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="inlineStr">
-        <is>
-          <t>14.55053042992741</t>
-        </is>
-      </c>
-      <c r="M152" s="2" t="inlineStr">
-        <is>
-          <t>Ainda foi um piloto ate o fim de 2024, em MC tinha 7,615, Nampula 18,706, Sofala 5,917</t>
-        </is>
-      </c>
-      <c r="N152" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_151.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>hiv_152</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>TDR Sifilis</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>Medicamentos/
-Insumos</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t>Reduzir a transmissão de sífilis</t>
-        </is>
-      </c>
-      <c r="G153" s="3" t="inlineStr">
-        <is>
-          <t>Unidades Sanitarias</t>
-        </is>
-      </c>
-      <c r="H153" s="3" t="inlineStr">
-        <is>
-          <t>Medicamentos e insumos para tratamento</t>
-        </is>
-      </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>&lt;2018</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>Pessoas com sinais ou sintomas</t>
-        </is>
-      </c>
-      <c r="K153" s="3" t="e">
-        <v>#VALUE!</v>
+          <t>266.240</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>93.2%</t>
+        </is>
       </c>
       <c r="L153" s="3" t="inlineStr">
         <is>
-          <t>2.041635729911516</t>
-        </is>
-      </c>
-      <c r="M153" s="3" t="inlineStr">
-        <is>
-          <t>testados para Sifilis no livro de ITS</t>
-        </is>
-      </c>
+          <t>14.80509942741094</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr"/>
       <c r="N153" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_152.html</t>
@@ -8934,18 +9007,17 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>PTV (Eliminação Tripla)</t>
+          <t>TB/HIV</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>ARVs PTV</t>
+          <t>Formações/Treinos</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Medicamentos/
-Insumos</t>
+          <t>Apoio técncio e logistico nas formações provinciais, distritais e nas US.</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8955,7 +9027,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Melhorar o tratamento e adesão ao tratamento de HIV</t>
+          <t>Aumentar a capacidade de resposta a TB e HIV</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -8965,34 +9037,18 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Medicamentos e insumos para tratamento</t>
+          <t>Recursos humanos e materiais para formação</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>&lt;2015</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>134.000</t>
-        </is>
-      </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>81.8%</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="inlineStr">
-        <is>
-          <t>8.066636253214423</t>
-        </is>
-      </c>
-      <c r="M154" s="2" t="inlineStr">
-        <is>
-          <t>MG HIV+ na CPN</t>
-        </is>
-      </c>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr"/>
       <c r="N154" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_153.html</t>
@@ -9007,18 +9063,17 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>PTV (Eliminação Tripla)</t>
+          <t>TB/HIV</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>DUO Sifilis e HIV</t>
+          <t>Supplies</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Medicamentos/
-Insumos</t>
+          <t>Alocação de medicamentos e insumos para tratamento de TB e HIV</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
@@ -9028,7 +9083,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Aumentar a eficiência do tratamento</t>
+          <t>Garantir o tratamento adequado</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -9043,1246 +9098,16 @@
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>2.111.754</t>
-        </is>
-      </c>
-      <c r="K155" s="3" t="inlineStr">
-        <is>
-          <t>99.0%</t>
-        </is>
-      </c>
-      <c r="L155" s="3" t="inlineStr">
-        <is>
-          <t>1.33270233448056</t>
-        </is>
-      </c>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr"/>
+      <c r="K155" s="3" t="inlineStr"/>
+      <c r="L155" s="3" t="inlineStr"/>
       <c r="M155" s="3" t="inlineStr"/>
       <c r="N155" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_154.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>hiv_155</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>RH</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>▪Nacional: 1 assessora de SMI
-▪Provincial: Gestor de SMI (MC 1, Gaza 1), Gestora de CaCU (1 MC)
-▪Distritos: Oficiais distritais de SMI
-▪US: Alocação de enfermeiras de SMI, conselheiras de SMI, Maes Mentoras</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>Aumentar a eficiência do tratamento</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr"/>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="inlineStr"/>
-      <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="2" t="inlineStr"/>
-      <c r="M156" s="2" t="inlineStr"/>
-      <c r="N156" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_155.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>hiv_156</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>Formações/Treinos</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>Apoio técnico e logístico para a realização de formações em sala e em serviço a nivel Provincial, Distrital e da US</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F157" s="3" t="inlineStr">
-        <is>
-          <t>Aumentar a eficiência do tratamento</t>
-        </is>
-      </c>
-      <c r="G157" s="3" t="inlineStr"/>
-      <c r="H157" s="3" t="inlineStr"/>
-      <c r="I157" s="3" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
-      <c r="J157" s="3" t="inlineStr"/>
-      <c r="K157" s="3" t="inlineStr"/>
-      <c r="L157" s="3" t="inlineStr"/>
-      <c r="M157" s="3" t="inlineStr"/>
-      <c r="N157" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_156.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>hiv_157</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Supplies</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>Alocacao de material escritorio, material medico cirurgico, instrumentos de registo e material IEC</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>Aumentar a eficiência do tratamento</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr"/>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="inlineStr"/>
-      <c r="K158" s="2" t="inlineStr"/>
-      <c r="L158" s="2" t="inlineStr"/>
-      <c r="M158" s="2" t="inlineStr"/>
-      <c r="N158" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_157.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>hiv_158</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="inlineStr">
-        <is>
-          <t>Apoio Tecnico</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>Apoio técnico ao Sistema Nacional de Saúde através de oficiais técnicos nas Unidades Sanitárias e distritos, gestores a nível provincial e assessores técnicos a nível central, garantindo apoio direto no terreno, coordenação programática e orientação estratégica para a melhoria da qualidade dos serviços.</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F159" s="3" t="inlineStr">
-        <is>
-          <t>Aumentar a eficiência do tratamento</t>
-        </is>
-      </c>
-      <c r="G159" s="3" t="inlineStr"/>
-      <c r="H159" s="3" t="inlineStr"/>
-      <c r="I159" s="3" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
-      <c r="J159" s="3" t="inlineStr"/>
-      <c r="K159" s="3" t="inlineStr"/>
-      <c r="L159" s="3" t="inlineStr"/>
-      <c r="M159" s="3" t="inlineStr"/>
-      <c r="N159" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_158.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>hiv_159</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>PTV</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.Assistencia técnica atraves das assistentes de PTV/Supervisão conjunta com DPS/SPS e SDSMAS
-2. Encontros de analise e discussão de dados e encontros de coordenação de actividade da área                                                                                                                                                                                                                                                                                                                                                           7. Encontros de coordenação com actores comunitários                                                                                                                                                                                                                                                                                 8. Formações de atualização da área (novas normas)                                                                                                                                                                                                                                                                                9.  Provisão directa de serviços através dos ESMI/Assistentes de SMI alocados pelo projecto                                                                                                                                                                                                    10. Contratação das MM, manutenção e supervisão das actividades                                                                                                                                                                                                                                                                                                                                                                                                                                  12. Exercícios de ligação entre serviços (maternidade/CCR e CCR/Serviços tarv)     </t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>Aumentar a eficiência do tratamento</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr"/>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>Desde o inicio do Projecto em 2019</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>Mulheres gravidas e lactantes
-Provedores dos servicos de SMI
-MM</t>
-        </is>
-      </c>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>Todas as US AJUDA (149) Manica (51), Niassa(18), Sofala (47) e Tete (33)</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="inlineStr"/>
-      <c r="M160" s="2" t="inlineStr"/>
-      <c r="N160" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_159.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="inlineStr">
-        <is>
-          <t>hiv_160</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="inlineStr">
-        <is>
-          <t>CACUM</t>
-        </is>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.Compra de aparelhos de termoablacao para as provincia  e transporte de aparelho comprados com  fundos do Misau                                                                                                                                                                                                                                                                           5. Compra de aparelhos de Leep para as provincias                                                                                                                                                                                                                                                                                                        6. Aquisição de insumos (Acido acetico, lugol, hemogin, mangueiras, especulos, pincas, panelas de esterilizacao, )filtros de carvao, etc)para maquinas de LEEP e material medico cirurgico (Marqueza, gambiar), manutenção dos equipamentosetc.                                                                                                                                                                                                                                 7. Apoio na formacao de Termoabalaco e de Leep                                                                                                                                                                                                                                                                                         8. Fornecimento de credito e telemovel aos hospitais de referencia                                                                                                                                                                                                                                                      9. Fornecimento de subsidio de transporte a mulheres com lesao maior que 75% para o hospital de referencia                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        12. Geracao de lista de mulheres sem rastreio a mais de 1 ano, para referencia para rastreio        </t>
-        </is>
-      </c>
-      <c r="E161" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F161" s="3" t="inlineStr">
-        <is>
-          <t>Aumentar a eficiência do tratamento</t>
-        </is>
-      </c>
-      <c r="G161" s="3" t="inlineStr"/>
-      <c r="H161" s="3" t="inlineStr"/>
-      <c r="I161" s="3" t="inlineStr">
-        <is>
-          <t>Desde o inicio do Projecto em 2019</t>
-        </is>
-      </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>Mulher Lactante  e pacientes HIV+                                                                                                                                                                                  ESMI</t>
-        </is>
-      </c>
-      <c r="K161" s="3" t="inlineStr">
-        <is>
-          <t>Todas as US AJUDA (149) Manica (51), Niassa(18), Sofala (47) e Tete (33)</t>
-        </is>
-      </c>
-      <c r="L161" s="3" t="inlineStr"/>
-      <c r="M161" s="3" t="inlineStr"/>
-      <c r="N161" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_160.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>hiv_161</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>Oferta do pacote de PTV do HIV, Sífilis e Hepatite B</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>Aumentar a cobertura das intervenções de PTV</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>Recursos humanos e materiais para implementação</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-      <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="2" t="inlineStr"/>
-      <c r="M162" s="2" t="inlineStr"/>
-      <c r="N162" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_161.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>hiv_162</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>Reuniões</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>Realização da oficina de trabalho, nacionail e provinciais, no âmbito da monitoria da implementação do Plano Nacional de Tripla Eliminação da Transmissão Vertical do HIV, Sífilis e Hepatite B 2026- 2030</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>Melhorar a coordenação e implementação</t>
-        </is>
-      </c>
-      <c r="G163" s="3" t="inlineStr">
-        <is>
-          <t>Nacional e Provincial</t>
-        </is>
-      </c>
-      <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>Recursos para logística e organização de reuniões</t>
-        </is>
-      </c>
-      <c r="I163" s="3" t="inlineStr"/>
-      <c r="J163" s="3" t="inlineStr"/>
-      <c r="K163" s="3" t="inlineStr"/>
-      <c r="L163" s="3" t="inlineStr"/>
-      <c r="M163" s="3" t="inlineStr"/>
-      <c r="N163" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_162.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>hiv_163</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Formações/Treinos</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>Actualizações do pacote de PTV, incluíndo capacitações e conversão para a plataforma de telessáude</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>disponibilizar o pacote no plataforma telesaude</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>equipamento de gravação, tempo, plataform de telesaude</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-      <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="2" t="inlineStr"/>
-      <c r="M164" s="2" t="inlineStr"/>
-      <c r="N164" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_163.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>hiv_164</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Supervisão integrada de PTV e SMI</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t>Garantir a eliminação da transmissão vertical</t>
-        </is>
-      </c>
-      <c r="G165" s="3" t="inlineStr">
-        <is>
-          <t>Unidades Sanitarias</t>
-        </is>
-      </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>Recursos humanos e materiais necessários</t>
-        </is>
-      </c>
-      <c r="I165" s="3" t="inlineStr"/>
-      <c r="J165" s="3" t="inlineStr"/>
-      <c r="K165" s="3" t="inlineStr"/>
-      <c r="L165" s="3" t="inlineStr"/>
-      <c r="M165" s="3" t="inlineStr"/>
-      <c r="N165" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_164.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>hiv_165</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>Avaliação do meio termo da implementação do Plano Nacional  de Tripla ETV do HIV, Sífilis e Hepatite B 2026- 2030</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>Monitorar o progresso e eficácia do plano</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>Recursos humanos e materiais para avaliação</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-      <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="2" t="inlineStr"/>
-      <c r="M166" s="2" t="inlineStr"/>
-      <c r="N166" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_165.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="inlineStr">
-        <is>
-          <t>hiv_166</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>RH (Nivel Central)</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>Assessor para área de PTV  no MISAU</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F167" s="3" t="inlineStr">
-        <is>
-          <t>Fortalecer a gestão e implementação das intervenções</t>
-        </is>
-      </c>
-      <c r="G167" s="3" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>Recursos humanos qualificados e materiais de apoio</t>
-        </is>
-      </c>
-      <c r="I167" s="3" t="inlineStr"/>
-      <c r="J167" s="3" t="inlineStr"/>
-      <c r="K167" s="3" t="inlineStr"/>
-      <c r="L167" s="3" t="inlineStr"/>
-      <c r="M167" s="3" t="inlineStr"/>
-      <c r="N167" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_166.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>hiv_167</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>RH (Nivel Central)</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>Contratação de enfermeiras para o sector de SMI (CPN, CCR e SAAJ)</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>Melhorar a capacidade de atendimento</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>Unidades Sanitarias</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>Recursos financeiros para contratação</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-      <c r="K168" s="2" t="inlineStr"/>
-      <c r="L168" s="2" t="inlineStr"/>
-      <c r="M168" s="2" t="inlineStr"/>
-      <c r="N168" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_167.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>hiv_168</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>Formações/Treinos</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Desenvolvimento e implementação do pacote de formação de pais e cuidadores, líderes comunitários, religiosos e políticos em matéria de PTV, SSR e PF </t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F169" s="3" t="inlineStr">
-        <is>
-          <t>Aumentar a capacidade de resposta comunitária</t>
-        </is>
-      </c>
-      <c r="G169" s="3" t="inlineStr">
-        <is>
-          <t>Communidade</t>
-        </is>
-      </c>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>Materiais de formação e recursos humanos</t>
-        </is>
-      </c>
-      <c r="I169" s="3" t="inlineStr"/>
-      <c r="J169" s="3" t="inlineStr"/>
-      <c r="K169" s="3" t="inlineStr"/>
-      <c r="L169" s="3" t="inlineStr"/>
-      <c r="M169" s="3" t="inlineStr"/>
-      <c r="N169" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_168.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>hiv_169</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>Desenvolvimento de material IEC no âmbito da tripla ETV do HIV, Sífilis e Hepatite B</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>Aumentar a conscientização e educação em saúde</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>Recursos para desenvolvimento de materiais de comunicação</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr"/>
-      <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="2" t="inlineStr"/>
-      <c r="M170" s="2" t="inlineStr"/>
-      <c r="N170" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_169.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>hiv_170</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">
-Supplies/Insumos</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>Reprodução de material de apoio no âmbito da tripla ETV do HIV, Sífilis e Hepatite B</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t>Disponibilizar instrumentos para registo e/ou melhoria de atendimento</t>
-        </is>
-      </c>
-      <c r="G171" s="3" t="inlineStr">
-        <is>
-          <t>nacional</t>
-        </is>
-      </c>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>contratos de impressão</t>
-        </is>
-      </c>
-      <c r="I171" s="3" t="inlineStr"/>
-      <c r="J171" s="3" t="inlineStr"/>
-      <c r="K171" s="3" t="inlineStr"/>
-      <c r="L171" s="3" t="inlineStr"/>
-      <c r="M171" s="3" t="inlineStr"/>
-      <c r="N171" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_170.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>hiv_171</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>PTV (Eliminação Tripla)</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>Intervenção 
-(Planificada ou Em Curso)</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>Avaliação para identificar barreiras locais, facilitadores, mitos e percepções em torno da Tripla Eliminação para informar a estratégia de CMSC.</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>Informar estratégias e intervenções baseadas em evidências</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>Recursos para pesquisa e coleta de dados</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr"/>
-      <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="2" t="inlineStr"/>
-      <c r="M172" s="2" t="inlineStr"/>
-      <c r="N172" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_171.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>hiv_172</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>TB/HIV</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>TPT</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>Medicamentos/
-Insumos</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t>Melhorar o tratamento e prevenção de TB</t>
-        </is>
-      </c>
-      <c r="G173" s="3" t="inlineStr">
-        <is>
-          <t>Unidades Sanitarias</t>
-        </is>
-      </c>
-      <c r="H173" s="3" t="inlineStr">
-        <is>
-          <t>Medicamentos e insumos para tratamento</t>
-        </is>
-      </c>
-      <c r="I173" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="J173" s="3" t="inlineStr">
-        <is>
-          <t>266.240</t>
-        </is>
-      </c>
-      <c r="K173" s="3" t="inlineStr">
-        <is>
-          <t>93.2%</t>
-        </is>
-      </c>
-      <c r="L173" s="3" t="inlineStr">
-        <is>
-          <t>14.80509942741094</t>
-        </is>
-      </c>
-      <c r="M173" s="3" t="inlineStr"/>
-      <c r="N173" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_172.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>hiv_173</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>TB/HIV</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>RH</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>▪Nacional: Assessor de TB
-▪Provincial: Gestores de TB (MC 1, Gaza 1)
-▪Distritos (MC): Oficiais distritais de TB/HIV 
-▪US: Alocação de conselheiros leigos, Técnicos de Medicina Geral, Enfermeiros para a PU da TB e Oficiais de tosse.</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>Melhorar o tratamento e prevenção de TB</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr"/>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="inlineStr"/>
-      <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="2" t="inlineStr"/>
-      <c r="M174" s="2" t="inlineStr"/>
-      <c r="N174" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_173.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="inlineStr">
-        <is>
-          <t>hiv_174</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>TB/HIV</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>Formações/Treinos</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>Apoio técncio e logistico nas formações provinciais, distritais e nas US.</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F175" s="3" t="inlineStr">
-        <is>
-          <t>Melhorar o tratamento e prevenção de TB</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="inlineStr"/>
-      <c r="H175" s="3" t="inlineStr"/>
-      <c r="I175" s="3" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
-      <c r="J175" s="3" t="inlineStr"/>
-      <c r="K175" s="3" t="inlineStr"/>
-      <c r="L175" s="3" t="inlineStr"/>
-      <c r="M175" s="3" t="inlineStr"/>
-      <c r="N175" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_174.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>hiv_175</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>TB/HIV</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>Supplies</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
-        <is>
-          <t>∙ Alocacao de consumiveis hospitalares (máscaras cirurgicas e N95, alcoól, testes rápidos de gravidez, fits de glícemia);
-∙ Aquisição e distribuição de mobiliario (mesas para provedores e utentes, secretarias, ventoinhas para PCI);
-∙ Alocação de consumiveis de escritório (canetas, sebentas, lápis, marcadores);
-∙Alocação de equipamento hospitalar (glicometros, ECG, Nebulizadores, esfigmomanometros)</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>Melhorar o tratamento e prevenção de TB</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr"/>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="inlineStr"/>
-      <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="2" t="inlineStr"/>
-      <c r="M176" s="2" t="inlineStr"/>
-      <c r="N176" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_175.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>hiv_176</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>TB/HIV</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>Apoio Tecnico</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>Apoio técnico ao Sistema Nacional de Saúde através de oficiais técnicos nas Unidades Sanitárias e distritos, gestores a nível provincial e assessores técnicos a nível central, garantindo apoio direto no terreno, coordenação programática e orientação estratégica para a melhoria da qualidade dos serviços.</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F177" s="3" t="inlineStr">
-        <is>
-          <t>Melhorar o tratamento e prevenção de TB</t>
-        </is>
-      </c>
-      <c r="G177" s="3" t="inlineStr"/>
-      <c r="H177" s="3" t="inlineStr"/>
-      <c r="I177" s="3" t="inlineStr">
-        <is>
-          <t>2011 (MC)
-2025 (Gaza)</t>
-        </is>
-      </c>
-      <c r="J177" s="3" t="inlineStr"/>
-      <c r="K177" s="3" t="inlineStr"/>
-      <c r="L177" s="3" t="inlineStr"/>
-      <c r="M177" s="3" t="inlineStr"/>
-      <c r="N177" s="3" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_176.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>hiv_177</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>TB/HIV</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>1. TPT (inicio e completude) a todos pacientes vivendo com HIV
-2. Seguimento da cascata de TX_TB (rastreio de TB em PVHIV e seguimento dos presuntivos até ao diagnóstico TB e inicio do Tratamento)
-3. Rastreio de TB em todas portas de entrada incluindo o FAST em 26 unidades sanitárias
-4. Apoio a PU de TB/HIV
-5. APSS e retenção a todos pacientes com TB
-6. Aquisição de equipamentos e insumos para expanção de paragem unica TB
-7. Apoio tecnico nas melhoria de qualidade de TB
-8. Reprodução e distribuição dos instrumentos de TB</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>Prim/Sec/ Tec/Quar</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>Melhorar o tratamento e prevenção de TB</t>
-        </is>
-      </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr"/>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>Desde o inicio do Projecto em 2019</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="inlineStr"/>
-      <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="2" t="inlineStr"/>
-      <c r="M178" s="2" t="inlineStr"/>
-      <c r="N178" s="2" t="inlineStr">
-        <is>
-          <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_177.html</t>
         </is>
       </c>
     </row>

--- a/hiv/catalogo_HIV.xlsx
+++ b/hiv/catalogo_HIV.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N155"/>
+  <dimension ref="A1:O155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -454,11 +454,12 @@
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -509,25 +510,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Gastos em 2024 (USD)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Pop. elegível</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Cobertura</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Custo por unidade</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>URL da Ficha</t>
         </is>
@@ -577,21 +583,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>200.000</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
           <t>2.477.000</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>82.0%</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>0.09841212043675299</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_01.html</t>
         </is>
@@ -643,11 +654,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_02.html</t>
         </is>
@@ -701,11 +717,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_03.html</t>
         </is>
@@ -753,11 +774,16 @@
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_04.html</t>
         </is>
@@ -806,11 +832,16 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_05.html</t>
         </is>
@@ -859,11 +890,16 @@
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_06.html</t>
         </is>
@@ -911,11 +947,16 @@
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_07.html</t>
         </is>
@@ -963,11 +1004,16 @@
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_08.html</t>
         </is>
@@ -1016,11 +1062,16 @@
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_09.html</t>
         </is>
@@ -1069,11 +1120,16 @@
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_10.html</t>
         </is>
@@ -1122,11 +1178,16 @@
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_11.html</t>
         </is>
@@ -1175,11 +1236,16 @@
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K13" s="3" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_12.html</t>
         </is>
@@ -1228,11 +1294,16 @@
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_13.html</t>
         </is>
@@ -1281,11 +1352,16 @@
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K15" s="3" t="inlineStr"/>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_14.html</t>
         </is>
@@ -1340,21 +1416,26 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>4.938.632</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>254.946</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>50.22630007782692</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>0.385679676495397</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_15.html</t>
         </is>
@@ -1409,21 +1490,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>6.887.521</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
           <t>254.946</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>50.22630007782692</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>0.537877067032586</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_16.html</t>
         </is>
@@ -1471,11 +1557,16 @@
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_17.html</t>
         </is>
@@ -1523,11 +1614,16 @@
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" s="3" t="inlineStr"/>
       <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_18.html</t>
         </is>
@@ -1576,11 +1672,16 @@
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_19.html</t>
         </is>
@@ -1629,11 +1730,16 @@
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
       <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_20.html</t>
         </is>
@@ -1682,11 +1788,16 @@
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_21.html</t>
         </is>
@@ -1734,11 +1845,16 @@
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K23" s="3" t="inlineStr"/>
       <c r="L23" s="3" t="inlineStr"/>
       <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_22.html</t>
         </is>
@@ -1786,11 +1902,16 @@
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_23.html</t>
         </is>
@@ -1838,11 +1959,16 @@
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K25" s="3" t="inlineStr"/>
       <c r="L25" s="3" t="inlineStr"/>
       <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="3" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_24.html</t>
         </is>
@@ -1890,11 +2016,16 @@
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_25.html</t>
         </is>
@@ -1942,11 +2073,16 @@
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K27" s="3" t="inlineStr"/>
       <c r="L27" s="3" t="inlineStr"/>
       <c r="M27" s="3" t="inlineStr"/>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_26.html</t>
         </is>
@@ -1994,11 +2130,16 @@
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_27.html</t>
         </is>
@@ -2047,11 +2188,16 @@
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K29" s="3" t="inlineStr"/>
       <c r="L29" s="3" t="inlineStr"/>
       <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_28.html</t>
         </is>
@@ -2100,11 +2246,16 @@
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_29.html</t>
         </is>
@@ -2153,11 +2304,16 @@
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="inlineStr"/>
       <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr">
+      <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_30.html</t>
         </is>
@@ -2206,11 +2362,16 @@
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_31.html</t>
         </is>
@@ -2265,21 +2426,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>61.567.205</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
           <t>2.300.000</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>84.1%</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>31.82389388066507</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_32.html</t>
         </is>
@@ -2331,11 +2497,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_33.html</t>
         </is>
@@ -2387,11 +2558,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K35" s="3" t="inlineStr"/>
       <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr">
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_34.html</t>
         </is>
@@ -2443,11 +2619,16 @@
           <t>Sem Informação</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_35.html</t>
         </is>
@@ -2495,11 +2676,16 @@
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K37" s="3" t="inlineStr"/>
       <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr">
+      <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_36.html</t>
         </is>
@@ -2548,11 +2734,16 @@
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_37.html</t>
         </is>
@@ -2600,11 +2791,16 @@
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K39" s="3" t="inlineStr"/>
       <c r="L39" s="3" t="inlineStr"/>
       <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr">
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_38.html</t>
         </is>
@@ -2653,11 +2849,16 @@
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_39.html</t>
         </is>
@@ -2705,11 +2906,16 @@
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K41" s="3" t="inlineStr"/>
       <c r="L41" s="3" t="inlineStr"/>
       <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr">
+      <c r="N41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_40.html</t>
         </is>
@@ -2757,11 +2963,16 @@
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_41.html</t>
         </is>
@@ -2809,11 +3020,16 @@
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K43" s="3" t="inlineStr"/>
       <c r="L43" s="3" t="inlineStr"/>
       <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="3" t="inlineStr">
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_42.html</t>
         </is>
@@ -2862,11 +3078,16 @@
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_43.html</t>
         </is>
@@ -2914,11 +3135,16 @@
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K45" s="3" t="inlineStr"/>
       <c r="L45" s="3" t="inlineStr"/>
       <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr">
+      <c r="N45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_44.html</t>
         </is>
@@ -2967,11 +3193,16 @@
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_45.html</t>
         </is>
@@ -3019,11 +3250,16 @@
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K47" s="3" t="inlineStr"/>
       <c r="L47" s="3" t="inlineStr"/>
       <c r="M47" s="3" t="inlineStr"/>
-      <c r="N47" s="3" t="inlineStr">
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_46.html</t>
         </is>
@@ -3072,11 +3308,16 @@
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_47.html</t>
         </is>
@@ -3124,11 +3365,16 @@
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K49" s="3" t="inlineStr"/>
       <c r="L49" s="3" t="inlineStr"/>
       <c r="M49" s="3" t="inlineStr"/>
-      <c r="N49" s="3" t="inlineStr">
+      <c r="N49" s="3" t="inlineStr"/>
+      <c r="O49" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_48.html</t>
         </is>
@@ -3177,11 +3423,16 @@
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_49.html</t>
         </is>
@@ -3230,11 +3481,16 @@
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K51" s="3" t="inlineStr"/>
       <c r="L51" s="3" t="inlineStr"/>
       <c r="M51" s="3" t="inlineStr"/>
-      <c r="N51" s="3" t="inlineStr">
+      <c r="N51" s="3" t="inlineStr"/>
+      <c r="O51" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_50.html</t>
         </is>
@@ -3282,11 +3538,16 @@
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_51.html</t>
         </is>
@@ -3341,25 +3602,30 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>3.850.406</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
           <t>245.610</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="L53" s="3" t="inlineStr">
         <is>
           <t>51.7%</t>
         </is>
       </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="M53" s="3" t="inlineStr">
         <is>
           <t>30.33081522210056</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr">
+      <c r="N53" s="3" t="inlineStr">
         <is>
           <t>Dados de SESP</t>
         </is>
       </c>
-      <c r="N53" s="3" t="inlineStr">
+      <c r="O53" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_52.html</t>
         </is>
@@ -3414,21 +3680,26 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
+          <t>4.007.197</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
           <t>2.032.370</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>81.1%</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>2.430270082098699</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_53.html</t>
         </is>
@@ -3483,21 +3754,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>3.993.859</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
           <t>177.000</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="L55" s="3" t="inlineStr">
         <is>
           <t>55.2%</t>
         </is>
       </c>
-      <c r="L55" s="3" t="inlineStr">
+      <c r="M55" s="3" t="inlineStr">
         <is>
           <t>40.8587316200843</t>
         </is>
       </c>
-      <c r="M55" s="3" t="inlineStr"/>
-      <c r="N55" s="3" t="inlineStr">
+      <c r="N55" s="3" t="inlineStr"/>
+      <c r="O55" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_54.html</t>
         </is>
@@ -3550,11 +3826,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_55.html</t>
         </is>
@@ -3607,11 +3888,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K57" s="3" t="inlineStr"/>
       <c r="L57" s="3" t="inlineStr"/>
       <c r="M57" s="3" t="inlineStr"/>
-      <c r="N57" s="3" t="inlineStr">
+      <c r="N57" s="3" t="inlineStr"/>
+      <c r="O57" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_56.html</t>
         </is>
@@ -3659,11 +3945,16 @@
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_57.html</t>
         </is>
@@ -3711,11 +4002,16 @@
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr"/>
-      <c r="J59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K59" s="3" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr"/>
       <c r="M59" s="3" t="inlineStr"/>
-      <c r="N59" s="3" t="inlineStr">
+      <c r="N59" s="3" t="inlineStr"/>
+      <c r="O59" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_58.html</t>
         </is>
@@ -3764,11 +4060,16 @@
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_59.html</t>
         </is>
@@ -3816,11 +4117,16 @@
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr"/>
-      <c r="J61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K61" s="3" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr"/>
       <c r="M61" s="3" t="inlineStr"/>
-      <c r="N61" s="3" t="inlineStr">
+      <c r="N61" s="3" t="inlineStr"/>
+      <c r="O61" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_60.html</t>
         </is>
@@ -3868,11 +4174,16 @@
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_61.html</t>
         </is>
@@ -3920,11 +4231,16 @@
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr"/>
-      <c r="J63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K63" s="3" t="inlineStr"/>
       <c r="L63" s="3" t="inlineStr"/>
       <c r="M63" s="3" t="inlineStr"/>
-      <c r="N63" s="3" t="inlineStr">
+      <c r="N63" s="3" t="inlineStr"/>
+      <c r="O63" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_62.html</t>
         </is>
@@ -3979,23 +4295,28 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
+          <t>509.142</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
           <t>158.532</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="L64" s="2" t="e">
+      <c r="M64" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t>264541 novos inicios e 175826 reinicios</t>
         </is>
       </c>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_63.html</t>
         </is>
@@ -4050,17 +4371,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>752.995</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
           <t>158.532</t>
         </is>
       </c>
-      <c r="K65" s="3" t="inlineStr">
+      <c r="L65" s="3" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
-      <c r="N65" s="3" t="inlineStr">
+      <c r="N65" s="3" t="inlineStr"/>
+      <c r="O65" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_64.html</t>
         </is>
@@ -4115,17 +4441,22 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
+          <t>2.000.618</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
           <t>158.532</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_65.html</t>
         </is>
@@ -4174,11 +4505,16 @@
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr"/>
-      <c r="J67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K67" s="3" t="inlineStr"/>
       <c r="L67" s="3" t="inlineStr"/>
       <c r="M67" s="3" t="inlineStr"/>
-      <c r="N67" s="3" t="inlineStr">
+      <c r="N67" s="3" t="inlineStr"/>
+      <c r="O67" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_66.html</t>
         </is>
@@ -4227,11 +4563,16 @@
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr">
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_67.html</t>
         </is>
@@ -4280,11 +4621,16 @@
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr"/>
-      <c r="J69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K69" s="3" t="inlineStr"/>
       <c r="L69" s="3" t="inlineStr"/>
       <c r="M69" s="3" t="inlineStr"/>
-      <c r="N69" s="3" t="inlineStr">
+      <c r="N69" s="3" t="inlineStr"/>
+      <c r="O69" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_68.html</t>
         </is>
@@ -4333,11 +4679,16 @@
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr">
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_69.html</t>
         </is>
@@ -4386,11 +4737,16 @@
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K71" s="3" t="inlineStr"/>
       <c r="L71" s="3" t="inlineStr"/>
       <c r="M71" s="3" t="inlineStr"/>
-      <c r="N71" s="3" t="inlineStr">
+      <c r="N71" s="3" t="inlineStr"/>
+      <c r="O71" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_70.html</t>
         </is>
@@ -4439,11 +4795,16 @@
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr">
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_71.html</t>
         </is>
@@ -4492,11 +4853,16 @@
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr"/>
-      <c r="J73" s="3" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K73" s="3" t="inlineStr"/>
       <c r="L73" s="3" t="inlineStr"/>
       <c r="M73" s="3" t="inlineStr"/>
-      <c r="N73" s="3" t="inlineStr">
+      <c r="N73" s="3" t="inlineStr"/>
+      <c r="O73" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_72.html</t>
         </is>
@@ -4544,11 +4910,16 @@
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_73.html</t>
         </is>
@@ -4596,11 +4967,16 @@
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K75" s="3" t="inlineStr"/>
       <c r="L75" s="3" t="inlineStr"/>
       <c r="M75" s="3" t="inlineStr"/>
-      <c r="N75" s="3" t="inlineStr">
+      <c r="N75" s="3" t="inlineStr"/>
+      <c r="O75" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_74.html</t>
         </is>
@@ -4649,11 +5025,16 @@
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_75.html</t>
         </is>
@@ -4702,11 +5083,16 @@
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr"/>
-      <c r="J77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K77" s="3" t="inlineStr"/>
       <c r="L77" s="3" t="inlineStr"/>
       <c r="M77" s="3" t="inlineStr"/>
-      <c r="N77" s="3" t="inlineStr">
+      <c r="N77" s="3" t="inlineStr"/>
+      <c r="O77" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_76.html</t>
         </is>
@@ -4755,11 +5141,16 @@
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_77.html</t>
         </is>
@@ -4808,11 +5199,16 @@
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr"/>
-      <c r="J79" s="3" t="inlineStr"/>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K79" s="3" t="inlineStr"/>
       <c r="L79" s="3" t="inlineStr"/>
       <c r="M79" s="3" t="inlineStr"/>
-      <c r="N79" s="3" t="inlineStr">
+      <c r="N79" s="3" t="inlineStr"/>
+      <c r="O79" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_78.html</t>
         </is>
@@ -4861,11 +5257,16 @@
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_79.html</t>
         </is>
@@ -4914,11 +5315,16 @@
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr"/>
-      <c r="J81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K81" s="3" t="inlineStr"/>
       <c r="L81" s="3" t="inlineStr"/>
       <c r="M81" s="3" t="inlineStr"/>
-      <c r="N81" s="3" t="inlineStr">
+      <c r="N81" s="3" t="inlineStr"/>
+      <c r="O81" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_80.html</t>
         </is>
@@ -4967,11 +5373,16 @@
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_81.html</t>
         </is>
@@ -5020,11 +5431,16 @@
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr"/>
-      <c r="J83" s="3" t="inlineStr"/>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K83" s="3" t="inlineStr"/>
       <c r="L83" s="3" t="inlineStr"/>
       <c r="M83" s="3" t="inlineStr"/>
-      <c r="N83" s="3" t="inlineStr">
+      <c r="N83" s="3" t="inlineStr"/>
+      <c r="O83" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_82.html</t>
         </is>
@@ -5073,11 +5489,16 @@
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr">
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_83.html</t>
         </is>
@@ -5125,11 +5546,16 @@
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr"/>
-      <c r="J85" s="3" t="inlineStr"/>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K85" s="3" t="inlineStr"/>
       <c r="L85" s="3" t="inlineStr"/>
       <c r="M85" s="3" t="inlineStr"/>
-      <c r="N85" s="3" t="inlineStr">
+      <c r="N85" s="3" t="inlineStr"/>
+      <c r="O85" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_84.html</t>
         </is>
@@ -5177,11 +5603,16 @@
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr"/>
-      <c r="N86" s="2" t="inlineStr">
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_85.html</t>
         </is>
@@ -5230,11 +5661,16 @@
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr"/>
-      <c r="J87" s="3" t="inlineStr"/>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K87" s="3" t="inlineStr"/>
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
-      <c r="N87" s="3" t="inlineStr">
+      <c r="N87" s="3" t="inlineStr"/>
+      <c r="O87" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_86.html</t>
         </is>
@@ -5282,11 +5718,16 @@
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_87.html</t>
         </is>
@@ -5334,11 +5775,16 @@
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr"/>
-      <c r="J89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K89" s="3" t="inlineStr"/>
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
-      <c r="N89" s="3" t="inlineStr">
+      <c r="N89" s="3" t="inlineStr"/>
+      <c r="O89" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_88.html</t>
         </is>
@@ -5392,23 +5838,28 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
+          <t>249.000</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K90" s="2" t="e">
+      <c r="L90" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="M90" s="2" t="inlineStr">
         <is>
           <t>3507.042253521127</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="N90" s="2" t="inlineStr">
         <is>
           <t># alcancado sao Unidade Santiarias</t>
         </is>
       </c>
-      <c r="N90" s="2" t="inlineStr">
+      <c r="O90" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_89.html</t>
         </is>
@@ -5460,11 +5911,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J91" s="3" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K91" s="3" t="inlineStr"/>
       <c r="L91" s="3" t="inlineStr"/>
       <c r="M91" s="3" t="inlineStr"/>
-      <c r="N91" s="3" t="inlineStr">
+      <c r="N91" s="3" t="inlineStr"/>
+      <c r="O91" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_90.html</t>
         </is>
@@ -5517,11 +5973,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr">
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_91.html</t>
         </is>
@@ -5569,11 +6030,16 @@
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr"/>
-      <c r="J93" s="3" t="inlineStr"/>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K93" s="3" t="inlineStr"/>
       <c r="L93" s="3" t="inlineStr"/>
       <c r="M93" s="3" t="inlineStr"/>
-      <c r="N93" s="3" t="inlineStr">
+      <c r="N93" s="3" t="inlineStr"/>
+      <c r="O93" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_92.html</t>
         </is>
@@ -5621,11 +6087,16 @@
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr"/>
-      <c r="N94" s="2" t="inlineStr">
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_93.html</t>
         </is>
@@ -5673,11 +6144,16 @@
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr"/>
-      <c r="J95" s="3" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K95" s="3" t="inlineStr"/>
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
-      <c r="N95" s="3" t="inlineStr">
+      <c r="N95" s="3" t="inlineStr"/>
+      <c r="O95" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_94.html</t>
         </is>
@@ -5726,11 +6202,16 @@
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr">
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_95.html</t>
         </is>
@@ -5779,11 +6260,16 @@
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr"/>
-      <c r="J97" s="3" t="inlineStr"/>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K97" s="3" t="inlineStr"/>
       <c r="L97" s="3" t="inlineStr"/>
       <c r="M97" s="3" t="inlineStr"/>
-      <c r="N97" s="3" t="inlineStr">
+      <c r="N97" s="3" t="inlineStr"/>
+      <c r="O97" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_96.html</t>
         </is>
@@ -5832,11 +6318,16 @@
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr">
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_97.html</t>
         </is>
@@ -5885,11 +6376,16 @@
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr"/>
-      <c r="J99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K99" s="3" t="inlineStr"/>
       <c r="L99" s="3" t="inlineStr"/>
       <c r="M99" s="3" t="inlineStr"/>
-      <c r="N99" s="3" t="inlineStr">
+      <c r="N99" s="3" t="inlineStr"/>
+      <c r="O99" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_98.html</t>
         </is>
@@ -5938,11 +6434,16 @@
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr">
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_99.html</t>
         </is>
@@ -5990,11 +6491,16 @@
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr"/>
-      <c r="J101" s="3" t="inlineStr"/>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K101" s="3" t="inlineStr"/>
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
-      <c r="N101" s="3" t="inlineStr">
+      <c r="N101" s="3" t="inlineStr"/>
+      <c r="O101" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_100.html</t>
         </is>
@@ -6038,11 +6544,16 @@
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr">
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_101.html</t>
         </is>
@@ -6090,11 +6601,16 @@
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr"/>
-      <c r="J103" s="3" t="inlineStr"/>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K103" s="3" t="inlineStr"/>
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
-      <c r="N103" s="3" t="inlineStr">
+      <c r="N103" s="3" t="inlineStr"/>
+      <c r="O103" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_102.html</t>
         </is>
@@ -6142,11 +6658,16 @@
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr"/>
       <c r="M104" s="2" t="inlineStr"/>
-      <c r="N104" s="2" t="inlineStr">
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_103.html</t>
         </is>
@@ -6200,21 +6721,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>250.000</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
           <t>2.032.370</t>
         </is>
       </c>
-      <c r="K105" s="3" t="inlineStr">
+      <c r="L105" s="3" t="inlineStr">
         <is>
           <t>91.0%</t>
         </is>
       </c>
-      <c r="L105" s="3" t="inlineStr">
+      <c r="M105" s="3" t="inlineStr">
         <is>
           <t>0.1351748107687824</t>
         </is>
       </c>
-      <c r="M105" s="3" t="inlineStr"/>
-      <c r="N105" s="3" t="inlineStr">
+      <c r="N105" s="3" t="inlineStr"/>
+      <c r="O105" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_104.html</t>
         </is>
@@ -6263,11 +6789,16 @@
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr"/>
       <c r="M106" s="2" t="inlineStr"/>
-      <c r="N106" s="2" t="inlineStr">
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_105.html</t>
         </is>
@@ -6313,11 +6844,16 @@
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr"/>
-      <c r="J107" s="3" t="inlineStr"/>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K107" s="3" t="inlineStr"/>
       <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="3" t="inlineStr"/>
-      <c r="N107" s="3" t="inlineStr">
+      <c r="N107" s="3" t="inlineStr"/>
+      <c r="O107" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_106.html</t>
         </is>
@@ -6361,11 +6897,16 @@
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr"/>
       <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr">
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_107.html</t>
         </is>
@@ -6410,11 +6951,16 @@
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr"/>
-      <c r="J109" s="3" t="inlineStr"/>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K109" s="3" t="inlineStr"/>
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
-      <c r="N109" s="3" t="inlineStr">
+      <c r="N109" s="3" t="inlineStr"/>
+      <c r="O109" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_108.html</t>
         </is>
@@ -6459,11 +7005,16 @@
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr"/>
       <c r="M110" s="2" t="inlineStr"/>
-      <c r="N110" s="2" t="inlineStr">
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_109.html</t>
         </is>
@@ -6508,11 +7059,16 @@
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr"/>
-      <c r="J111" s="3" t="inlineStr"/>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K111" s="3" t="inlineStr"/>
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
-      <c r="N111" s="3" t="inlineStr">
+      <c r="N111" s="3" t="inlineStr"/>
+      <c r="O111" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_110.html</t>
         </is>
@@ -6557,11 +7113,16 @@
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr"/>
       <c r="M112" s="2" t="inlineStr"/>
-      <c r="N112" s="2" t="inlineStr">
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_111.html</t>
         </is>
@@ -6611,11 +7172,16 @@
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr"/>
-      <c r="J113" s="3" t="inlineStr"/>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K113" s="3" t="inlineStr"/>
       <c r="L113" s="3" t="inlineStr"/>
       <c r="M113" s="3" t="inlineStr"/>
-      <c r="N113" s="3" t="inlineStr">
+      <c r="N113" s="3" t="inlineStr"/>
+      <c r="O113" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_112.html</t>
         </is>
@@ -6664,11 +7230,16 @@
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr"/>
       <c r="M114" s="2" t="inlineStr"/>
-      <c r="N114" s="2" t="inlineStr">
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_113.html</t>
         </is>
@@ -6717,11 +7288,16 @@
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr"/>
-      <c r="J115" s="3" t="inlineStr"/>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K115" s="3" t="inlineStr"/>
       <c r="L115" s="3" t="inlineStr"/>
       <c r="M115" s="3" t="inlineStr"/>
-      <c r="N115" s="3" t="inlineStr">
+      <c r="N115" s="3" t="inlineStr"/>
+      <c r="O115" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_114.html</t>
         </is>
@@ -6773,11 +7349,16 @@
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr"/>
       <c r="M116" s="2" t="inlineStr"/>
-      <c r="N116" s="2" t="inlineStr">
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_115.html</t>
         </is>
@@ -6832,23 +7413,28 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>82.431</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K117" s="3" t="e">
+      <c r="L117" s="3" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="L117" s="3" t="inlineStr">
+      <c r="M117" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="M117" s="3" t="inlineStr">
+      <c r="N117" s="3" t="inlineStr">
         <is>
           <t>Nao iniciou em 2024</t>
         </is>
       </c>
-      <c r="N117" s="3" t="inlineStr">
+      <c r="O117" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_116.html</t>
         </is>
@@ -6903,25 +7489,30 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
+          <t>133.754</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
           <t>3.185.533</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr">
+      <c r="L118" s="2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="L118" s="2" t="inlineStr">
+      <c r="M118" s="2" t="inlineStr">
         <is>
           <t>3715.393500000001</t>
         </is>
       </c>
-      <c r="M118" s="2" t="inlineStr">
+      <c r="N118" s="2" t="inlineStr">
         <is>
           <t>36 RAMJ 15-24 em seguimento no ano 2024, pois foi o inicio do piloto</t>
         </is>
       </c>
-      <c r="N118" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_117.html</t>
         </is>
@@ -6974,23 +7565,28 @@
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="J119" s="3" t="e">
-        <v>#VALUE!</v>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>147.227</t>
+        </is>
       </c>
       <c r="K119" s="3" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="L119" s="3" t="inlineStr">
+      <c r="L119" s="3" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
         <is>
           <t>0.061678806032677</t>
         </is>
       </c>
-      <c r="M119" s="3" t="inlineStr">
+      <c r="N119" s="3" t="inlineStr">
         <is>
           <t>dados de distribucao, Hom + Mulh 15-49</t>
         </is>
       </c>
-      <c r="N119" s="3" t="inlineStr">
+      <c r="O119" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_118.html</t>
         </is>
@@ -7045,23 +7641,28 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
+          <t>665.169</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
           <t>todos utentes na US</t>
         </is>
       </c>
-      <c r="K120" s="2" t="e">
+      <c r="L120" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="L120" s="2" t="inlineStr">
+      <c r="M120" s="2" t="inlineStr">
         <is>
           <t>0.6309392820691827</t>
         </is>
       </c>
-      <c r="M120" s="2" t="inlineStr">
+      <c r="N120" s="2" t="inlineStr">
         <is>
           <t>por causa de cobertura de livro de ITS não é possivel calcular um pop. Eligivel</t>
         </is>
       </c>
-      <c r="N120" s="2" t="inlineStr">
+      <c r="O120" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_119.html</t>
         </is>
@@ -7116,25 +7717,30 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>2.579.520</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
           <t>8.159.149</t>
         </is>
       </c>
-      <c r="K121" s="3" t="inlineStr">
+      <c r="L121" s="3" t="inlineStr">
         <is>
           <t>68.6%</t>
         </is>
       </c>
-      <c r="L121" s="3" t="inlineStr">
+      <c r="M121" s="3" t="inlineStr">
         <is>
           <t>0.4605463310123192</t>
         </is>
       </c>
-      <c r="M121" s="3" t="inlineStr">
+      <c r="N121" s="3" t="inlineStr">
         <is>
           <t>dados de distribucao Mulher 15 - 49 anos</t>
         </is>
       </c>
-      <c r="N121" s="3" t="inlineStr">
+      <c r="O121" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_120.html</t>
         </is>
@@ -7189,25 +7795,30 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
+          <t>5.527.092</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
           <t>30.767.054</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr">
+      <c r="L122" s="2" t="inlineStr">
         <is>
           <t>0.8%</t>
         </is>
       </c>
-      <c r="L122" s="2" t="inlineStr">
+      <c r="M122" s="2" t="inlineStr">
         <is>
           <t>21.33839519575633</t>
         </is>
       </c>
-      <c r="M122" s="2" t="inlineStr">
+      <c r="N122" s="2" t="inlineStr">
         <is>
           <t>Novo inicios a PrEP para o ano 2024</t>
         </is>
       </c>
-      <c r="N122" s="2" t="inlineStr">
+      <c r="O122" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_121.html</t>
         </is>
@@ -7262,25 +7873,30 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>7.491.341</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
           <t>7.388.905</t>
         </is>
       </c>
-      <c r="K123" s="3" t="inlineStr">
+      <c r="L123" s="3" t="inlineStr">
         <is>
           <t>21.810947630264565</t>
         </is>
       </c>
-      <c r="L123" s="3" t="inlineStr">
+      <c r="M123" s="3" t="inlineStr">
         <is>
           <t>0.04648415651820172</t>
         </is>
       </c>
-      <c r="M123" s="3" t="inlineStr">
+      <c r="N123" s="3" t="inlineStr">
         <is>
           <t>dados de distribucao Homen 15 - 49 anos</t>
         </is>
       </c>
-      <c r="N123" s="3" t="inlineStr">
+      <c r="O123" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_122.html</t>
         </is>
@@ -7332,11 +7948,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
       <c r="M124" s="2" t="inlineStr"/>
-      <c r="N124" s="2" t="inlineStr">
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_123.html</t>
         </is>
@@ -7388,11 +8009,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J125" s="3" t="inlineStr"/>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K125" s="3" t="inlineStr"/>
       <c r="L125" s="3" t="inlineStr"/>
       <c r="M125" s="3" t="inlineStr"/>
-      <c r="N125" s="3" t="inlineStr">
+      <c r="N125" s="3" t="inlineStr"/>
+      <c r="O125" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_124.html</t>
         </is>
@@ -7440,11 +8066,16 @@
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr"/>
       <c r="M126" s="2" t="inlineStr"/>
-      <c r="N126" s="2" t="inlineStr">
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_125.html</t>
         </is>
@@ -7493,11 +8124,16 @@
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr"/>
-      <c r="J127" s="3" t="inlineStr"/>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K127" s="3" t="inlineStr"/>
       <c r="L127" s="3" t="inlineStr"/>
       <c r="M127" s="3" t="inlineStr"/>
-      <c r="N127" s="3" t="inlineStr">
+      <c r="N127" s="3" t="inlineStr"/>
+      <c r="O127" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_126.html</t>
         </is>
@@ -7546,11 +8182,16 @@
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr"/>
       <c r="M128" s="2" t="inlineStr"/>
-      <c r="N128" s="2" t="inlineStr">
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_127.html</t>
         </is>
@@ -7599,11 +8240,16 @@
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr"/>
-      <c r="J129" s="3" t="inlineStr"/>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K129" s="3" t="inlineStr"/>
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
-      <c r="N129" s="3" t="inlineStr">
+      <c r="N129" s="3" t="inlineStr"/>
+      <c r="O129" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_128.html</t>
         </is>
@@ -7652,11 +8298,16 @@
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr"/>
       <c r="M130" s="2" t="inlineStr"/>
-      <c r="N130" s="2" t="inlineStr">
+      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_129.html</t>
         </is>
@@ -7705,11 +8356,16 @@
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr"/>
-      <c r="J131" s="3" t="inlineStr"/>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K131" s="3" t="inlineStr"/>
       <c r="L131" s="3" t="inlineStr"/>
       <c r="M131" s="3" t="inlineStr"/>
-      <c r="N131" s="3" t="inlineStr">
+      <c r="N131" s="3" t="inlineStr"/>
+      <c r="O131" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_130.html</t>
         </is>
@@ -7757,11 +8413,16 @@
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr"/>
       <c r="M132" s="2" t="inlineStr"/>
-      <c r="N132" s="2" t="inlineStr">
+      <c r="N132" s="2" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_131.html</t>
         </is>
@@ -7809,11 +8470,16 @@
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr"/>
-      <c r="J133" s="3" t="inlineStr"/>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K133" s="3" t="inlineStr"/>
       <c r="L133" s="3" t="inlineStr"/>
       <c r="M133" s="3" t="inlineStr"/>
-      <c r="N133" s="3" t="inlineStr">
+      <c r="N133" s="3" t="inlineStr"/>
+      <c r="O133" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_132.html</t>
         </is>
@@ -7868,23 +8534,28 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
+          <t>48.899</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
           <t>36.171</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
+      <c r="L134" s="2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="L134" s="2" t="e">
+      <c r="M134" s="2" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="M134" s="2" t="inlineStr">
+      <c r="N134" s="2" t="inlineStr">
         <is>
           <t>Carga Viral para VHB nao foi implmentado em 2024</t>
         </is>
       </c>
-      <c r="N134" s="2" t="inlineStr">
+      <c r="O134" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_133.html</t>
         </is>
@@ -7939,25 +8610,30 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>469.080</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
           <t>36.171</t>
         </is>
       </c>
-      <c r="K135" s="3" t="inlineStr">
+      <c r="L135" s="3" t="inlineStr">
         <is>
           <t>89.1%</t>
         </is>
       </c>
-      <c r="L135" s="3" t="inlineStr">
+      <c r="M135" s="3" t="inlineStr">
         <is>
           <t>14.55053042992741</t>
         </is>
       </c>
-      <c r="M135" s="3" t="inlineStr">
+      <c r="N135" s="3" t="inlineStr">
         <is>
           <t>Ainda foi um piloto ate o fim de 2024, em MC tinha 7,615, Nampula 18,706, Sofala 5,917</t>
         </is>
       </c>
-      <c r="N135" s="3" t="inlineStr">
+      <c r="O135" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_134.html</t>
         </is>
@@ -8012,23 +8688,28 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
+          <t>750.350</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
           <t>Pessoas com sinais ou sintomas</t>
         </is>
       </c>
-      <c r="K136" s="2" t="e">
+      <c r="L136" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="L136" s="2" t="inlineStr">
+      <c r="M136" s="2" t="inlineStr">
         <is>
           <t>2.041635729911516</t>
         </is>
       </c>
-      <c r="M136" s="2" t="inlineStr">
+      <c r="N136" s="2" t="inlineStr">
         <is>
           <t>testados para Sifilis no livro de ITS</t>
         </is>
       </c>
-      <c r="N136" s="2" t="inlineStr">
+      <c r="O136" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_135.html</t>
         </is>
@@ -8083,25 +8764,30 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>884.603</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
           <t>134.000</t>
         </is>
       </c>
-      <c r="K137" s="3" t="inlineStr">
+      <c r="L137" s="3" t="inlineStr">
         <is>
           <t>81.8%</t>
         </is>
       </c>
-      <c r="L137" s="3" t="inlineStr">
+      <c r="M137" s="3" t="inlineStr">
         <is>
           <t>8.066636253214423</t>
         </is>
       </c>
-      <c r="M137" s="3" t="inlineStr">
+      <c r="N137" s="3" t="inlineStr">
         <is>
           <t>MG HIV+ na CPN</t>
         </is>
       </c>
-      <c r="N137" s="3" t="inlineStr">
+      <c r="O137" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_136.html</t>
         </is>
@@ -8156,21 +8842,26 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
+          <t>2.786.852</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
           <t>2.111.754</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
+      <c r="L138" s="2" t="inlineStr">
         <is>
           <t>99.0%</t>
         </is>
       </c>
-      <c r="L138" s="2" t="inlineStr">
+      <c r="M138" s="2" t="inlineStr">
         <is>
           <t>1.33270233448056</t>
         </is>
       </c>
-      <c r="M138" s="2" t="inlineStr"/>
-      <c r="N138" s="2" t="inlineStr">
+      <c r="N138" s="2" t="inlineStr"/>
+      <c r="O138" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_137.html</t>
         </is>
@@ -8222,11 +8913,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J139" s="3" t="inlineStr"/>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K139" s="3" t="inlineStr"/>
       <c r="L139" s="3" t="inlineStr"/>
       <c r="M139" s="3" t="inlineStr"/>
-      <c r="N139" s="3" t="inlineStr">
+      <c r="N139" s="3" t="inlineStr"/>
+      <c r="O139" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_138.html</t>
         </is>
@@ -8278,11 +8974,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr"/>
       <c r="M140" s="2" t="inlineStr"/>
-      <c r="N140" s="2" t="inlineStr">
+      <c r="N140" s="2" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_139.html</t>
         </is>
@@ -8336,17 +9037,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
           <t>Mulher Lactante  e pacientes HIV+                                                                                                                                                                                  ESMI</t>
         </is>
       </c>
-      <c r="K141" s="3" t="inlineStr">
+      <c r="L141" s="3" t="inlineStr">
         <is>
           <t>Todas as US AJUDA (149) Manica (51), Niassa(18), Sofala (47) e Tete (33)</t>
         </is>
       </c>
-      <c r="L141" s="3" t="inlineStr"/>
       <c r="M141" s="3" t="inlineStr"/>
-      <c r="N141" s="3" t="inlineStr">
+      <c r="N141" s="3" t="inlineStr"/>
+      <c r="O141" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_140.html</t>
         </is>
@@ -8395,11 +9101,16 @@
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr"/>
       <c r="M142" s="2" t="inlineStr"/>
-      <c r="N142" s="2" t="inlineStr">
+      <c r="N142" s="2" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_141.html</t>
         </is>
@@ -8447,11 +9158,16 @@
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr"/>
-      <c r="J143" s="3" t="inlineStr"/>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K143" s="3" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr"/>
       <c r="M143" s="3" t="inlineStr"/>
-      <c r="N143" s="3" t="inlineStr">
+      <c r="N143" s="3" t="inlineStr"/>
+      <c r="O143" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_142.html</t>
         </is>
@@ -8499,11 +9215,16 @@
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr"/>
       <c r="M144" s="2" t="inlineStr"/>
-      <c r="N144" s="2" t="inlineStr">
+      <c r="N144" s="2" t="inlineStr"/>
+      <c r="O144" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_143.html</t>
         </is>
@@ -8552,11 +9273,16 @@
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr"/>
-      <c r="J145" s="3" t="inlineStr"/>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K145" s="3" t="inlineStr"/>
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="3" t="inlineStr"/>
-      <c r="N145" s="3" t="inlineStr">
+      <c r="N145" s="3" t="inlineStr"/>
+      <c r="O145" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_144.html</t>
         </is>
@@ -8605,11 +9331,16 @@
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr"/>
       <c r="M146" s="2" t="inlineStr"/>
-      <c r="N146" s="2" t="inlineStr">
+      <c r="N146" s="2" t="inlineStr"/>
+      <c r="O146" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_145.html</t>
         </is>
@@ -8657,11 +9388,16 @@
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr"/>
-      <c r="J147" s="3" t="inlineStr"/>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K147" s="3" t="inlineStr"/>
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
-      <c r="N147" s="3" t="inlineStr">
+      <c r="N147" s="3" t="inlineStr"/>
+      <c r="O147" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_146.html</t>
         </is>
@@ -8709,11 +9445,16 @@
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr"/>
       <c r="M148" s="2" t="inlineStr"/>
-      <c r="N148" s="2" t="inlineStr">
+      <c r="N148" s="2" t="inlineStr"/>
+      <c r="O148" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_147.html</t>
         </is>
@@ -8761,11 +9502,16 @@
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr"/>
-      <c r="J149" s="3" t="inlineStr"/>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K149" s="3" t="inlineStr"/>
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
-      <c r="N149" s="3" t="inlineStr">
+      <c r="N149" s="3" t="inlineStr"/>
+      <c r="O149" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_148.html</t>
         </is>
@@ -8814,11 +9560,16 @@
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr"/>
       <c r="M150" s="2" t="inlineStr"/>
-      <c r="N150" s="2" t="inlineStr">
+      <c r="N150" s="2" t="inlineStr"/>
+      <c r="O150" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_149.html</t>
         </is>
@@ -8867,11 +9618,16 @@
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr"/>
-      <c r="J151" s="3" t="inlineStr"/>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K151" s="3" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr"/>
       <c r="M151" s="3" t="inlineStr"/>
-      <c r="N151" s="3" t="inlineStr">
+      <c r="N151" s="3" t="inlineStr"/>
+      <c r="O151" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_150.html</t>
         </is>
@@ -8920,11 +9676,16 @@
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr"/>
       <c r="M152" s="2" t="inlineStr"/>
-      <c r="N152" s="2" t="inlineStr">
+      <c r="N152" s="2" t="inlineStr"/>
+      <c r="O152" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_151.html</t>
         </is>
@@ -8979,21 +9740,26 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>3.674.196</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
           <t>266.240</t>
         </is>
       </c>
-      <c r="K153" s="3" t="inlineStr">
+      <c r="L153" s="3" t="inlineStr">
         <is>
           <t>93.2%</t>
         </is>
       </c>
-      <c r="L153" s="3" t="inlineStr">
+      <c r="M153" s="3" t="inlineStr">
         <is>
           <t>14.80509942741094</t>
         </is>
       </c>
-      <c r="M153" s="3" t="inlineStr"/>
-      <c r="N153" s="3" t="inlineStr">
+      <c r="N153" s="3" t="inlineStr"/>
+      <c r="O153" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_152.html</t>
         </is>
@@ -9045,11 +9811,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr"/>
       <c r="M154" s="2" t="inlineStr"/>
-      <c r="N154" s="2" t="inlineStr">
+      <c r="N154" s="2" t="inlineStr"/>
+      <c r="O154" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_153.html</t>
         </is>
@@ -9101,11 +9872,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="J155" s="3" t="inlineStr"/>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="K155" s="3" t="inlineStr"/>
       <c r="L155" s="3" t="inlineStr"/>
       <c r="M155" s="3" t="inlineStr"/>
-      <c r="N155" s="3" t="inlineStr">
+      <c r="N155" s="3" t="inlineStr"/>
+      <c r="O155" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_154.html</t>
         </is>

--- a/hiv/catalogo_HIV.xlsx
+++ b/hiv/catalogo_HIV.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O155"/>
+  <dimension ref="A1:R155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -453,13 +453,16 @@
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="35" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="35" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -505,35 +508,50 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Etapas chave para a implementação</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Riscos e limitações</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Possíveis factores associados aos riscos</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Ano de início</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Gastos em 2024 (USD)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Pop. elegível</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Cobertura</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Custo por unidade</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>URL da Ficha</t>
         </is>
@@ -576,33 +594,36 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>200.000</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>2.477.000</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>82.0%</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>0.09841212043675299</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_01.html</t>
         </is>
@@ -651,19 +672,34 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>Planejamento e execução de formações</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Resistência dos profissionais à formação</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Falta de motivação e tempo disponível</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_02.html</t>
         </is>
@@ -714,19 +750,34 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de suprimentos</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas na entrega de suprimentos</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Infraestrutura inadequada em áreas remotas</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_03.html</t>
         </is>
@@ -773,17 +824,32 @@
           <t>Recursos humanos qualificados</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Formação e capacitação dos conselheiros</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
+          <t>Monitoramento continuo da adesão</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Falta de recursos e resistência cultural</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_04.html</t>
         </is>
@@ -831,17 +897,32 @@
           <t>Materiais de apoio</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Realização de visitas domiciliares e seguimento</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+          <t>Adesão baixa em populações vulneráveis</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Estigmatização e discriminação social</t>
+        </is>
+      </c>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_05.html</t>
         </is>
@@ -889,17 +970,24 @@
           <t>contratos de impressão</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Impressão, distribução</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_06.html</t>
         </is>
@@ -946,17 +1034,32 @@
           <t>Formação e materiais de apoio</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Programação de sessões de capacitação</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+          <t>Rotatividade de pessoal</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas e falta de motivação</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_07.html</t>
         </is>
@@ -1003,17 +1106,28 @@
           <t>equipamento de gravação, tempo, plataform de telesaude</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
+          <t>sem plataforma</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_08.html</t>
         </is>
@@ -1061,17 +1175,32 @@
           <t>Recursos humanos e materiais de apoio</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Formação de conselheiros e seguimento de utentes</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t>Estigmatização social e resistência à consulta</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Desigualdade de gênero e desapego à saúde</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_09.html</t>
         </is>
@@ -1119,17 +1248,32 @@
           <t>Profissionais de saúde qualificados</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Implementação de rastreios regulares</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+          <t>Baixa participação devido ao estigma mental</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Lacunas no conhecimento sobre saúde mental</t>
+        </is>
+      </c>
       <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_10.html</t>
         </is>
@@ -1177,17 +1321,32 @@
           <t>Materiais educativos e formações</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Sessões com as famílias</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>Dificuldades emocionais e de aceitação nas famílias</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Falta de suporte familiar e social</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_11.html</t>
         </is>
@@ -1235,17 +1394,32 @@
           <t>Programa de certificação e avaliação</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Realização de auditorias e treinamentos</t>
+        </is>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
+          <t>Resistência para mudança de cultura nos serviços de saúde</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Tradições locais e sensibilização inadequada</t>
+        </is>
+      </c>
       <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_12.html</t>
         </is>
@@ -1293,17 +1467,32 @@
           <t>Recursos e tecnologia para avaliação</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Revisão e treino de pessoal</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+          <t>Falta de recursos financeiros e humanos</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Condições econômicas locais desfavoráveis</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_13.html</t>
         </is>
@@ -1351,17 +1540,32 @@
           <t>Formadores e recursos informativos</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Criação e distribuição do guia</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
+          <t>Falta de engajamento dos pares</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Desinteresse ou desconexão da comunidade</t>
+        </is>
+      </c>
       <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_14.html</t>
         </is>
@@ -1411,31 +1615,46 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>Campanhas de sensibilização</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Resistência à testagem em comunidades</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Desinformação e medo do diagnóstico</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>4.938.632</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>254.946</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>50.22630007782692</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>0.385679676495397</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_15.html</t>
         </is>
@@ -1485,31 +1704,46 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
+          <t>Implementação de testes em massa</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas na distribuição de testes</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Acesso limitado às áreas remotas</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t>2001</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>6.887.521</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>254.946</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>50.22630007782692</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>0.537877067032586</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_16.html</t>
         </is>
@@ -1556,17 +1790,32 @@
           <t>Capacidade de gestão e coordenação</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Supervisão e avaliação contínua</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
+          <t>Dificuldade em manter uma força de trabalho estável</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Desafios administrativos e de recursos</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_17.html</t>
         </is>
@@ -1613,17 +1862,32 @@
           <t>Formação e supervisão de pessoal</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Coordenação entre unidades e implementação</t>
+        </is>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
+          <t>Alta rotatividade do pessoal</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Condições de trabalho e baixos incentivos</t>
+        </is>
+      </c>
       <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_18.html</t>
         </is>
@@ -1671,17 +1935,32 @@
           <t>Materiais e reagentes para teste</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Implementação de campanhas de sensibilização</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+          <t>Resistência do público a realizar testes</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Cultura local e desinformação</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_19.html</t>
         </is>
@@ -1729,17 +2008,32 @@
           <t>Recursos humanos e materiais de apoio</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Formação de pessoal e distribuição de medicamentos</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
+          <t>Baixa adesão devido ao estigma e desinformação</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Falta de informação sobre a PrEP e resistência cultural</t>
+        </is>
+      </c>
       <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_20.html</t>
         </is>
@@ -1787,17 +2081,32 @@
           <t>Treinamento e materiais informativos</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Identificação de casos e seguimento de contatos</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
+          <t>Dificuldades na identificação de contatos devido à estigmatização</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Resistência social e medo de revelação de status</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_21.html</t>
         </is>
@@ -1844,17 +2153,24 @@
           <t>contratos de impressão</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Impressão, distribução</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="3" t="inlineStr"/>
       <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_22.html</t>
         </is>
@@ -1901,17 +2217,32 @@
           <t>Materiais de formação e recursos humanos</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Realização de sessões de formação e capacitação</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
+          <t>Falta de adesão por parte dos profissionais de saúde</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas e falta de motivação entre os profissionais</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_23.html</t>
         </is>
@@ -1958,17 +2289,28 @@
           <t>equipamento de gravação, tempo, plataform de telesaude</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
+          <t>sem plataforma</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr"/>
       <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_24.html</t>
         </is>
@@ -2015,17 +2357,32 @@
           <t>Recursos para capacitação e equipamentos</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Programação de treinamentos e supervisão</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
+          <t>Resistência à mudança de práticas estabelecidas</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Tradições locais e falta de apoio institucional</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_25.html</t>
         </is>
@@ -2072,17 +2429,32 @@
           <t>Materiais de formação e acompanhamento</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Avaliação e feedback contínuo</t>
+        </is>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
+          <t>Dificuldades em manter um padrão de qualidade</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Falta de recursos e suporte institucional</t>
+        </is>
+      </c>
       <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_26.html</t>
         </is>
@@ -2129,17 +2501,32 @@
           <t>Recursos humanos qualificados e materiais</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Treinamento e supervisão contínua</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+          <t>Dificuldades na implementação devido a falta de pessoal</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Alta rotatividade de profissionais e falta de incentivos</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_27.html</t>
         </is>
@@ -2187,17 +2574,32 @@
           <t>Materiais de apoio e reagentes para teste</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Implementação de protocolos de acolhimento</t>
+        </is>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
+          <t>Resistência por parte dos utentes em se submeter ao teste</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Estigma associado ao HIV e falta de privacidade</t>
+        </is>
+      </c>
       <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_28.html</t>
         </is>
@@ -2245,17 +2647,32 @@
           <t>Recursos e sensibilização nas comunidades</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Campanhas de sensibilização e acompanhamento</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
+          <t>Baixa procura devido ao medo de diagnóstico</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Desinformação e preconceito social</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_29.html</t>
         </is>
@@ -2303,17 +2720,32 @@
           <t>Recursos para tratamento e capacitação</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Implementação de protocolos de atendimento</t>
+        </is>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
+          <t>Dificuldades no acesso a tratamento em áreas remotas</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Desigualdade de acesso a serviços de saúde</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_30.html</t>
         </is>
@@ -2361,17 +2793,32 @@
           <t>Materiais e equipamentos para testes</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Implementação de campanhas de testagem</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
+          <t>Resistência ao teste por medo do resultado</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Estigma e falta de informação nas comunidades</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_31.html</t>
         </is>
@@ -2421,31 +2868,46 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
+          <t>Monitoramento contínuo do estoque e distribuição</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Falta de recursos financeiros para compra de insumos</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Desigualdade no acesso a financiamento e doações</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>61.567.205</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>2.300.000</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t>84.1%</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>31.82389388066507</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr"/>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_32.html</t>
         </is>
@@ -2494,19 +2956,34 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
+          <t>Planejamento e execução de treinamentos</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Falta de adesão dos profissionais às novas práticas</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Resistência à mudança e falta de suporte institucional</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_33.html</t>
         </is>
@@ -2555,19 +3032,34 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de suprimentos</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Dificuldades na gestão de inventário e distribuição</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Falta de controle e supervisão adequados</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr"/>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N35" s="3" t="inlineStr"/>
-      <c r="O35" s="3" t="inlineStr">
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_34.html</t>
         </is>
@@ -2616,19 +3108,34 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
+          <t>Planejamento e execução de reuniões híbridas</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>Dificuldade em engajar participantes devido à falta de tecnologia</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Diferenças de acesso à tecnologia entre as comunidades</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_35.html</t>
         </is>
@@ -2675,17 +3182,32 @@
           <t>Recursos humanos qualificados e materiais de apoio</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Realização de oficinas de trabalho</t>
+        </is>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr"/>
+          <t>Resistência à mudança de práticas estabelecidas</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Cultura organizacional nas unidades de saúde</t>
+        </is>
+      </c>
       <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr">
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_36.html</t>
         </is>
@@ -2733,17 +3255,32 @@
           <t>Equipe de monitores e ferramentas de avaliação</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Planejamento e execução de visitas regulares</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t>Dificuldades logísticas na coordenação das visitas</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Falta de transporte e recursos para a equipe de monitoramento</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_37.html</t>
         </is>
@@ -2790,17 +3327,32 @@
           <t>Materiais de formação e logística</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Implementação de oficinas provinciais</t>
+        </is>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr"/>
+          <t>Baixa participação devido a compromissos locais</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Conflitos de agenda e falta de interesse local</t>
+        </is>
+      </c>
       <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="3" t="inlineStr">
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_38.html</t>
         </is>
@@ -2848,17 +3400,32 @@
           <t>Materiais educativos e recursos humanos</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Criação de campanhas de sensibilização</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
+          <t>Dificuldade em mudar normas sociais que desencorajam o engajamento</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Estigmatização e resistência cultural</t>
+        </is>
+      </c>
       <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_39.html</t>
         </is>
@@ -2905,17 +3472,32 @@
           <t>Recursos financeiros para recrutamento e treinamento</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Recrutamento e treinamento contínuo</t>
+        </is>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr"/>
+          <t>Alta rotatividade de profissionais de saúde</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Condições de trabalho e falta de incentivos</t>
+        </is>
+      </c>
       <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="3" t="inlineStr"/>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N41" s="3" t="inlineStr"/>
-      <c r="O41" s="3" t="inlineStr">
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_40.html</t>
         </is>
@@ -2962,17 +3544,24 @@
           <t>contratos de impressão</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Impressão, distribução</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_41.html</t>
         </is>
@@ -3019,17 +3608,24 @@
           <t>contratos de impressão</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Impressão, distribução</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="3" t="inlineStr"/>
       <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N43" s="3" t="inlineStr"/>
-      <c r="O43" s="3" t="inlineStr">
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_42.html</t>
         </is>
@@ -3077,17 +3673,32 @@
           <t>Documentos e formações</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Realizar sessões de atualização</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
+          <t>Resistência a novas diretrizes</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Falta de cumprimento das normas</t>
+        </is>
+      </c>
       <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_43.html</t>
         </is>
@@ -3134,17 +3745,32 @@
           <t>Recursos humanos e materiais necessários</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Implementação de monitoramentos</t>
+        </is>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr"/>
+          <t>Dificuldades em logística de material</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Estigmas e crenças em comunidades locais</t>
+        </is>
+      </c>
       <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N45" s="3" t="inlineStr"/>
-      <c r="O45" s="3" t="inlineStr">
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_44.html</t>
         </is>
@@ -3192,17 +3818,32 @@
           <t>Acompanhamento e suporte dos profissionais de saúde</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Monitoramento da adesão e seguimento dos utentes</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>Desmotivação dos utentes devido a efeitos colaterais</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Falta de informação e apoio emocional ao paciente</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_45.html</t>
         </is>
@@ -3249,17 +3890,32 @@
           <t>Materiais e recursos para oficinas</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Criação de grupos de apoio e oficinas de sensibilização</t>
+        </is>
+      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr"/>
+          <t>Dificuldade em manter a participação ativa</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Desinteresse por parte dos utentes e falta de continuidade</t>
+        </is>
+      </c>
       <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N47" s="3" t="inlineStr"/>
-      <c r="O47" s="3" t="inlineStr">
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_46.html</t>
         </is>
@@ -3307,17 +3963,32 @@
           <t>Recursos humanos qualificados e materiais de apoio</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Treinamento e integração dos serviços</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
+          <t>Resistência à mudança de abordagem de serviços de saúde</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Barreiras institucionais e falta de coordenação entre serviços</t>
+        </is>
+      </c>
       <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_47.html</t>
         </is>
@@ -3364,17 +4035,32 @@
           <t>Materiais de formação e recursos humanos para capacitação</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>Treinamento de equipes e implementação de protocolos</t>
+        </is>
+      </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr"/>
+          <t>Resistência à mudança de práticas estabelecidas</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Cultura organizacional nas unidades de saúde</t>
+        </is>
+      </c>
       <c r="L49" s="3" t="inlineStr"/>
-      <c r="M49" s="3" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N49" s="3" t="inlineStr"/>
-      <c r="O49" s="3" t="inlineStr">
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_48.html</t>
         </is>
@@ -3422,17 +4108,32 @@
           <t>Materiais educativos e formação contínua</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Sessões de formação e acompanhamento prático</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
+          <t>Falta de adesão dos clínicos à formação</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Desinteresse ou falta de tempo dos profissionais</t>
+        </is>
+      </c>
       <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_49.html</t>
         </is>
@@ -3480,17 +4181,32 @@
           <t>Equipe de monitores e ferramentas de avaliação</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Planejamento e execução de visitas regulares</t>
+        </is>
+      </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr"/>
+          <t>Dificuldades logísticas na coordenação das visitas</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Falta de transporte e recursos para a equipe de monitoramento</t>
+        </is>
+      </c>
       <c r="L51" s="3" t="inlineStr"/>
-      <c r="M51" s="3" t="inlineStr"/>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N51" s="3" t="inlineStr"/>
-      <c r="O51" s="3" t="inlineStr">
+      <c r="O51" s="3" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr"/>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_50.html</t>
         </is>
@@ -3537,17 +4253,28 @@
           <t>equipamento de gravação, tempo, plataform de telesaude</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
+          <t>sem plataforma</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_51.html</t>
         </is>
@@ -3597,35 +4324,50 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
+          <t>Implementação de protocolos de teste</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>Falta de insumos e equipamentos para realização dos testes</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Desigualdade de acesso a recursos e insumos</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="M53" s="3" t="inlineStr">
         <is>
           <t>3.850.406</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="N53" s="3" t="inlineStr">
         <is>
           <t>245.610</t>
         </is>
       </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="O53" s="3" t="inlineStr">
         <is>
           <t>51.7%</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr">
+      <c r="P53" s="3" t="inlineStr">
         <is>
           <t>30.33081522210056</t>
         </is>
       </c>
-      <c r="N53" s="3" t="inlineStr">
+      <c r="Q53" s="3" t="inlineStr">
         <is>
           <t>Dados de SESP</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
+      <c r="R53" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_52.html</t>
         </is>
@@ -3675,31 +4417,46 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
+          <t>Monitoramento contínuo e seguimento de pacientes</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Resistência dos pacientes em realizar os testes</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Estigmatização e falta de informação sobre a carga viral</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>4.007.197</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>2.032.370</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>81.1%</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>2.430270082098699</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr">
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_53.html</t>
         </is>
@@ -3749,31 +4506,46 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
+          <t>Distribuição e monitoramento do uso dos ARVs</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>Falta de insumos e dificuldade no armazenamento adequado</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Logística ineficaz e desinformação sobre a disponibilidade</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="M55" s="3" t="inlineStr">
         <is>
           <t>3.993.859</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="N55" s="3" t="inlineStr">
         <is>
           <t>177.000</t>
         </is>
       </c>
-      <c r="L55" s="3" t="inlineStr">
+      <c r="O55" s="3" t="inlineStr">
         <is>
           <t>55.2%</t>
         </is>
       </c>
-      <c r="M55" s="3" t="inlineStr">
+      <c r="P55" s="3" t="inlineStr">
         <is>
           <t>40.8587316200843</t>
         </is>
       </c>
-      <c r="N55" s="3" t="inlineStr"/>
-      <c r="O55" s="3" t="inlineStr">
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_54.html</t>
         </is>
@@ -3823,19 +4595,34 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de suprimentos pediátricos</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas na entrega de medicamentos</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Infraestrutura inadequada em áreas remotas</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr">
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_55.html</t>
         </is>
@@ -3885,19 +4672,34 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
+          <t>Planejamento e execução de formações em saúde</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Resistência à mudança e falta de adesão às formações</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Dificuldades de acesso a informações e materiais</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr"/>
-      <c r="L57" s="3" t="inlineStr"/>
-      <c r="M57" s="3" t="inlineStr"/>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N57" s="3" t="inlineStr"/>
-      <c r="O57" s="3" t="inlineStr">
+      <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr"/>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_56.html</t>
         </is>
@@ -3944,17 +4746,32 @@
           <t>Recursos financeiros para recrutamento e treinamento</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Recrutamento e capacitação contínua</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
+          <t>Alta rotatividade de profissionais de saúde</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Condições de trabalho e falta de incentivos</t>
+        </is>
+      </c>
       <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr">
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_57.html</t>
         </is>
@@ -4001,17 +4818,32 @@
           <t>Recursos humanos qualificados e materiais de apoio</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Treinamento e supervisão de pessoal</t>
+        </is>
+      </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr"/>
+          <t>Dificuldade em manter a continuidade do suporte</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Falta de formação especializada e recursos limitados</t>
+        </is>
+      </c>
       <c r="L59" s="3" t="inlineStr"/>
-      <c r="M59" s="3" t="inlineStr"/>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N59" s="3" t="inlineStr"/>
-      <c r="O59" s="3" t="inlineStr">
+      <c r="O59" s="3" t="inlineStr"/>
+      <c r="P59" s="3" t="inlineStr"/>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_58.html</t>
         </is>
@@ -4059,17 +4891,32 @@
           <t>Recursos para capacitação e acompanhamento</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Campanhas de sensibilização e monitoramento de progresso</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr"/>
+          <t>Dificuldade em engajar as mães devido a barreiras sociais</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Estigmatização e falta de apoio comunitário</t>
+        </is>
+      </c>
       <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr">
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_59.html</t>
         </is>
@@ -4116,17 +4963,24 @@
           <t>contratos de impressão</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr"/>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Impressão, distribução</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="3" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr"/>
-      <c r="M61" s="3" t="inlineStr"/>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N61" s="3" t="inlineStr"/>
-      <c r="O61" s="3" t="inlineStr">
+      <c r="O61" s="3" t="inlineStr"/>
+      <c r="P61" s="3" t="inlineStr"/>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_60.html</t>
         </is>
@@ -4173,17 +5027,32 @@
           <t>Materiais de formação e recursos humanos</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Treinamentos regulares e feedback contínuo</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr"/>
+          <t>Resistência à mudança de normas e práticas estabelecidas</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Falta de engajamento da comunidade e resistência cultural</t>
+        </is>
+      </c>
       <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr">
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_61.html</t>
         </is>
@@ -4230,17 +5099,28 @@
           <t>equipamento de gravação, tempo, plataform de telesaude</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
+          <t>sem plataforma</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr"/>
       <c r="L63" s="3" t="inlineStr"/>
-      <c r="M63" s="3" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N63" s="3" t="inlineStr"/>
-      <c r="O63" s="3" t="inlineStr">
+      <c r="O63" s="3" t="inlineStr"/>
+      <c r="P63" s="3" t="inlineStr"/>
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_62.html</t>
         </is>
@@ -4290,33 +5170,48 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
+          <t>Implementação de protocolos de teste</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Falta de insumos e equipamentos adequados</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Desigualdade no acesso a recursos de saúde</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>509.142</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t>158.532</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="M64" s="2" t="e">
+      <c r="P64" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="Q64" s="2" t="inlineStr">
         <is>
           <t>264541 novos inicios e 175826 reinicios</t>
         </is>
       </c>
-      <c r="O64" s="2" t="inlineStr">
+      <c r="R64" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_63.html</t>
         </is>
@@ -4366,27 +5261,42 @@
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
+          <t>Monitoramento do estoque e distribuição</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas na distribuição de medicamentos</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Falta de infraestrutura de transporte</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="J65" s="3" t="inlineStr">
+      <c r="M65" s="3" t="inlineStr">
         <is>
           <t>752.995</t>
         </is>
       </c>
-      <c r="K65" s="3" t="inlineStr">
+      <c r="N65" s="3" t="inlineStr">
         <is>
           <t>158.532</t>
         </is>
       </c>
-      <c r="L65" s="3" t="inlineStr">
+      <c r="O65" s="3" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="M65" s="3" t="inlineStr"/>
-      <c r="N65" s="3" t="inlineStr"/>
-      <c r="O65" s="3" t="inlineStr">
+      <c r="P65" s="3" t="inlineStr"/>
+      <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_64.html</t>
         </is>
@@ -4436,27 +5346,42 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
+          <t>Implementação de protocolos de tratamento</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Resistência ao tratamento devido a estigmas sociais</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Falta de informação e apoio psicossocial</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>2.000.618</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>158.532</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>15.2%</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr"/>
-      <c r="O66" s="2" t="inlineStr">
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_65.html</t>
         </is>
@@ -4504,17 +5429,32 @@
           <t>Recursos para formação e capacitação de profissionais</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Realização de treinamentos e workshops</t>
+        </is>
+      </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr"/>
+          <t>Falta de adesão dos profissionais às formações</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>Desinteresse ou falta de tempo dos profissionais</t>
+        </is>
+      </c>
       <c r="L67" s="3" t="inlineStr"/>
-      <c r="M67" s="3" t="inlineStr"/>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N67" s="3" t="inlineStr"/>
-      <c r="O67" s="3" t="inlineStr">
+      <c r="O67" s="3" t="inlineStr"/>
+      <c r="P67" s="3" t="inlineStr"/>
+      <c r="Q67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_66.html</t>
         </is>
@@ -4562,17 +5502,32 @@
           <t>Equipe de monitores e ferramentas de avaliação</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Planejamento e execução de visitas regulares</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr"/>
+          <t>Dificuldades logísticas na coordenação das visitas</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Falta de transporte e recursos para a equipe de monitoramento</t>
+        </is>
+      </c>
       <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr"/>
-      <c r="O68" s="2" t="inlineStr">
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_67.html</t>
         </is>
@@ -4620,17 +5575,32 @@
           <t>Materiais e recursos para expansão de serviços</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Implementação de protocolos de tratamento</t>
+        </is>
+      </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr"/>
+          <t>Dificuldades em obter equipamentos necessários para o tratamento</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Falta de financiamento e apoio institucional</t>
+        </is>
+      </c>
       <c r="L69" s="3" t="inlineStr"/>
-      <c r="M69" s="3" t="inlineStr"/>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N69" s="3" t="inlineStr"/>
-      <c r="O69" s="3" t="inlineStr">
+      <c r="O69" s="3" t="inlineStr"/>
+      <c r="P69" s="3" t="inlineStr"/>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_68.html</t>
         </is>
@@ -4678,17 +5648,32 @@
           <t>Recursos humanos e materiais necessários para a implementação</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Monitoramento da qualidade dos serviços</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr"/>
+          <t>Falta de pessoal e alta demanda por serviços</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Desigualdade no acesso a serviços de saúde</t>
+        </is>
+      </c>
       <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr">
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_69.html</t>
         </is>
@@ -4736,17 +5721,32 @@
           <t>Recursos para capacitação e materiais de apoio</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Treinamento e supervisão de pessoal</t>
+        </is>
+      </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K71" s="3" t="inlineStr"/>
+          <t>Resistência à integração de serviços de saúde</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Barreiras institucionais e falta de coordenação</t>
+        </is>
+      </c>
       <c r="L71" s="3" t="inlineStr"/>
-      <c r="M71" s="3" t="inlineStr"/>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N71" s="3" t="inlineStr"/>
-      <c r="O71" s="3" t="inlineStr">
+      <c r="O71" s="3" t="inlineStr"/>
+      <c r="P71" s="3" t="inlineStr"/>
+      <c r="Q71" s="3" t="inlineStr"/>
+      <c r="R71" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_70.html</t>
         </is>
@@ -4794,17 +5794,32 @@
           <t>Materiais de formação e recursos humanos para capacitação</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Realização de formações regulares e feedback contínuo</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr"/>
+          <t>Dificuldade em manter o engajamento dos profissionais</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Falta de motivação e apoio contínuo</t>
+        </is>
+      </c>
       <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr"/>
-      <c r="O72" s="2" t="inlineStr">
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_71.html</t>
         </is>
@@ -4852,17 +5867,32 @@
           <t>Materiais de rastreio e formação de pessoal</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr"/>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>Implementação de campanhas de rastreio</t>
+        </is>
+      </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="inlineStr"/>
+          <t>Resistência das mulheres a realizar exames</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>Estigmas sociais e falta de sensibilização sobre a importância do rastreio</t>
+        </is>
+      </c>
       <c r="L73" s="3" t="inlineStr"/>
-      <c r="M73" s="3" t="inlineStr"/>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N73" s="3" t="inlineStr"/>
-      <c r="O73" s="3" t="inlineStr">
+      <c r="O73" s="3" t="inlineStr"/>
+      <c r="P73" s="3" t="inlineStr"/>
+      <c r="Q73" s="3" t="inlineStr"/>
+      <c r="R73" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_72.html</t>
         </is>
@@ -4909,17 +5939,32 @@
           <t>Recursos para reuniões e formadores</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Planejamento e execução de reuniões</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr"/>
+          <t>Resistência à participação dos profissionais de saúde</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Falta de interesse e desinformação sobre a importância das reuniões</t>
+        </is>
+      </c>
       <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr">
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_73.html</t>
         </is>
@@ -4966,17 +6011,32 @@
           <t>Materiais de formação e equipamentos para treinamento</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>Implementação de sessões de treinamento</t>
+        </is>
+      </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr"/>
+          <t>Dificuldades em manter a qualidade das formações</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>Falta de profissionais qualificados para ministrar os treinamentos</t>
+        </is>
+      </c>
       <c r="L75" s="3" t="inlineStr"/>
-      <c r="M75" s="3" t="inlineStr"/>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N75" s="3" t="inlineStr"/>
-      <c r="O75" s="3" t="inlineStr">
+      <c r="O75" s="3" t="inlineStr"/>
+      <c r="P75" s="3" t="inlineStr"/>
+      <c r="Q75" s="3" t="inlineStr"/>
+      <c r="R75" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_74.html</t>
         </is>
@@ -5024,17 +6084,32 @@
           <t>Equipamentos para monitoramento e recursos humanos</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Implementação de protocolos de monitoria</t>
+        </is>
+      </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
+          <t>Baixa adesão dos pacientes à monitoria</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Estigmas associados à testagem e monitoramento de HIV</t>
+        </is>
+      </c>
       <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr"/>
-      <c r="O76" s="2" t="inlineStr">
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_75.html</t>
         </is>
@@ -5082,17 +6157,32 @@
           <t>Equipamentos m-PIMA e formação de pessoal</t>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>Treinamento e implementação em campo</t>
+        </is>
+      </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr"/>
+          <t>Dificuldades logísticas na implementação em áreas remotas</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>Falta de infraestrutura e recursos de transporte</t>
+        </is>
+      </c>
       <c r="L77" s="3" t="inlineStr"/>
-      <c r="M77" s="3" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N77" s="3" t="inlineStr"/>
-      <c r="O77" s="3" t="inlineStr">
+      <c r="O77" s="3" t="inlineStr"/>
+      <c r="P77" s="3" t="inlineStr"/>
+      <c r="Q77" s="3" t="inlineStr"/>
+      <c r="R77" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_76.html</t>
         </is>
@@ -5140,17 +6230,32 @@
           <t>Materiais de avaliação e recursos humanos</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Implementação de avaliações regulares</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr"/>
+          <t>Falta de insumos e reagentes para testes</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Desigualdade no acesso a testes e insumos</t>
+        </is>
+      </c>
       <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr"/>
-      <c r="O78" s="2" t="inlineStr">
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_77.html</t>
         </is>
@@ -5198,17 +6303,24 @@
           <t>contratos de impressão</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr"/>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>Impressão, distribução</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr"/>
       <c r="K79" s="3" t="inlineStr"/>
       <c r="L79" s="3" t="inlineStr"/>
-      <c r="M79" s="3" t="inlineStr"/>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N79" s="3" t="inlineStr"/>
-      <c r="O79" s="3" t="inlineStr">
+      <c r="O79" s="3" t="inlineStr"/>
+      <c r="P79" s="3" t="inlineStr"/>
+      <c r="Q79" s="3" t="inlineStr"/>
+      <c r="R79" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_78.html</t>
         </is>
@@ -5256,17 +6368,32 @@
           <t>Recursos para aquisição de painéis de proficiência</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Monitoramento e reposição de painéis</t>
+        </is>
+      </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr"/>
+          <t>Falta de recursos financeiros para aquisição de painéis</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Dependência de doações e financiamentos externos</t>
+        </is>
+      </c>
       <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr">
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_79.html</t>
         </is>
@@ -5314,17 +6441,32 @@
           <t>Equipamentos e formação para uso de m-PIMA e GeneXpert</t>
         </is>
       </c>
-      <c r="I81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>Implementação e supervisão do uso de equipamentos</t>
+        </is>
+      </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="inlineStr"/>
+          <t>Resistência à adoção de novas tecnologias</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>Falta de formação e apoio técnico contínuo</t>
+        </is>
+      </c>
       <c r="L81" s="3" t="inlineStr"/>
-      <c r="M81" s="3" t="inlineStr"/>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N81" s="3" t="inlineStr"/>
-      <c r="O81" s="3" t="inlineStr">
+      <c r="O81" s="3" t="inlineStr"/>
+      <c r="P81" s="3" t="inlineStr"/>
+      <c r="Q81" s="3" t="inlineStr"/>
+      <c r="R81" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_80.html</t>
         </is>
@@ -5372,17 +6514,32 @@
           <t>Recursos humanos e protocolos de revisão</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Implementação de processos de revisão de casos</t>
+        </is>
+      </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
+          <t>Dificuldades em identificar todos os pacientes necessários</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Falta de informação e registro adequado dos pacientes</t>
+        </is>
+      </c>
       <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr"/>
-      <c r="O82" s="2" t="inlineStr">
+      <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_81.html</t>
         </is>
@@ -5430,17 +6587,32 @@
           <t>Materiais para verificação e recursos humanos</t>
         </is>
       </c>
-      <c r="I83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>Implementação de processos de verificação</t>
+        </is>
+      </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="inlineStr"/>
+          <t>Dificuldades logísticas na distribuição de insumos</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>Falta de transporte e monitoramento adequado</t>
+        </is>
+      </c>
       <c r="L83" s="3" t="inlineStr"/>
-      <c r="M83" s="3" t="inlineStr"/>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N83" s="3" t="inlineStr"/>
-      <c r="O83" s="3" t="inlineStr">
+      <c r="O83" s="3" t="inlineStr"/>
+      <c r="P83" s="3" t="inlineStr"/>
+      <c r="Q83" s="3" t="inlineStr"/>
+      <c r="R83" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_82.html</t>
         </is>
@@ -5488,17 +6660,32 @@
           <t>Recursos para quantificação e logística</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Planejamento e execução de quantificação</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr"/>
+          <t>Dificuldades na previsão de demanda e suprimento</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Flutuações nas necessidades de insumos e falta de dados históricos</t>
+        </is>
+      </c>
       <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr"/>
-      <c r="O84" s="2" t="inlineStr">
+      <c r="O84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_83.html</t>
         </is>
@@ -5545,17 +6732,32 @@
           <t>Recursos humanos qualificados e materiais de apoio</t>
         </is>
       </c>
-      <c r="I85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>Planejamento e execução de supervisões</t>
+        </is>
+      </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr"/>
+          <t>Resistência dos profissionais em adotar novas práticas</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>Baixa motivação e falta de treinamento prévio</t>
+        </is>
+      </c>
       <c r="L85" s="3" t="inlineStr"/>
-      <c r="M85" s="3" t="inlineStr"/>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N85" s="3" t="inlineStr"/>
-      <c r="O85" s="3" t="inlineStr">
+      <c r="O85" s="3" t="inlineStr"/>
+      <c r="P85" s="3" t="inlineStr"/>
+      <c r="Q85" s="3" t="inlineStr"/>
+      <c r="R85" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_84.html</t>
         </is>
@@ -5602,17 +6804,32 @@
           <t>Recursos financeiros para aquisição de medicamentos</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Monitoramento de estoque e distribuição</t>
+        </is>
+      </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr"/>
+          <t>Falta de financiamento e recursos para aquisição de insumos</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Dependência de doações e flutuações na demanda</t>
+        </is>
+      </c>
       <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr"/>
-      <c r="O86" s="2" t="inlineStr">
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_85.html</t>
         </is>
@@ -5660,17 +6877,32 @@
           <t>Logística de transporte e recursos humanos</t>
         </is>
       </c>
-      <c r="I87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>Planejamento e execução de transporte de medicamentos</t>
+        </is>
+      </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K87" s="3" t="inlineStr"/>
+          <t>Dificuldades logísticas e falta de infraestrutura de transporte</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>Condições de estrada e segurança nas áreas rurais</t>
+        </is>
+      </c>
       <c r="L87" s="3" t="inlineStr"/>
-      <c r="M87" s="3" t="inlineStr"/>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N87" s="3" t="inlineStr"/>
-      <c r="O87" s="3" t="inlineStr">
+      <c r="O87" s="3" t="inlineStr"/>
+      <c r="P87" s="3" t="inlineStr"/>
+      <c r="Q87" s="3" t="inlineStr"/>
+      <c r="R87" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_86.html</t>
         </is>
@@ -5717,17 +6949,32 @@
           <t>Materiais de formação e recursos humanos</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Treinamento e distribuição dos manuais</t>
+        </is>
+      </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr"/>
+          <t>Resistência à adoção de novas práticas de gestão</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Falta de interesse e suporte institucional</t>
+        </is>
+      </c>
       <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr">
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_87.html</t>
         </is>
@@ -5774,17 +7021,32 @@
           <t>Recursos financeiros para aquisição de insumos</t>
         </is>
       </c>
-      <c r="I89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>Monitoramento do estoque e distribuição</t>
+        </is>
+      </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K89" s="3" t="inlineStr"/>
+          <t>Dificuldades na previsão e aquisição de insumos</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>Flutuações na necessidade de medicamentos e falta de dados históricos</t>
+        </is>
+      </c>
       <c r="L89" s="3" t="inlineStr"/>
-      <c r="M89" s="3" t="inlineStr"/>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N89" s="3" t="inlineStr"/>
-      <c r="O89" s="3" t="inlineStr">
+      <c r="O89" s="3" t="inlineStr"/>
+      <c r="P89" s="3" t="inlineStr"/>
+      <c r="Q89" s="3" t="inlineStr"/>
+      <c r="R89" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_88.html</t>
         </is>
@@ -5833,33 +7095,48 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
+          <t>Implementação de avaliações regulares</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Falta de dados precisos e confiáveis</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Desigualdade na coleta de dados e falta de capacitação</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="M90" s="2" t="inlineStr">
         <is>
           <t>249.000</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
+      <c r="N90" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L90" s="2" t="e">
+      <c r="O90" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="P90" s="2" t="inlineStr">
         <is>
           <t>3507.042253521127</t>
         </is>
       </c>
-      <c r="N90" s="2" t="inlineStr">
+      <c r="Q90" s="2" t="inlineStr">
         <is>
           <t># alcancado sao Unidade Santiarias</t>
         </is>
       </c>
-      <c r="O90" s="2" t="inlineStr">
+      <c r="R90" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_89.html</t>
         </is>
@@ -5908,19 +7185,34 @@
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
+          <t>Planejamento e execução de suprimentos</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas na entrega e distribuição de suprimentos</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>Falta de infraestrutura de transporte adequada</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K91" s="3" t="inlineStr"/>
-      <c r="L91" s="3" t="inlineStr"/>
-      <c r="M91" s="3" t="inlineStr"/>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N91" s="3" t="inlineStr"/>
-      <c r="O91" s="3" t="inlineStr">
+      <c r="O91" s="3" t="inlineStr"/>
+      <c r="P91" s="3" t="inlineStr"/>
+      <c r="Q91" s="3" t="inlineStr"/>
+      <c r="R91" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_90.html</t>
         </is>
@@ -5970,19 +7262,34 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
+          <t>Planejamento e execução de treinamentos</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Baixa adesão e resistência em comunidades locais</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Estigmas sociais e falta de informação</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr"/>
-      <c r="O92" s="2" t="inlineStr">
+      <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_91.html</t>
         </is>
@@ -6029,17 +7336,32 @@
           <t>Recursos para avaliação e monitoramento</t>
         </is>
       </c>
-      <c r="I93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>Revisão e avaliação anual do plano</t>
+        </is>
+      </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K93" s="3" t="inlineStr"/>
+          <t>Dificuldades em coletar dados de forma sistemática</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>Falta de coordenação entre diferentes níveis de gestão</t>
+        </is>
+      </c>
       <c r="L93" s="3" t="inlineStr"/>
-      <c r="M93" s="3" t="inlineStr"/>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N93" s="3" t="inlineStr"/>
-      <c r="O93" s="3" t="inlineStr">
+      <c r="O93" s="3" t="inlineStr"/>
+      <c r="P93" s="3" t="inlineStr"/>
+      <c r="Q93" s="3" t="inlineStr"/>
+      <c r="R93" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_92.html</t>
         </is>
@@ -6086,17 +7408,32 @@
           <t>Materiais de formação e logística para oficinas</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Planejamento e execução de oficinas</t>
+        </is>
+      </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr"/>
+          <t>Baixa participação devido a compromissos locais</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Conflitos de agenda e falta de interesse local</t>
+        </is>
+      </c>
       <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr"/>
-      <c r="O94" s="2" t="inlineStr">
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_93.html</t>
         </is>
@@ -6143,17 +7480,28 @@
           <t>equipamento de gravação, tempo, plataform de telesaude</t>
         </is>
       </c>
-      <c r="I95" s="3" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
+          <t>sem plataforma</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr"/>
       <c r="L95" s="3" t="inlineStr"/>
-      <c r="M95" s="3" t="inlineStr"/>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N95" s="3" t="inlineStr"/>
-      <c r="O95" s="3" t="inlineStr">
+      <c r="O95" s="3" t="inlineStr"/>
+      <c r="P95" s="3" t="inlineStr"/>
+      <c r="Q95" s="3" t="inlineStr"/>
+      <c r="R95" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_94.html</t>
         </is>
@@ -6201,17 +7549,32 @@
           <t>Recursos humanos e ferramentas para avaliação</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Implementação de rondas anuais</t>
+        </is>
+      </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr"/>
+          <t>Dificuldades na implementação de avaliações regulares</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Falta de recursos e motivação dos avaliadores</t>
+        </is>
+      </c>
       <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr"/>
-      <c r="O96" s="2" t="inlineStr">
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_95.html</t>
         </is>
@@ -6259,17 +7622,32 @@
           <t>Recursos para visitas e apoio técnico</t>
         </is>
       </c>
-      <c r="I97" s="3" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>Planejamento e execução de visitas de apoio</t>
+        </is>
+      </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr"/>
+          <t>Resistência à implementação de recomendações de melhoria</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>Falta de comprometimento dos profissionais envolvidos</t>
+        </is>
+      </c>
       <c r="L97" s="3" t="inlineStr"/>
-      <c r="M97" s="3" t="inlineStr"/>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N97" s="3" t="inlineStr"/>
-      <c r="O97" s="3" t="inlineStr">
+      <c r="O97" s="3" t="inlineStr"/>
+      <c r="P97" s="3" t="inlineStr"/>
+      <c r="Q97" s="3" t="inlineStr"/>
+      <c r="R97" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_96.html</t>
         </is>
@@ -6317,17 +7695,32 @@
           <t>Recursos tecnológicos e humanos para desenvolvimento</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Implementação e treinamento de uso de sistemas</t>
+        </is>
+      </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr"/>
+          <t>Dificuldades técnicas na implementação de sistemas</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Falta de formação e suporte técnico contínuo</t>
+        </is>
+      </c>
       <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr">
+      <c r="O98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_97.html</t>
         </is>
@@ -6375,17 +7768,32 @@
           <t>Recursos técnicos e humanos para desenvolvimento</t>
         </is>
       </c>
-      <c r="I99" s="3" t="inlineStr"/>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>Planejamento e implementação dos novos instrumentos</t>
+        </is>
+      </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="inlineStr"/>
+          <t>Resistência à adoção de novos sistemas por parte dos profissionais</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>Falta de capacitação e medo de mudanças</t>
+        </is>
+      </c>
       <c r="L99" s="3" t="inlineStr"/>
-      <c r="M99" s="3" t="inlineStr"/>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N99" s="3" t="inlineStr"/>
-      <c r="O99" s="3" t="inlineStr">
+      <c r="O99" s="3" t="inlineStr"/>
+      <c r="P99" s="3" t="inlineStr"/>
+      <c r="Q99" s="3" t="inlineStr"/>
+      <c r="R99" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_98.html</t>
         </is>
@@ -6433,17 +7841,24 @@
           <t>contratos de impressão</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Impressão, distribução</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr">
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_99.html</t>
         </is>
@@ -6490,17 +7905,32 @@
           <t>Recursos financeiros para aquisição de equipamentos</t>
         </is>
       </c>
-      <c r="I101" s="3" t="inlineStr"/>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>Identificação de necessidades e aquisição de equipamentos</t>
+        </is>
+      </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr"/>
+          <t>Falta de recursos financeiros e disponibilidade de equipamentos</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>Orçamentos limitados e concorrência por fundos</t>
+        </is>
+      </c>
       <c r="L101" s="3" t="inlineStr"/>
-      <c r="M101" s="3" t="inlineStr"/>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N101" s="3" t="inlineStr"/>
-      <c r="O101" s="3" t="inlineStr">
+      <c r="O101" s="3" t="inlineStr"/>
+      <c r="P101" s="3" t="inlineStr"/>
+      <c r="Q101" s="3" t="inlineStr"/>
+      <c r="R101" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_100.html</t>
         </is>
@@ -6543,17 +7973,32 @@
           <t>Recursos humanos qualificados e materiais de apoio</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Recrutamento e capacitação de assessores</t>
+        </is>
+      </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr"/>
+          <t>Dificuldade em encontrar profissionais qualificados</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Alto nível de rotatividade e falta de incentivos</t>
+        </is>
+      </c>
       <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr">
+      <c r="O102" s="2" t="inlineStr"/>
+      <c r="P102" s="2" t="inlineStr"/>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_101.html</t>
         </is>
@@ -6600,17 +8045,32 @@
           <t>Recursos financeiros para aquisição de licenças</t>
         </is>
       </c>
-      <c r="I103" s="3" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>Planejamento e compra de licenças</t>
+        </is>
+      </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr"/>
+          <t>Dificuldade em garantir a continuidade das licenças</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>Orçamentos limitados e gestão ineficaz das licenças</t>
+        </is>
+      </c>
       <c r="L103" s="3" t="inlineStr"/>
-      <c r="M103" s="3" t="inlineStr"/>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N103" s="3" t="inlineStr"/>
-      <c r="O103" s="3" t="inlineStr">
+      <c r="O103" s="3" t="inlineStr"/>
+      <c r="P103" s="3" t="inlineStr"/>
+      <c r="Q103" s="3" t="inlineStr"/>
+      <c r="R103" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_102.html</t>
         </is>
@@ -6657,17 +8117,32 @@
           <t>Recursos financeiros para serviços de comunicação</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Identificação de provedores e contratação de serviços</t>
+        </is>
+      </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr"/>
+          <t>Falta de infraestrutura de comunicação em áreas remotas</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas e custos elevados</t>
+        </is>
+      </c>
       <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr"/>
-      <c r="O104" s="2" t="inlineStr">
+      <c r="O104" s="2" t="inlineStr"/>
+      <c r="P104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_103.html</t>
         </is>
@@ -6716,31 +8191,46 @@
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
+          <t>Planejamento e execução dos ciclos PDSA</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>Resistência à mudança por parte dos profissionais</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>Falta de motivação e suporte institucional</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="J105" s="3" t="inlineStr">
+      <c r="M105" s="3" t="inlineStr">
         <is>
           <t>250.000</t>
         </is>
       </c>
-      <c r="K105" s="3" t="inlineStr">
+      <c r="N105" s="3" t="inlineStr">
         <is>
           <t>2.032.370</t>
         </is>
       </c>
-      <c r="L105" s="3" t="inlineStr">
+      <c r="O105" s="3" t="inlineStr">
         <is>
           <t>91.0%</t>
         </is>
       </c>
-      <c r="M105" s="3" t="inlineStr">
+      <c r="P105" s="3" t="inlineStr">
         <is>
           <t>0.1351748107687824</t>
         </is>
       </c>
-      <c r="N105" s="3" t="inlineStr"/>
-      <c r="O105" s="3" t="inlineStr">
+      <c r="Q105" s="3" t="inlineStr"/>
+      <c r="R105" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_104.html</t>
         </is>
@@ -6788,17 +8278,28 @@
           <t>equipamento de gravação, tempo, plataform de telesaude</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
+          <t>sem plataforma</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N106" s="2" t="inlineStr"/>
-      <c r="O106" s="2" t="inlineStr">
+      <c r="O106" s="2" t="inlineStr"/>
+      <c r="P106" s="2" t="inlineStr"/>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_105.html</t>
         </is>
@@ -6843,17 +8344,32 @@
           <t>Recursos humanos qualificados e capacitação</t>
         </is>
       </c>
-      <c r="I107" s="3" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>Recrutamento e formação de assessores</t>
+        </is>
+      </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K107" s="3" t="inlineStr"/>
+          <t>Dificuldade em reter profissionais qualificados</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>Alta rotatividade e falta de incentivos</t>
+        </is>
+      </c>
       <c r="L107" s="3" t="inlineStr"/>
-      <c r="M107" s="3" t="inlineStr"/>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N107" s="3" t="inlineStr"/>
-      <c r="O107" s="3" t="inlineStr">
+      <c r="O107" s="3" t="inlineStr"/>
+      <c r="P107" s="3" t="inlineStr"/>
+      <c r="Q107" s="3" t="inlineStr"/>
+      <c r="R107" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_106.html</t>
         </is>
@@ -6896,17 +8412,32 @@
           <t>Recursos humanos e materiais para elaboração</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Criação e validação do manual</t>
+        </is>
+      </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr"/>
+          <t>Resistência à adoção de novos procedimentos</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Falta de engajamento dos profissionais envolvidos</t>
+        </is>
+      </c>
       <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N108" s="2" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr">
+      <c r="O108" s="2" t="inlineStr"/>
+      <c r="P108" s="2" t="inlineStr"/>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_107.html</t>
         </is>
@@ -6950,17 +8481,32 @@
           <t>Recursos para campanhas de sensibilização</t>
         </is>
       </c>
-      <c r="I109" s="3" t="inlineStr"/>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>Implementação de campanhas de engajamento</t>
+        </is>
+      </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K109" s="3" t="inlineStr"/>
+          <t>Dificuldade em engajar a comunidade devido a estigmas sociais</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>Falta de confiança nas instituições de saúde</t>
+        </is>
+      </c>
       <c r="L109" s="3" t="inlineStr"/>
-      <c r="M109" s="3" t="inlineStr"/>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N109" s="3" t="inlineStr"/>
-      <c r="O109" s="3" t="inlineStr">
+      <c r="O109" s="3" t="inlineStr"/>
+      <c r="P109" s="3" t="inlineStr"/>
+      <c r="Q109" s="3" t="inlineStr"/>
+      <c r="R109" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_108.html</t>
         </is>
@@ -7004,17 +8550,32 @@
           <t>Recursos tecnológicos e humanos para implementação</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Planejamento e uso da ferramenta eletrónica</t>
+        </is>
+      </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr"/>
+          <t>Resistência à adoção de novas tecnologias</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Falta de formação e suporte técnico contínuo</t>
+        </is>
+      </c>
       <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N110" s="2" t="inlineStr"/>
-      <c r="O110" s="2" t="inlineStr">
+      <c r="O110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="inlineStr"/>
+      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_109.html</t>
         </is>
@@ -7058,17 +8619,32 @@
           <t>Recursos tecnológicos e humanos para desenvolvimento</t>
         </is>
       </c>
-      <c r="I111" s="3" t="inlineStr"/>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>Implementação e treinamento de uso de sistemas</t>
+        </is>
+      </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K111" s="3" t="inlineStr"/>
+          <t>Dificuldades técnicas na implementação de sistemas</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>Falta de formação e suporte técnico contínuo</t>
+        </is>
+      </c>
       <c r="L111" s="3" t="inlineStr"/>
-      <c r="M111" s="3" t="inlineStr"/>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N111" s="3" t="inlineStr"/>
-      <c r="O111" s="3" t="inlineStr">
+      <c r="O111" s="3" t="inlineStr"/>
+      <c r="P111" s="3" t="inlineStr"/>
+      <c r="Q111" s="3" t="inlineStr"/>
+      <c r="R111" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_110.html</t>
         </is>
@@ -7112,17 +8688,32 @@
           <t>Recursos humanos e materiais para implementação</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Planejamento e execução dos ciclos PDSA</t>
+        </is>
+      </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr"/>
+          <t>Resistência à mudança por parte dos profissionais</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Falta de motivação e suporte institucional</t>
+        </is>
+      </c>
       <c r="L112" s="2" t="inlineStr"/>
-      <c r="M112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N112" s="2" t="inlineStr"/>
-      <c r="O112" s="2" t="inlineStr">
+      <c r="O112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr"/>
+      <c r="Q112" s="2" t="inlineStr"/>
+      <c r="R112" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_111.html</t>
         </is>
@@ -7171,17 +8762,32 @@
           <t>Materiais de formação e recursos humanos</t>
         </is>
       </c>
-      <c r="I113" s="3" t="inlineStr"/>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>Realização de sessões de mentoria</t>
+        </is>
+      </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K113" s="3" t="inlineStr"/>
+          <t>Dificuldades na coordenação e logística das sessões</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>Falta de tempo e recursos dos profissionais envolvidos</t>
+        </is>
+      </c>
       <c r="L113" s="3" t="inlineStr"/>
-      <c r="M113" s="3" t="inlineStr"/>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N113" s="3" t="inlineStr"/>
-      <c r="O113" s="3" t="inlineStr">
+      <c r="O113" s="3" t="inlineStr"/>
+      <c r="P113" s="3" t="inlineStr"/>
+      <c r="Q113" s="3" t="inlineStr"/>
+      <c r="R113" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_112.html</t>
         </is>
@@ -7229,17 +8835,32 @@
           <t>Recursos tecnológicos e humanos para desenvolvimento</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Desenvolvimento e implementação do dashboard</t>
+        </is>
+      </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr"/>
+          <t>Falta de infraestrutura tecnológica em áreas remotas</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Dificuldades de conexão à internet e treinamento inadequado</t>
+        </is>
+      </c>
       <c r="L114" s="2" t="inlineStr"/>
-      <c r="M114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N114" s="2" t="inlineStr"/>
-      <c r="O114" s="2" t="inlineStr">
+      <c r="O114" s="2" t="inlineStr"/>
+      <c r="P114" s="2" t="inlineStr"/>
+      <c r="Q114" s="2" t="inlineStr"/>
+      <c r="R114" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_113.html</t>
         </is>
@@ -7287,17 +8908,32 @@
           <t>Recursos para logística e organização de eventos</t>
         </is>
       </c>
-      <c r="I115" s="3" t="inlineStr"/>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>Planejamento e execução da reunião</t>
+        </is>
+      </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K115" s="3" t="inlineStr"/>
+          <t>Baixa participação devido a compromissos locais</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>Falta de interesse ou motivação dos participantes</t>
+        </is>
+      </c>
       <c r="L115" s="3" t="inlineStr"/>
-      <c r="M115" s="3" t="inlineStr"/>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N115" s="3" t="inlineStr"/>
-      <c r="O115" s="3" t="inlineStr">
+      <c r="O115" s="3" t="inlineStr"/>
+      <c r="P115" s="3" t="inlineStr"/>
+      <c r="Q115" s="3" t="inlineStr"/>
+      <c r="R115" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_114.html</t>
         </is>
@@ -7348,17 +8984,24 @@
           <t>contratos de impressão</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Impressão, distribução</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N116" s="2" t="inlineStr"/>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O116" s="2" t="inlineStr"/>
+      <c r="P116" s="2" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr"/>
+      <c r="R116" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_115.html</t>
         </is>
@@ -7408,33 +9051,48 @@
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de PrEP Vaginal</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>Falta de adesão dos utentes ao uso da PrEP</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>Estigmas sociais e falta de informação sobre a PrEP</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J117" s="3" t="inlineStr">
+      <c r="M117" s="3" t="inlineStr">
         <is>
           <t>82.431</t>
         </is>
       </c>
-      <c r="K117" s="3" t="inlineStr">
+      <c r="N117" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L117" s="3" t="e">
+      <c r="O117" s="3" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="M117" s="3" t="inlineStr">
+      <c r="P117" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="N117" s="3" t="inlineStr">
+      <c r="Q117" s="3" t="inlineStr">
         <is>
           <t>Nao iniciou em 2024</t>
         </is>
       </c>
-      <c r="O117" s="3" t="inlineStr">
+      <c r="R117" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_116.html</t>
         </is>
@@ -7484,35 +9142,50 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de PrEP Injectável</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas na distribuição de insumos</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Falta de infraestrutura de saúde nas comunidades</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr">
+      <c r="M118" s="2" t="inlineStr">
         <is>
           <t>133.754</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr">
+      <c r="N118" s="2" t="inlineStr">
         <is>
           <t>3.185.533</t>
         </is>
       </c>
-      <c r="L118" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="M118" s="2" t="inlineStr">
+      <c r="P118" s="2" t="inlineStr">
         <is>
           <t>3715.393500000001</t>
         </is>
       </c>
-      <c r="N118" s="2" t="inlineStr">
+      <c r="Q118" s="2" t="inlineStr">
         <is>
           <t>36 RAMJ 15-24 em seguimento no ano 2024, pois foi o inicio do piloto</t>
         </is>
       </c>
-      <c r="O118" s="2" t="inlineStr">
+      <c r="R118" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_117.html</t>
         </is>
@@ -7562,31 +9235,46 @@
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de lubrificantes</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>Falta de conscientização sobre a importância do uso de lubrificantes</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>Desigualdade no acesso a insumos de saúde</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="J119" s="3" t="inlineStr">
+      <c r="M119" s="3" t="inlineStr">
         <is>
           <t>147.227</t>
         </is>
       </c>
-      <c r="K119" s="3" t="e">
+      <c r="N119" s="3" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="L119" s="3" t="e">
+      <c r="O119" s="3" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="M119" s="3" t="inlineStr">
+      <c r="P119" s="3" t="inlineStr">
         <is>
           <t>0.061678806032677</t>
         </is>
       </c>
-      <c r="N119" s="3" t="inlineStr">
+      <c r="Q119" s="3" t="inlineStr">
         <is>
           <t>dados de distribucao, Hom + Mulh 15-49</t>
         </is>
       </c>
-      <c r="O119" s="3" t="inlineStr">
+      <c r="R119" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_118.html</t>
         </is>
@@ -7636,33 +9324,48 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de medicamentos para ITS</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Falta de insumos e resistência ao tratamento</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>Falta de informação e educação em saúde</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
           <t>2021 (novo versao)</t>
         </is>
       </c>
-      <c r="J120" s="2" t="inlineStr">
+      <c r="M120" s="2" t="inlineStr">
         <is>
           <t>665.169</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr">
+      <c r="N120" s="2" t="inlineStr">
         <is>
           <t>todos utentes na US</t>
         </is>
       </c>
-      <c r="L120" s="2" t="e">
+      <c r="O120" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="M120" s="2" t="inlineStr">
+      <c r="P120" s="2" t="inlineStr">
         <is>
           <t>0.6309392820691827</t>
         </is>
       </c>
-      <c r="N120" s="2" t="inlineStr">
+      <c r="Q120" s="2" t="inlineStr">
         <is>
           <t>por causa de cobertura de livro de ITS não é possivel calcular um pop. Eligivel</t>
         </is>
       </c>
-      <c r="O120" s="2" t="inlineStr">
+      <c r="R120" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_119.html</t>
         </is>
@@ -7712,35 +9415,50 @@
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de preservativos</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>Dificuldades na aceitação e uso de preservativos</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>Barreiras culturais e sociais</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="J121" s="3" t="inlineStr">
+      <c r="M121" s="3" t="inlineStr">
         <is>
           <t>2.579.520</t>
         </is>
       </c>
-      <c r="K121" s="3" t="inlineStr">
+      <c r="N121" s="3" t="inlineStr">
         <is>
           <t>8.159.149</t>
         </is>
       </c>
-      <c r="L121" s="3" t="inlineStr">
+      <c r="O121" s="3" t="inlineStr">
         <is>
           <t>68.6%</t>
         </is>
       </c>
-      <c r="M121" s="3" t="inlineStr">
+      <c r="P121" s="3" t="inlineStr">
         <is>
           <t>0.4605463310123192</t>
         </is>
       </c>
-      <c r="N121" s="3" t="inlineStr">
+      <c r="Q121" s="3" t="inlineStr">
         <is>
           <t>dados de distribucao Mulher 15 - 49 anos</t>
         </is>
       </c>
-      <c r="O121" s="3" t="inlineStr">
+      <c r="R121" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_120.html</t>
         </is>
@@ -7790,35 +9508,50 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de PrEP Oral</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Baixa adesão dos utentes ao uso de PrEP Oral</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Estigmas e falta de informação sobre a PrEP</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="J122" s="2" t="inlineStr">
+      <c r="M122" s="2" t="inlineStr">
         <is>
           <t>5.527.092</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr">
+      <c r="N122" s="2" t="inlineStr">
         <is>
           <t>30.767.054</t>
         </is>
       </c>
-      <c r="L122" s="2" t="inlineStr">
+      <c r="O122" s="2" t="inlineStr">
         <is>
           <t>0.8%</t>
         </is>
       </c>
-      <c r="M122" s="2" t="inlineStr">
+      <c r="P122" s="2" t="inlineStr">
         <is>
           <t>21.33839519575633</t>
         </is>
       </c>
-      <c r="N122" s="2" t="inlineStr">
+      <c r="Q122" s="2" t="inlineStr">
         <is>
           <t>Novo inicios a PrEP para o ano 2024</t>
         </is>
       </c>
-      <c r="O122" s="2" t="inlineStr">
+      <c r="R122" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_121.html</t>
         </is>
@@ -7868,35 +9601,50 @@
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
+          <t>Implementação de campanhas de sensibilização e distribuição</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>Dificuldades na aceitação e uso de preservativos</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>Barreiras culturais e sociais</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="J123" s="3" t="inlineStr">
+      <c r="M123" s="3" t="inlineStr">
         <is>
           <t>7.491.341</t>
         </is>
       </c>
-      <c r="K123" s="3" t="inlineStr">
+      <c r="N123" s="3" t="inlineStr">
         <is>
           <t>7.388.905</t>
         </is>
       </c>
-      <c r="L123" s="3" t="inlineStr">
+      <c r="O123" s="3" t="inlineStr">
         <is>
           <t>21.810947630264565</t>
         </is>
       </c>
-      <c r="M123" s="3" t="inlineStr">
+      <c r="P123" s="3" t="inlineStr">
         <is>
           <t>0.04648415651820172</t>
         </is>
       </c>
-      <c r="N123" s="3" t="inlineStr">
+      <c r="Q123" s="3" t="inlineStr">
         <is>
           <t>dados de distribucao Homen 15 - 49 anos</t>
         </is>
       </c>
-      <c r="O123" s="3" t="inlineStr">
+      <c r="R123" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_122.html</t>
         </is>
@@ -7945,19 +9693,34 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
+          <t>Planejamento e execução de formações</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Resistência dos profissionais à formação</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>Falta de motivação e tempo disponível</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="inlineStr"/>
-      <c r="M124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N124" s="2" t="inlineStr"/>
-      <c r="O124" s="2" t="inlineStr">
+      <c r="O124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr"/>
+      <c r="Q124" s="2" t="inlineStr"/>
+      <c r="R124" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_123.html</t>
         </is>
@@ -8006,19 +9769,34 @@
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de suprimentos</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas na entrega de suprimentos</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>Infraestrutura inadequada em áreas remotas</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K125" s="3" t="inlineStr"/>
-      <c r="L125" s="3" t="inlineStr"/>
-      <c r="M125" s="3" t="inlineStr"/>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N125" s="3" t="inlineStr"/>
-      <c r="O125" s="3" t="inlineStr">
+      <c r="O125" s="3" t="inlineStr"/>
+      <c r="P125" s="3" t="inlineStr"/>
+      <c r="Q125" s="3" t="inlineStr"/>
+      <c r="R125" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_124.html</t>
         </is>
@@ -8065,17 +9843,32 @@
           <t>Materiais de capacitação e recursos humanos</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>Treinamento e capacitação de pessoal leigo</t>
+        </is>
+      </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K126" s="2" t="inlineStr"/>
+          <t>Resistência à mudança e falta de conhecimento sobre PrEP</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>Estigmas associados à utilização de PrEP</t>
+        </is>
+      </c>
       <c r="L126" s="2" t="inlineStr"/>
-      <c r="M126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N126" s="2" t="inlineStr"/>
-      <c r="O126" s="2" t="inlineStr">
+      <c r="O126" s="2" t="inlineStr"/>
+      <c r="P126" s="2" t="inlineStr"/>
+      <c r="Q126" s="2" t="inlineStr"/>
+      <c r="R126" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_125.html</t>
         </is>
@@ -8123,17 +9916,32 @@
           <t>Medicamentos e insumos para PrEP</t>
         </is>
       </c>
-      <c r="I127" s="3" t="inlineStr"/>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>Aquisição e distribuição de PrEP</t>
+        </is>
+      </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K127" s="3" t="inlineStr"/>
+          <t>Dificuldades logísticas na distribuição de insumos</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>Falta de infraestrutura de saúde nas comunidades</t>
+        </is>
+      </c>
       <c r="L127" s="3" t="inlineStr"/>
-      <c r="M127" s="3" t="inlineStr"/>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N127" s="3" t="inlineStr"/>
-      <c r="O127" s="3" t="inlineStr">
+      <c r="O127" s="3" t="inlineStr"/>
+      <c r="P127" s="3" t="inlineStr"/>
+      <c r="Q127" s="3" t="inlineStr"/>
+      <c r="R127" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_126.html</t>
         </is>
@@ -8181,17 +9989,32 @@
           <t>Recursos humanos e materiais para monitoramento</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Planejamento e execução de visitas de monitoria</t>
+        </is>
+      </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K128" s="2" t="inlineStr"/>
+          <t>Baixa adesão e resistência dos profissionais de saúde</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>Falta de motivação e apoio institucional</t>
+        </is>
+      </c>
       <c r="L128" s="2" t="inlineStr"/>
-      <c r="M128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N128" s="2" t="inlineStr"/>
-      <c r="O128" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr"/>
+      <c r="R128" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_127.html</t>
         </is>
@@ -8239,17 +10062,32 @@
           <t>Recursos para campanhas de sensibilização</t>
         </is>
       </c>
-      <c r="I129" s="3" t="inlineStr"/>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>Implementação de estratégias de criação de demanda</t>
+        </is>
+      </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K129" s="3" t="inlineStr"/>
+          <t>Dificuldades de engajamento da comunidade</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>Falta de informação e confiança nas instituições de saúde</t>
+        </is>
+      </c>
       <c r="L129" s="3" t="inlineStr"/>
-      <c r="M129" s="3" t="inlineStr"/>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N129" s="3" t="inlineStr"/>
-      <c r="O129" s="3" t="inlineStr">
+      <c r="O129" s="3" t="inlineStr"/>
+      <c r="P129" s="3" t="inlineStr"/>
+      <c r="Q129" s="3" t="inlineStr"/>
+      <c r="R129" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_128.html</t>
         </is>
@@ -8297,17 +10135,32 @@
           <t>Recursos para campanhas de sensibilização</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Implementação de estratégias de criação de demanda</t>
+        </is>
+      </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K130" s="2" t="inlineStr"/>
+          <t>Resistência à adoção de novas tecnologias</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Falta de formação e suporte técnico contínuo</t>
+        </is>
+      </c>
       <c r="L130" s="2" t="inlineStr"/>
-      <c r="M130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N130" s="2" t="inlineStr"/>
-      <c r="O130" s="2" t="inlineStr">
+      <c r="O130" s="2" t="inlineStr"/>
+      <c r="P130" s="2" t="inlineStr"/>
+      <c r="Q130" s="2" t="inlineStr"/>
+      <c r="R130" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_129.html</t>
         </is>
@@ -8355,17 +10208,24 @@
           <t>contratos de impressão</t>
         </is>
       </c>
-      <c r="I131" s="3" t="inlineStr"/>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>Impressão, distribução</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr"/>
       <c r="K131" s="3" t="inlineStr"/>
       <c r="L131" s="3" t="inlineStr"/>
-      <c r="M131" s="3" t="inlineStr"/>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N131" s="3" t="inlineStr"/>
-      <c r="O131" s="3" t="inlineStr">
+      <c r="O131" s="3" t="inlineStr"/>
+      <c r="P131" s="3" t="inlineStr"/>
+      <c r="Q131" s="3" t="inlineStr"/>
+      <c r="R131" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_130.html</t>
         </is>
@@ -8412,17 +10272,32 @@
           <t>Materiais de formação e recursos humanos</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Treinamento e capacitação de profissionais</t>
+        </is>
+      </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr"/>
+          <t>Dificuldades em manter a qualidade das formações</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Rotatividade alta de profissionais e falta de motivação</t>
+        </is>
+      </c>
       <c r="L132" s="2" t="inlineStr"/>
-      <c r="M132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N132" s="2" t="inlineStr"/>
-      <c r="O132" s="2" t="inlineStr">
+      <c r="O132" s="2" t="inlineStr"/>
+      <c r="P132" s="2" t="inlineStr"/>
+      <c r="Q132" s="2" t="inlineStr"/>
+      <c r="R132" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_131.html</t>
         </is>
@@ -8469,17 +10344,32 @@
           <t>Recursos para a realização da reunião</t>
         </is>
       </c>
-      <c r="I133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>Planejamento e execução da reunião</t>
+        </is>
+      </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K133" s="3" t="inlineStr"/>
+          <t>Baixa participação devido a compromissos locais</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>Falta de interesse e motivação dos participantes</t>
+        </is>
+      </c>
       <c r="L133" s="3" t="inlineStr"/>
-      <c r="M133" s="3" t="inlineStr"/>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N133" s="3" t="inlineStr"/>
-      <c r="O133" s="3" t="inlineStr">
+      <c r="O133" s="3" t="inlineStr"/>
+      <c r="P133" s="3" t="inlineStr"/>
+      <c r="Q133" s="3" t="inlineStr"/>
+      <c r="R133" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_132.html</t>
         </is>
@@ -8529,33 +10419,48 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição dos medicamentos</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas na distribuição de medicamentos</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Falta de infraestrutura adequada nas unidades de saúde</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="M134" s="2" t="inlineStr">
         <is>
           <t>48.899</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
+      <c r="N134" s="2" t="inlineStr">
         <is>
           <t>36.171</t>
         </is>
       </c>
-      <c r="L134" s="2" t="inlineStr">
+      <c r="O134" s="2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="M134" s="2" t="e">
+      <c r="P134" s="2" t="e">
         <v>#DIV/0!</v>
       </c>
-      <c r="N134" s="2" t="inlineStr">
+      <c r="Q134" s="2" t="inlineStr">
         <is>
           <t>Carga Viral para VHB nao foi implmentado em 2024</t>
         </is>
       </c>
-      <c r="O134" s="2" t="inlineStr">
+      <c r="R134" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_133.html</t>
         </is>
@@ -8605,35 +10510,50 @@
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição dos medicamentos</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>Dificuldades de acesso e resistência ao tratamento</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>Estigmas sociais e falta de informação sobre Hepatite B</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="J135" s="3" t="inlineStr">
+      <c r="M135" s="3" t="inlineStr">
         <is>
           <t>469.080</t>
         </is>
       </c>
-      <c r="K135" s="3" t="inlineStr">
+      <c r="N135" s="3" t="inlineStr">
         <is>
           <t>36.171</t>
         </is>
       </c>
-      <c r="L135" s="3" t="inlineStr">
+      <c r="O135" s="3" t="inlineStr">
         <is>
           <t>89.1%</t>
         </is>
       </c>
-      <c r="M135" s="3" t="inlineStr">
+      <c r="P135" s="3" t="inlineStr">
         <is>
           <t>14.55053042992741</t>
         </is>
       </c>
-      <c r="N135" s="3" t="inlineStr">
+      <c r="Q135" s="3" t="inlineStr">
         <is>
           <t>Ainda foi um piloto ate o fim de 2024, em MC tinha 7,615, Nampula 18,706, Sofala 5,917</t>
         </is>
       </c>
-      <c r="O135" s="3" t="inlineStr">
+      <c r="R135" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_134.html</t>
         </is>
@@ -8683,33 +10603,48 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de medicamentos</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas na distribuição de medicamentos</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Falta de infraestrutura nas unidades de saúde</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
           <t>&lt;2018</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="M136" s="2" t="inlineStr">
         <is>
           <t>750.350</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr">
+      <c r="N136" s="2" t="inlineStr">
         <is>
           <t>Pessoas com sinais ou sintomas</t>
         </is>
       </c>
-      <c r="L136" s="2" t="e">
+      <c r="O136" s="2" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="M136" s="2" t="inlineStr">
+      <c r="P136" s="2" t="inlineStr">
         <is>
           <t>2.041635729911516</t>
         </is>
       </c>
-      <c r="N136" s="2" t="inlineStr">
+      <c r="Q136" s="2" t="inlineStr">
         <is>
           <t>testados para Sifilis no livro de ITS</t>
         </is>
       </c>
-      <c r="O136" s="2" t="inlineStr">
+      <c r="R136" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_135.html</t>
         </is>
@@ -8759,35 +10694,50 @@
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de ARVs</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>Resistência ao tratamento e falta de adesão</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>Estigmas sociais e falta de informação sobre HIV</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
           <t>&lt;2015</t>
         </is>
       </c>
-      <c r="J137" s="3" t="inlineStr">
+      <c r="M137" s="3" t="inlineStr">
         <is>
           <t>884.603</t>
         </is>
       </c>
-      <c r="K137" s="3" t="inlineStr">
+      <c r="N137" s="3" t="inlineStr">
         <is>
           <t>134.000</t>
         </is>
       </c>
-      <c r="L137" s="3" t="inlineStr">
+      <c r="O137" s="3" t="inlineStr">
         <is>
           <t>81.8%</t>
         </is>
       </c>
-      <c r="M137" s="3" t="inlineStr">
+      <c r="P137" s="3" t="inlineStr">
         <is>
           <t>8.066636253214423</t>
         </is>
       </c>
-      <c r="N137" s="3" t="inlineStr">
+      <c r="Q137" s="3" t="inlineStr">
         <is>
           <t>MG HIV+ na CPN</t>
         </is>
       </c>
-      <c r="O137" s="3" t="inlineStr">
+      <c r="R137" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_136.html</t>
         </is>
@@ -8837,31 +10787,46 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de medicamentos</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas e acesso limitado a medicamentos</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Falta de recursos financeiros e humanos</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="M138" s="2" t="inlineStr">
         <is>
           <t>2.786.852</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
+      <c r="N138" s="2" t="inlineStr">
         <is>
           <t>2.111.754</t>
         </is>
       </c>
-      <c r="L138" s="2" t="inlineStr">
+      <c r="O138" s="2" t="inlineStr">
         <is>
           <t>99.0%</t>
         </is>
       </c>
-      <c r="M138" s="2" t="inlineStr">
+      <c r="P138" s="2" t="inlineStr">
         <is>
           <t>1.33270233448056</t>
         </is>
       </c>
-      <c r="N138" s="2" t="inlineStr"/>
-      <c r="O138" s="2" t="inlineStr">
+      <c r="Q138" s="2" t="inlineStr"/>
+      <c r="R138" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_137.html</t>
         </is>
@@ -8910,19 +10875,34 @@
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
+          <t>Planejamento e execução de treinamentos</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>Falta de adesão dos profissionais às novas práticas</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>Resistência à mudança e falta de suporte institucional</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K139" s="3" t="inlineStr"/>
-      <c r="L139" s="3" t="inlineStr"/>
-      <c r="M139" s="3" t="inlineStr"/>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N139" s="3" t="inlineStr"/>
-      <c r="O139" s="3" t="inlineStr">
+      <c r="O139" s="3" t="inlineStr"/>
+      <c r="P139" s="3" t="inlineStr"/>
+      <c r="Q139" s="3" t="inlineStr"/>
+      <c r="R139" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_138.html</t>
         </is>
@@ -8971,19 +10951,34 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de suprimentos</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>Dificuldades na gestão de inventário e distribuição</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Falta de controle e supervisão adequados</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="2" t="inlineStr"/>
-      <c r="M140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N140" s="2" t="inlineStr"/>
-      <c r="O140" s="2" t="inlineStr">
+      <c r="O140" s="2" t="inlineStr"/>
+      <c r="P140" s="2" t="inlineStr"/>
+      <c r="Q140" s="2" t="inlineStr"/>
+      <c r="R140" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_139.html</t>
         </is>
@@ -9032,27 +11027,42 @@
       </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
+          <t>Planejamento e execução do sistema</t>
         </is>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
+          <t>Dificuldades na aceitação do sistema por parte dos profissionais</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
+          <t>Resistência a novas tecnologias e falta de capacitação</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>Mulher Lactante  e pacientes HIV+                                                                                                                                                                                  ESMI</t>
         </is>
       </c>
-      <c r="L141" s="3" t="inlineStr">
+      <c r="O141" s="3" t="inlineStr">
         <is>
           <t>Todas as US AJUDA (149) Manica (51), Niassa(18), Sofala (47) e Tete (33)</t>
         </is>
       </c>
-      <c r="M141" s="3" t="inlineStr"/>
-      <c r="N141" s="3" t="inlineStr"/>
-      <c r="O141" s="3" t="inlineStr">
+      <c r="P141" s="3" t="inlineStr"/>
+      <c r="Q141" s="3" t="inlineStr"/>
+      <c r="R141" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_140.html</t>
         </is>
@@ -9100,17 +11110,32 @@
           <t>Recursos humanos e materiais para implementação</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Monitoramento e avaliação contínua</t>
+        </is>
+      </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K142" s="2" t="inlineStr"/>
+          <t>Baixa adesão e resistência da comunidade</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Falta de conscientização e educação em saúde</t>
+        </is>
+      </c>
       <c r="L142" s="2" t="inlineStr"/>
-      <c r="M142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N142" s="2" t="inlineStr"/>
-      <c r="O142" s="2" t="inlineStr">
+      <c r="O142" s="2" t="inlineStr"/>
+      <c r="P142" s="2" t="inlineStr"/>
+      <c r="Q142" s="2" t="inlineStr"/>
+      <c r="R142" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_141.html</t>
         </is>
@@ -9157,17 +11182,32 @@
           <t>Recursos para logística e organização de reuniões</t>
         </is>
       </c>
-      <c r="I143" s="3" t="inlineStr"/>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>Planejamento e execução de reuniões</t>
+        </is>
+      </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K143" s="3" t="inlineStr"/>
+          <t>Dificuldades de participação e comprometimento</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>Falta de interesse e motivação dos participantes</t>
+        </is>
+      </c>
       <c r="L143" s="3" t="inlineStr"/>
-      <c r="M143" s="3" t="inlineStr"/>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N143" s="3" t="inlineStr"/>
-      <c r="O143" s="3" t="inlineStr">
+      <c r="O143" s="3" t="inlineStr"/>
+      <c r="P143" s="3" t="inlineStr"/>
+      <c r="Q143" s="3" t="inlineStr"/>
+      <c r="R143" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_142.html</t>
         </is>
@@ -9214,17 +11254,28 @@
           <t>equipamento de gravação, tempo, plataform de telesaude</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
+          <t>sem plataforma</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr"/>
-      <c r="M144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N144" s="2" t="inlineStr"/>
-      <c r="O144" s="2" t="inlineStr">
+      <c r="O144" s="2" t="inlineStr"/>
+      <c r="P144" s="2" t="inlineStr"/>
+      <c r="Q144" s="2" t="inlineStr"/>
+      <c r="R144" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_143.html</t>
         </is>
@@ -9272,17 +11323,32 @@
           <t>Recursos humanos e materiais necessários</t>
         </is>
       </c>
-      <c r="I145" s="3" t="inlineStr"/>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>Implementação de monitoramentos</t>
+        </is>
+      </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K145" s="3" t="inlineStr"/>
+          <t>Dificuldades em logística de material</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>Estigmas e crenças em comunidades locais</t>
+        </is>
+      </c>
       <c r="L145" s="3" t="inlineStr"/>
-      <c r="M145" s="3" t="inlineStr"/>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N145" s="3" t="inlineStr"/>
-      <c r="O145" s="3" t="inlineStr">
+      <c r="O145" s="3" t="inlineStr"/>
+      <c r="P145" s="3" t="inlineStr"/>
+      <c r="Q145" s="3" t="inlineStr"/>
+      <c r="R145" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_144.html</t>
         </is>
@@ -9330,17 +11396,32 @@
           <t>Recursos humanos e materiais para avaliação</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Planejamento e execução da avaliação</t>
+        </is>
+      </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K146" s="2" t="inlineStr"/>
+          <t>Dificuldades na coleta de dados e resistência dos profissionais</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Falta de motivação e apoio institucional</t>
+        </is>
+      </c>
       <c r="L146" s="2" t="inlineStr"/>
-      <c r="M146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N146" s="2" t="inlineStr"/>
-      <c r="O146" s="2" t="inlineStr">
+      <c r="O146" s="2" t="inlineStr"/>
+      <c r="P146" s="2" t="inlineStr"/>
+      <c r="Q146" s="2" t="inlineStr"/>
+      <c r="R146" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_145.html</t>
         </is>
@@ -9387,17 +11468,32 @@
           <t>Recursos humanos qualificados e materiais de apoio</t>
         </is>
       </c>
-      <c r="I147" s="3" t="inlineStr"/>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>Recrutamento e capacitação de assessores</t>
+        </is>
+      </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K147" s="3" t="inlineStr"/>
+          <t>Dificuldade em reter profissionais qualificados</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>Alta rotatividade e falta de incentivos</t>
+        </is>
+      </c>
       <c r="L147" s="3" t="inlineStr"/>
-      <c r="M147" s="3" t="inlineStr"/>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N147" s="3" t="inlineStr"/>
-      <c r="O147" s="3" t="inlineStr">
+      <c r="O147" s="3" t="inlineStr"/>
+      <c r="P147" s="3" t="inlineStr"/>
+      <c r="Q147" s="3" t="inlineStr"/>
+      <c r="R147" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_146.html</t>
         </is>
@@ -9444,17 +11540,32 @@
           <t>Recursos financeiros para contratação</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Processo de recrutamento e seleção</t>
+        </is>
+      </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K148" s="2" t="inlineStr"/>
+          <t>Dificuldades na atração de profissionais para áreas remotas</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>Condições de trabalho e falta de incentivos</t>
+        </is>
+      </c>
       <c r="L148" s="2" t="inlineStr"/>
-      <c r="M148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N148" s="2" t="inlineStr"/>
-      <c r="O148" s="2" t="inlineStr">
+      <c r="O148" s="2" t="inlineStr"/>
+      <c r="P148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr"/>
+      <c r="R148" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_147.html</t>
         </is>
@@ -9501,17 +11612,32 @@
           <t>Materiais de formação e recursos humanos</t>
         </is>
       </c>
-      <c r="I149" s="3" t="inlineStr"/>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>Planejamento e execução de treinamentos</t>
+        </is>
+      </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K149" s="3" t="inlineStr"/>
+          <t>Resistência à adoção de novas práticas de cuidado</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>Falta de suporte e motivação dos cuidadores</t>
+        </is>
+      </c>
       <c r="L149" s="3" t="inlineStr"/>
-      <c r="M149" s="3" t="inlineStr"/>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N149" s="3" t="inlineStr"/>
-      <c r="O149" s="3" t="inlineStr">
+      <c r="O149" s="3" t="inlineStr"/>
+      <c r="P149" s="3" t="inlineStr"/>
+      <c r="Q149" s="3" t="inlineStr"/>
+      <c r="R149" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_148.html</t>
         </is>
@@ -9559,17 +11685,32 @@
           <t>Recursos para desenvolvimento de materiais de comunicação</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Criação e distribuição de materiais IEC</t>
+        </is>
+      </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K150" s="2" t="inlineStr"/>
+          <t>Dificuldades na aceitação e disseminação do material</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>Falta de interesse e confiança nas mensagens de saúde</t>
+        </is>
+      </c>
       <c r="L150" s="2" t="inlineStr"/>
-      <c r="M150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N150" s="2" t="inlineStr"/>
-      <c r="O150" s="2" t="inlineStr">
+      <c r="O150" s="2" t="inlineStr"/>
+      <c r="P150" s="2" t="inlineStr"/>
+      <c r="Q150" s="2" t="inlineStr"/>
+      <c r="R150" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_149.html</t>
         </is>
@@ -9617,17 +11758,24 @@
           <t>contratos de impressão</t>
         </is>
       </c>
-      <c r="I151" s="3" t="inlineStr"/>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>Impressão, distribução</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr"/>
       <c r="K151" s="3" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr"/>
-      <c r="M151" s="3" t="inlineStr"/>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N151" s="3" t="inlineStr"/>
-      <c r="O151" s="3" t="inlineStr">
+      <c r="O151" s="3" t="inlineStr"/>
+      <c r="P151" s="3" t="inlineStr"/>
+      <c r="Q151" s="3" t="inlineStr"/>
+      <c r="R151" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_150.html</t>
         </is>
@@ -9675,17 +11823,32 @@
           <t>Recursos para pesquisa e coleta de dados</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Realização de estudos e entrevistas com a comunidade</t>
+        </is>
+      </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K152" s="2" t="inlineStr"/>
+          <t>Dificuldades em alcançar comunidades remotas e resistência à pesquisa</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>Falta de confiança nas instituições de saúde e estigmas sociais</t>
+        </is>
+      </c>
       <c r="L152" s="2" t="inlineStr"/>
-      <c r="M152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N152" s="2" t="inlineStr"/>
-      <c r="O152" s="2" t="inlineStr">
+      <c r="O152" s="2" t="inlineStr"/>
+      <c r="P152" s="2" t="inlineStr"/>
+      <c r="Q152" s="2" t="inlineStr"/>
+      <c r="R152" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_151.html</t>
         </is>
@@ -9735,31 +11898,46 @@
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de medicamentos</t>
+        </is>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas e resistência ao tratamento</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>Falta de conscientização sobre TB e suas implicações</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="J153" s="3" t="inlineStr">
+      <c r="M153" s="3" t="inlineStr">
         <is>
           <t>3.674.196</t>
         </is>
       </c>
-      <c r="K153" s="3" t="inlineStr">
+      <c r="N153" s="3" t="inlineStr">
         <is>
           <t>266.240</t>
         </is>
       </c>
-      <c r="L153" s="3" t="inlineStr">
+      <c r="O153" s="3" t="inlineStr">
         <is>
           <t>93.2%</t>
         </is>
       </c>
-      <c r="M153" s="3" t="inlineStr">
+      <c r="P153" s="3" t="inlineStr">
         <is>
           <t>14.80509942741094</t>
         </is>
       </c>
-      <c r="N153" s="3" t="inlineStr"/>
-      <c r="O153" s="3" t="inlineStr">
+      <c r="Q153" s="3" t="inlineStr"/>
+      <c r="R153" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_152.html</t>
         </is>
@@ -9808,19 +11986,34 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
+          <t>Planejamento e execução de treinamentos</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Baixa participação dos profissionais de saúde pediátrica</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>Falta de interesse e motivação</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="2" t="inlineStr"/>
-      <c r="M154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N154" s="2" t="inlineStr"/>
-      <c r="O154" s="2" t="inlineStr">
+      <c r="O154" s="2" t="inlineStr"/>
+      <c r="P154" s="2" t="inlineStr"/>
+      <c r="Q154" s="2" t="inlineStr"/>
+      <c r="R154" s="2" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_153.html</t>
         </is>
@@ -9869,19 +12062,34 @@
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
+          <t>Aquisição e distribuição de suprimentos</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>Dificuldades logísticas na entrega de medicamentos</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>Infraestrutura inadequada em áreas remotas</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>Sem Informação</t>
-        </is>
-      </c>
-      <c r="K155" s="3" t="inlineStr"/>
-      <c r="L155" s="3" t="inlineStr"/>
-      <c r="M155" s="3" t="inlineStr"/>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>Sem Informação</t>
+        </is>
+      </c>
       <c r="N155" s="3" t="inlineStr"/>
-      <c r="O155" s="3" t="inlineStr">
+      <c r="O155" s="3" t="inlineStr"/>
+      <c r="P155" s="3" t="inlineStr"/>
+      <c r="Q155" s="3" t="inlineStr"/>
+      <c r="R155" s="3" t="inlineStr">
         <is>
           <t>https://kaiserso.github.io/INS_delphi/hiv/hiv_154.html</t>
         </is>
